--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -2538,7 +2538,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one recall</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D266"/>
+  <dimension ref="A1:D268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11745,7 +11745,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -11753,32 +11753,32 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>A family member already working here</t>
+          <t>Month by month</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>यहाँ पहले से काम कर रहा घरवाला</t>
+          <t>हर महीने का अलग-अलग</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>A friend or someone from the village</t>
+          <t>One total for the whole year</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>दोस्त या गाँव का कोई आदमी</t>
+          <t>पूरे साल का एक जोड़</t>
         </is>
       </c>
     </row>
@@ -11789,16 +11789,16 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>A thekedar or contractor I now work for</t>
+          <t>A family member already working here</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
+          <t>यहाँ पहले से काम कर रहा घरवाला</t>
         </is>
       </c>
     </row>
@@ -11809,16 +11809,16 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>An agent or middleman who placed me (usually for a fee)</t>
+          <t>A friend or someone from the village</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
+          <t>दोस्त या गाँव का कोई आदमी</t>
         </is>
       </c>
     </row>
@@ -11829,16 +11829,16 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>No one; I found it myself</t>
+          <t>A thekedar or contractor I now work for</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>कोई नहीं, ख़ुद ढूँढा</t>
+          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
         </is>
       </c>
     </row>
@@ -11849,16 +11849,16 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>The employer called me directly</t>
+          <t>An agent or middleman who placed me (usually for a fee)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>मालिक ने सीधे बुलाया</t>
+          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
         </is>
       </c>
     </row>
@@ -11869,56 +11869,56 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Someone else</t>
+          <t>No one; I found it myself</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>कोई नहीं, ख़ुद ढूँढा</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bank transfer</t>
+          <t>The employer called me directly</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>बैंक से</t>
+          <t>मालिक ने सीधे बुलाया</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>UPI or phone payment</t>
+          <t>Someone else</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>UPI या फ़ोन से</t>
+          <t>कोई और</t>
         </is>
       </c>
     </row>
@@ -11929,16 +11929,16 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Money order or post office</t>
+          <t>Bank transfer</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>मनीऑर्डर या डाकघर से</t>
+          <t>बैंक से</t>
         </is>
       </c>
     </row>
@@ -11949,16 +11949,16 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Sent with someone going home</t>
+          <t>UPI or phone payment</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>घर जा रहे किसी के हाथ</t>
+          <t>UPI या फ़ोन से</t>
         </is>
       </c>
     </row>
@@ -11969,16 +11969,16 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Carried it myself</t>
+          <t>Money order or post office</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>ख़ुद लेकर गए</t>
+          <t>मनीऑर्डर या डाकघर से</t>
         </is>
       </c>
     </row>
@@ -11989,56 +11989,56 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sent with someone going home</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>कोई और तरीक़ा</t>
+          <t>घर जा रहे किसी के हाथ</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Thatch/wood/mud</t>
+          <t>Carried it myself</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>फूस/लकड़ी/मिट्टी</t>
+          <t>ख़ुद लेकर गए</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tin/GI sheet</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>टीन/चादर</t>
+          <t>कोई और तरीक़ा</t>
         </is>
       </c>
     </row>
@@ -12049,96 +12049,96 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Concrete/RCC</t>
+          <t>Thatch/wood/mud</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>छत (कंक्रीट/RCC)</t>
+          <t>फूस/लकड़ी/मिट्टी</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Tin/GI sheet</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>टीन/चादर</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Concrete/RCC</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>छत (कंक्रीट/RCC)</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>पक्ष में</t>
+          <t>पुरुष</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>बीच में</t>
+          <t>महिला</t>
         </is>
       </c>
     </row>
@@ -12149,16 +12149,16 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>ख़िलाफ़</t>
+          <t>पक्ष में</t>
         </is>
       </c>
     </row>
@@ -12169,56 +12169,56 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Don't know / prefer not to say</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>पता नहीं / बताना नहीं चाहते</t>
+          <t>बीच में</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>ख़िलाफ़</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Don't know / prefer not to say</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>पता नहीं / बताना नहीं चाहते</t>
         </is>
       </c>
     </row>
@@ -12229,16 +12229,16 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
     </row>
@@ -12249,16 +12249,16 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
     </row>
@@ -12269,16 +12269,16 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>असम</t>
         </is>
       </c>
     </row>
@@ -12289,16 +12289,16 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>बिहार</t>
         </is>
       </c>
     </row>
@@ -12309,16 +12309,16 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
     </row>
@@ -12329,16 +12329,16 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>गोवा</t>
         </is>
       </c>
     </row>
@@ -12349,16 +12349,16 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>गुजरात</t>
         </is>
       </c>
     </row>
@@ -12369,16 +12369,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>हरियाणा</t>
         </is>
       </c>
     </row>
@@ -12389,16 +12389,16 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
     </row>
@@ -12409,16 +12409,16 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>झारखंड</t>
         </is>
       </c>
     </row>
@@ -12429,16 +12429,16 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
     </row>
@@ -12449,16 +12449,16 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>केरल</t>
         </is>
       </c>
     </row>
@@ -12469,16 +12469,16 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
     </row>
@@ -12489,16 +12489,16 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
     </row>
@@ -12509,16 +12509,16 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>मणिपुर</t>
         </is>
       </c>
     </row>
@@ -12529,16 +12529,16 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>मेघालय</t>
         </is>
       </c>
     </row>
@@ -12549,16 +12549,16 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
     </row>
@@ -12569,16 +12569,16 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>नागालैंड</t>
         </is>
       </c>
     </row>
@@ -12589,16 +12589,16 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>ओडिशा</t>
         </is>
       </c>
     </row>
@@ -12609,16 +12609,16 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>पंजाब</t>
         </is>
       </c>
     </row>
@@ -12629,16 +12629,16 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>राजस्थान</t>
         </is>
       </c>
     </row>
@@ -12649,16 +12649,16 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>सिक्किम</t>
         </is>
       </c>
     </row>
@@ -12669,16 +12669,16 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
     </row>
@@ -12689,16 +12689,16 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
     </row>
@@ -12709,16 +12709,16 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>उत्तराखंड</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
     </row>
@@ -12729,16 +12729,16 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
     </row>
@@ -12749,16 +12749,16 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>उत्तराखंड</t>
         </is>
       </c>
     </row>
@@ -12769,16 +12769,16 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
     </row>
@@ -12789,16 +12789,16 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
     </row>
@@ -12809,16 +12809,16 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
     </row>
@@ -12829,16 +12829,16 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
     </row>
@@ -12849,16 +12849,16 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>दिल्ली</t>
         </is>
       </c>
     </row>
@@ -12869,16 +12869,16 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
     </row>
@@ -12889,16 +12889,16 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>लद्दाख</t>
         </is>
       </c>
     </row>
@@ -12909,56 +12909,56 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Outside India</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>भारत से बाहर</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>Outside India</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>भारत से बाहर</t>
         </is>
       </c>
     </row>
@@ -12969,56 +12969,56 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
     </row>
@@ -13029,16 +13029,16 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
     </row>
@@ -13049,56 +13049,56 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>trtype</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>ITI or other trade course</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ITI या कोई और कारीगरी का कोर्स</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>trtype</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Hotel, catering or tourism</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>होटल, खानपान या पर्यटन</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
     </row>
@@ -13109,16 +13109,16 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Driving</t>
+          <t>ITI or other trade course</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>गाड़ी चलाना</t>
+          <t>ITI या कोई और कारीगरी का कोर्स</t>
         </is>
       </c>
     </row>
@@ -13129,16 +13129,16 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Mobile, computer or electrical repair</t>
+          <t>Hotel, catering or tourism</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>मोबाइल, कंप्यूटर या बिजली की मरम्मत</t>
+          <t>होटल, खानपान या पर्यटन</t>
         </is>
       </c>
     </row>
@@ -13149,16 +13149,16 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Tailoring or handicraft</t>
+          <t>Driving</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>सिलाई या दस्तकारी</t>
+          <t>गाड़ी चलाना</t>
         </is>
       </c>
     </row>
@@ -13169,16 +13169,16 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Animal handling or veterinary</t>
+          <t>Mobile, computer or electrical repair</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>जानवरों की देखभाल या पशु-चिकित्सा</t>
+          <t>मोबाइल, कंप्यूटर या बिजली की मरम्मत</t>
         </is>
       </c>
     </row>
@@ -13189,16 +13189,16 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Construction trade (mason, carpenter, plumber)</t>
+          <t>Tailoring or handicraft</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>निर्माण का काम (राजमिस्त्री, बढ़ई, प्लंबर)</t>
+          <t>सिलाई या दस्तकारी</t>
         </is>
       </c>
     </row>
@@ -13209,16 +13209,16 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Health or first aid</t>
+          <t>Animal handling or veterinary</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>सेहत या प्राथमिक उपचार</t>
+          <t>जानवरों की देखभाल या पशु-चिकित्सा</t>
         </is>
       </c>
     </row>
@@ -13229,56 +13229,56 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Construction trade (mason, carpenter, plumber)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>निर्माण का काम (राजमिस्त्री, बढ़ई, प्लंबर)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>trtype</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Health or first aid</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>सेहत या प्राथमिक उपचार</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>trtype</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>कोई और</t>
         </is>
       </c>
     </row>
@@ -13289,56 +13289,56 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
     </row>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
     </row>
@@ -13369,16 +13369,16 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
     </row>
@@ -13389,16 +13389,16 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
     </row>
@@ -13409,16 +13409,16 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
     </row>
@@ -13429,16 +13429,16 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
     </row>
@@ -13449,16 +13449,16 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
     </row>
@@ -13469,56 +13469,56 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
     </row>
@@ -13529,16 +13529,16 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Yes, through work</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>हाँ, काम की तरफ़ से</t>
         </is>
       </c>
     </row>
@@ -13549,63 +13549,63 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Only private or other insurance</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>कोई नहीं</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>पता नहीं</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -13625,7 +13625,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -13649,14 +13649,54 @@
         </is>
       </c>
       <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
         <v>97</v>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>पता नहीं</t>
         </is>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -1153,9 +1153,21 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
     </row>
@@ -1223,9 +1235,21 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Cannot be more than the household size minus the respondent.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
     </row>
@@ -1256,9 +1280,21 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of children under 15.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
     </row>
@@ -1293,9 +1329,21 @@
           <t>${n_children_6_14} &gt; 0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of children aged 6 to 14.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
     </row>
@@ -1689,22 +1737,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1712,48 +1760,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>${calc_offseason_work} &gt; 0</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Hours a day must be between 1 and 18.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1763,46 +1795,34 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>${calc_offseason_work} &gt; 0</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Days a week must be between 1 and 7.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1820,22 +1840,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one prevreason</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1857,22 +1877,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>training_received</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1890,22 +1910,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one prevreason</t>
+          <t>select_one trtype</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>training_type</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>What kind of course or training was it?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1915,7 +1935,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>${prev_occ_change} = 1</t>
+          <t>${training_received} = 1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1927,30 +1947,30 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>training_type_other</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was it? Write what they say.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>${training_type} = 9</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1960,34 +1980,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one trtype</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>training_type</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>What kind of course or training was it?</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>${training_received} = 1</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -1997,30 +1997,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>training_type_other</t>
+          <t>grp_C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>What was it? Write what they say.</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>${training_type} = 9</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2030,13 +2026,29 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>select_one activity</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>status_m1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>In January, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -2047,25 +2059,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>grp_C</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
+          <t>In February, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -2081,17 +2097,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In March, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2114,17 +2130,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In April, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2147,17 +2163,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In May, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2180,17 +2196,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In June, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2213,17 +2229,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In July, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2246,17 +2262,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In August, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2279,17 +2295,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In September, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2312,17 +2328,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In October, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2345,17 +2361,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In November, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2378,17 +2394,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>In December, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2406,154 +2422,158 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>calc_months_no_work</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>months with no paid work (hidden)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>calc_offseason_work</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity? (Fill the Yatra months first, then the others.)</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>months of other paid work (hidden)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one recall</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>calc_months_no_work</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>calc_offseason_work</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>select_one recall</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2561,7 +2581,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2576,17 +2600,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2596,7 +2620,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2613,17 +2637,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2633,7 +2657,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2650,17 +2674,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2670,7 +2694,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2687,17 +2711,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2707,7 +2731,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2724,17 +2748,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2744,7 +2768,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2761,17 +2785,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2781,7 +2805,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2798,17 +2822,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2818,7 +2842,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2835,17 +2859,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2855,7 +2879,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2872,17 +2896,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2892,7 +2916,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2909,17 +2933,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2929,7 +2953,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2946,17 +2970,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2966,7 +2990,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
+          <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2983,17 +3007,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3003,12 +3027,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+          <t>${knows_monthly_income} = 0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 100 out of every 100 rupees.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
     </row>
@@ -3020,17 +3056,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3038,11 +3074,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>${knows_monthly_income} = 0</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3057,17 +3089,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3075,48 +3107,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>${knows_monthly_income} = 0</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 100</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 100 out of every 100 rupees.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one remitmode</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3124,7 +3140,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3139,17 +3159,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3167,22 +3187,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>select_one remitmode</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3190,11 +3210,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -3209,17 +3225,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3227,10 +3243,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>${calc_offseason_work} &gt; 0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 18</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Hours a day must be between 1 and 18.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
     </row>
@@ -3242,17 +3274,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>days_week_offseason</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In those months, how many days a week do you usually work?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3260,10 +3292,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>${calc_offseason_work} &gt; 0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
     </row>
@@ -5856,22 +5904,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one collat</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -5881,7 +5929,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>${loan_against_asset} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -5893,22 +5941,22 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one collat</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -5918,7 +5966,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>${took_loan_12m} = 1</t>
+          <t>${loan_against_asset} = 1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr"/>
@@ -5956,17 +6004,17 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 30</t>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Cannot be more than the household has members.</t>
+          <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>घर के सदस्यों से ज़्यादा नहीं हो सकता।</t>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="J162" t="inlineStr"/>
@@ -6001,17 +6049,17 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 30</t>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Cannot be more than the household has members.</t>
+          <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>घर के सदस्यों से ज़्यादा नहीं हो सकता।</t>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
@@ -6215,17 +6263,17 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 30</t>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Cannot be more than the household has members.</t>
+          <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>घर के सदस्यों से ज़्यादा नहीं हो सकता।</t>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="J169" t="inlineStr"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K266"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,35 +441,45 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>hint::English (en)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>hint::हिन्दी (hi)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>required</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>relevant</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>constraint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>constraint_message::English (en)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>constraint_message::हिन्दी (hi)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>calculation</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>trigger</t>
         </is>
@@ -503,6 +513,8 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +544,8 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -554,17 +568,19 @@
           <t>सर्वेक्षक कौन है?</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -587,17 +603,19 @@
           <t>क्या आप इस बातचीत में शामिल होना चाहते हैं?</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -626,7 +644,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>${consent}</t>
         </is>
@@ -654,16 +674,18 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>${consent} = 1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -693,6 +715,8 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -722,6 +746,8 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -744,29 +770,31 @@
           <t>आपकी उम्र कितनी है? (पूरे साल)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>. &gt;= 10 and . &lt;= 90</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Age must be between 10 and 90.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>उम्र 10 से 90 के बीच होनी चाहिए।</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -789,17 +817,19 @@
           <t>आप पुरुष हैं या महिला?</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -822,17 +852,19 @@
           <t>आपके घर का मुखिया कौन है — आप खुद, या कोई और? अगर कोई और है, तो वे आपके क्या लगते हैं?</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -855,17 +887,19 @@
           <t>आपकी मातृभाषा कौन सी है — वह भाषा जो आपने घर में सबसे पहले सीखी?</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -888,21 +922,23 @@
           <t>वह कौन सी भाषा है? जैसा वे कहें वैसा ही लिख लीजिए।</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>${native_language} = 96 or ${native_language} = 97</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -925,17 +961,19 @@
           <t>क्या आपकी शादी हुई है, नहीं हुई है, या आप विधवा/विधुर या अलग हैं?</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -958,17 +996,19 @@
           <t>क्या आपको ठीक-ठीक याद है कि आपने कितने साल पढ़ाई की, कक्षा 1 से गिनकर?</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -991,21 +1031,23 @@
           <t>आपने कुल कितने साल पढ़ाई की? (अगर बिल्कुल नहीं पढ़े तो 0)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>${knows_years_schooling} = 1</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1028,21 +1070,23 @@
           <t>इनमें से कौन सा सबसे नज़दीक है: बिल्कुल नहीं पढ़े; थोड़ा पढ़े पर प्राइमरी पूरी नहीं की; प्राइमरी पूरी की पर दसवीं नहीं; या दसवीं या उससे ज़्यादा?</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>${knows_years_schooling} = 0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1065,29 +1109,31 @@
           <t>आपके घर में आपको मिलाकर कुल कितने लोग रहते हैं?</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 30</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Household size must be between 1 and 30.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>घर के लोग 1 से 30 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1110,17 +1156,19 @@
           <t>आपके घर में 10 साल या उससे बड़े सभी लोगों में से, क्या कम से कम एक ने छह साल या उससे ज़्यादा पढ़ाई पूरी की है?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1143,17 +1191,19 @@
           <t>आपका परिवार छोटा है — सिर्फ़ आप, पति/पत्नी और बिन ब्याहे बच्चे — या बड़ा, यानी माँ-बाप, भाई-भाभी या और रिश्तेदार साथ रहते हैं? (अगर अकेले रहते हैं तो वह बताइए।)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1176,29 +1226,31 @@
           <t>इनमें से कितने लोग, आपको मिलाकर, पैसा कमाते हैं?</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1221,21 +1273,23 @@
           <t>जो लोग कमाते हैं, उनमें सबसे ज़्यादा कमाने वाले आप ही हैं?</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>${n_earners} &gt; 1</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1258,29 +1312,31 @@
           <t>इनमें 15 साल से छोटे बच्चे कितने हैं?</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Cannot be more than the household size minus the respondent.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1303,29 +1359,31 @@
           <t>इनमें 6 से 14 साल के बच्चे कितने हैं?</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Cannot be more than the number of children under 15.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1348,33 +1406,35 @@
           <t>इन बच्चों में कितने अभी स्कूल नहीं जाते?</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>${n_children_6_14} &gt; 0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Cannot be more than the number of children aged 6 to 14.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1392,6 +1452,8 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1421,6 +1483,8 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1450,6 +1514,8 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1472,17 +1538,19 @@
           <t>यात्रा के मौसम में आपका मुख्य काम क्या है?</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1505,17 +1573,19 @@
           <t>अपने शब्दों में बताइए, यहाँ आपका मुख्य काम ठीक-ठीक क्या है? आप करते क्या हैं, और किसके लिए?</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1538,17 +1608,19 @@
           <t>इस काम में आप क्या हैं: अपना काम खुद करते हैं और कोई नौकर नहीं रखते; अपना काम है और दूसरों को काम पर रखते हैं; महीने की पक्की तनख़्वाह पाते हैं; या दिहाड़ी पर काम करते हैं?</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1571,29 +1643,31 @@
           <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 6</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Must be between 0 and 6.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>0 से 6 के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1616,21 +1690,23 @@
           <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>${n_other_activities} &gt; 0</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1653,21 +1729,23 @@
           <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>${n_other_activities} &gt; 0</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1690,17 +1768,19 @@
           <t>आप कितने यात्रा सीज़न से यह काम कर रहे हैं?</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1723,29 +1803,31 @@
           <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1768,29 +1850,31 @@
           <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>. &gt;= 1 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Days a week must be between 1 and 7.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1813,17 +1897,19 @@
           <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1846,21 +1932,23 @@
           <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>${prev_occ_change} = 1</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1883,17 +1971,19 @@
           <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1916,21 +2006,23 @@
           <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>${prev_occ_change} = 1</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1953,17 +2045,19 @@
           <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1986,21 +2080,23 @@
           <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>${training_received} = 1</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2024,16 +2120,18 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>${training_type} = 9</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2051,6 +2149,8 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2080,6 +2180,8 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2109,6 +2211,8 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2131,17 +2235,19 @@
           <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2164,17 +2270,19 @@
           <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2197,17 +2305,19 @@
           <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2230,17 +2340,19 @@
           <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2263,17 +2375,19 @@
           <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2296,17 +2410,19 @@
           <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2329,17 +2445,19 @@
           <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2362,17 +2480,19 @@
           <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2395,17 +2515,19 @@
           <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2428,17 +2550,19 @@
           <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2461,17 +2585,19 @@
           <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2494,17 +2620,19 @@
           <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2532,12 +2660,14 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2565,12 +2695,14 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
         <is>
           <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2593,17 +2725,19 @@
           <t>और जनवरी में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2626,17 +2760,19 @@
           <t>और फ़रवरी में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2659,17 +2795,19 @@
           <t>और मार्च में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2692,17 +2830,19 @@
           <t>और अप्रैल में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2725,17 +2865,19 @@
           <t>और मई में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2758,17 +2900,19 @@
           <t>और जून में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2791,17 +2935,19 @@
           <t>और जुलाई में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2824,17 +2970,19 @@
           <t>और अगस्त में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2857,17 +3005,19 @@
           <t>और सितंबर में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2890,17 +3040,19 @@
           <t>और अक्टूबर में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2923,17 +3075,19 @@
           <t>और नवंबर में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2956,17 +3110,19 @@
           <t>और दिसंबर में आप कहाँ रह रहे थे?</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2989,17 +3145,19 @@
           <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3022,21 +3180,23 @@
           <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3059,21 +3219,23 @@
           <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3096,21 +3258,23 @@
           <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3133,21 +3297,23 @@
           <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3170,21 +3336,23 @@
           <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3207,21 +3375,23 @@
           <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3244,21 +3414,23 @@
           <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3281,21 +3453,23 @@
           <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3318,21 +3492,23 @@
           <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3355,21 +3531,23 @@
           <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3392,21 +3570,23 @@
           <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3429,21 +3609,23 @@
           <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3466,21 +3648,23 @@
           <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3503,33 +3687,35 @@
           <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= 100</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Must be between 0 and 100 out of every 100 rupees.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3552,17 +3738,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3585,17 +3773,19 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3618,21 +3808,23 @@
           <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
         <is>
           <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3655,17 +3847,19 @@
           <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3688,17 +3882,19 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3721,33 +3917,35 @@
           <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>${calc_offseason_work} &gt; 0</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3770,33 +3968,35 @@
           <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
         <is>
           <t>${calc_offseason_work} &gt; 0</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>. &gt;= 1 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Days a week must be between 1 and 7.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3814,6 +4014,8 @@
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3843,6 +4045,8 @@
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3872,6 +4076,8 @@
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3894,17 +4100,19 @@
           <t>आपका पक्का घर कहाँ है?</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3927,17 +4135,19 @@
           <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3960,17 +4170,19 @@
           <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3993,17 +4205,19 @@
           <t>जब यात्रा का मौसम ख़त्म हो जाता है, तब क्या होता है — आप और आपके घरवाले यहीं रहते हैं, या अपने घर चले जाते हैं?</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4026,21 +4240,23 @@
           <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
         <is>
           <t>${closure_base} != 1</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4063,21 +4279,23 @@
           <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>${origin} != 1</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4100,17 +4318,19 @@
           <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4134,16 +4354,18 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
         <is>
           <t>${worked_away_in_closure} = 1</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4166,17 +4388,19 @@
           <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4200,16 +4424,18 @@
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
         <is>
           <t>${worked_other_places} = 1</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4232,17 +4458,19 @@
           <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4265,17 +4493,19 @@
           <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4299,16 +4529,18 @@
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
         <is>
           <t>${migration_referral} = 7</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4326,6 +4558,8 @@
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4355,6 +4589,8 @@
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4384,6 +4620,8 @@
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4406,17 +4644,19 @@
           <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4439,17 +4679,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4472,21 +4714,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4509,17 +4753,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4542,21 +4788,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4579,17 +4827,19 @@
           <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4612,21 +4862,23 @@
           <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4649,17 +4901,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4682,21 +4936,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4719,17 +4975,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4752,21 +5010,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4789,17 +5049,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4822,21 +5084,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4859,17 +5123,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4892,21 +5158,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4929,17 +5197,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4962,21 +5232,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4999,17 +5271,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5032,21 +5306,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5069,17 +5345,19 @@
           <t>यहाँ सीज़न में रहते हुए, आप अपना खाना ख़ुद बनाते हैं, ख़रीदकर खाते हैं, या दोनों?</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5102,21 +5380,23 @@
           <t>यहाँ आम काम के दिन में, अपने खाने और चाय पर कुल कितना ख़र्च होता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
         <is>
           <t>${cooks_own_meals_here} = 2 or ${cooks_own_meals_here} = 3</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5139,17 +5419,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5172,21 +5454,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5209,17 +5493,19 @@
           <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5242,21 +5528,23 @@
           <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
         <is>
           <t>${spend_differs_by_season} = 1</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5279,17 +5567,19 @@
           <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5312,17 +5602,19 @@
           <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5345,17 +5637,19 @@
           <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5378,17 +5672,19 @@
           <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5406,6 +5702,8 @@
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5435,6 +5733,8 @@
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5464,6 +5764,8 @@
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5486,17 +5788,19 @@
           <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5519,17 +5823,19 @@
           <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5552,17 +5858,19 @@
           <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5585,17 +5893,19 @@
           <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5618,17 +5928,19 @@
           <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5651,17 +5963,19 @@
           <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5684,17 +5998,19 @@
           <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5717,17 +6033,19 @@
           <t>क्या वह पानी घर पर ही मिल जाता है, या किसी को लाने जाना पड़ता है?</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5750,33 +6068,35 @@
           <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
         <is>
           <t>${water_on_premises} = 0</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>. &gt;= 0 and . &lt;= 300</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="J156" t="inlineStr">
         <is>
           <t>Minutes must be between 0 and 300.</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5799,21 +6119,23 @@
           <t>घर में आम तौर पर पानी कौन लाता है?</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
         <is>
           <t>${water_on_premises} = 0</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5836,17 +6158,19 @@
           <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5869,17 +6193,19 @@
           <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5902,17 +6228,19 @@
           <t>...रेडियो?</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5935,17 +6263,19 @@
           <t>...साइकिल?</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5968,17 +6298,19 @@
           <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6001,17 +6333,19 @@
           <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6034,17 +6368,19 @@
           <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6067,17 +6403,19 @@
           <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6100,17 +6438,19 @@
           <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6133,17 +6473,19 @@
           <t>...फ़्रिज?</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6166,17 +6508,19 @@
           <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6199,17 +6543,19 @@
           <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6232,17 +6578,19 @@
           <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6265,17 +6613,19 @@
           <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6298,17 +6648,19 @@
           <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6331,17 +6683,19 @@
           <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6364,17 +6718,19 @@
           <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6398,16 +6754,18 @@
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
         <is>
           <t>${owns_work_equipment} = 1</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6425,6 +6783,8 @@
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6454,6 +6814,8 @@
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6483,6 +6845,8 @@
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6505,17 +6869,19 @@
           <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6538,21 +6904,23 @@
           <t>क्या उनमें से कोई जन धन खाता है?</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
         <is>
           <t>${has_bank_account} = 1</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6575,17 +6943,19 @@
           <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6608,21 +6978,23 @@
           <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
         <is>
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6645,21 +7017,23 @@
           <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
         <is>
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6682,21 +7056,23 @@
           <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
         <is>
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6720,16 +7096,18 @@
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr">
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
         <is>
           <t>${pays_interest} = 1</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6752,21 +7130,23 @@
           <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6789,21 +7169,23 @@
           <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
         <is>
           <t>${loan_against_asset} = 1</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6826,29 +7208,31 @@
           <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
+      <c r="J188" t="inlineStr">
         <is>
           <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6871,29 +7255,31 @@
           <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
+      <c r="J189" t="inlineStr">
         <is>
           <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="K189" t="inlineStr">
         <is>
           <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6916,21 +7302,23 @@
           <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
         <is>
           <t>${land_cultivable_acres} &gt; 0</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6953,17 +7341,19 @@
           <t>पिछले 12 महीनों में क्या आपके घर को किसी सरकारी योजना से कुछ मिला (जैसे राशन, पेंशन, पैसा)?</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6987,16 +7377,18 @@
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
         <is>
           <t>${govt_scheme_beneficiary} = 1</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7019,17 +7411,19 @@
           <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7052,17 +7446,19 @@
           <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7085,29 +7481,31 @@
           <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="J195" t="inlineStr">
         <is>
           <t>Cannot be more than the number of people in the household.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="K195" t="inlineStr">
         <is>
           <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7125,6 +7523,8 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7154,6 +7554,8 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7183,6 +7585,8 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7205,17 +7609,19 @@
           <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7238,21 +7644,23 @@
           <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
         <is>
           <t>${morbidity_15d} = 1</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7275,21 +7683,23 @@
           <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
         <is>
           <t>${morbidity_15d} = 1</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7312,17 +7722,19 @@
           <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7345,17 +7757,19 @@
           <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7378,17 +7792,19 @@
           <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7411,17 +7827,19 @@
           <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7444,21 +7862,23 @@
           <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
         <is>
           <t>${birth_last_5y} = 1</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7481,21 +7901,23 @@
           <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
         <is>
           <t>${birth_last_5y} = 1</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7513,6 +7935,8 @@
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7542,6 +7966,8 @@
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7571,6 +7997,8 @@
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7593,17 +8021,19 @@
           <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7626,21 +8056,23 @@
           <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
         <is>
           <t>count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7663,29 +8095,31 @@
           <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
+      <c r="J213" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="K213" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr"/>
-      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7708,29 +8142,31 @@
           <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
+      <c r="J214" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7753,29 +8189,31 @@
           <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="J215" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="K215" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7798,29 +8236,31 @@
           <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="J216" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="K216" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7843,29 +8283,31 @@
           <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="J217" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="K217" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7888,29 +8330,31 @@
           <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="J218" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="K218" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7933,29 +8377,31 @@
           <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="J219" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="K219" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7978,29 +8424,31 @@
           <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="J220" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="K220" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8023,29 +8471,31 @@
           <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="J221" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="K221" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8068,29 +8518,31 @@
           <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
           <t>. &gt;= 0 and . &lt;= 7</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="J222" t="inlineStr">
         <is>
           <t>Must be between 0 and 7 days.</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="K222" t="inlineStr">
         <is>
           <t>0 से 7 दिन के बीच होना चाहिए।</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8108,6 +8560,8 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8137,6 +8591,8 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8166,6 +8622,8 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8188,17 +8646,19 @@
           <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8221,17 +8681,19 @@
           <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8249,6 +8711,8 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8278,6 +8742,8 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8307,6 +8773,8 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8329,17 +8797,19 @@
           <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8362,21 +8832,23 @@
           <t>अपने अभी के काम में आप क्या हैं: किसी प्राइवेट कंपनी के कर्मचारी; सरकारी विभाग के कर्मचारी; फ़ौज या पुलिस में; मालिक जो दूसरों को काम पर रखते हैं; अकेले काम करते हैं, कोई नौकर नहीं; घर के काम में बिना पैसे के हाथ बँटाते हैं; या किसी के घर में काम करते हैं?</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8401,19 +8873,29 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8436,21 +8918,23 @@
           <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
         <is>
           <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8473,21 +8957,23 @@
           <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8510,21 +8996,23 @@
           <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8547,21 +9035,23 @@
           <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8584,21 +9074,23 @@
           <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8621,21 +9113,23 @@
           <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8658,21 +9152,23 @@
           <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8695,21 +9191,23 @@
           <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
         <is>
           <t>${job_situation} &lt;= 7</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8732,21 +9230,23 @@
           <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8769,21 +9269,23 @@
           <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
         <is>
           <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8806,17 +9308,19 @@
           <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8834,6 +9338,8 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8863,6 +9369,8 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8892,6 +9400,8 @@
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8914,17 +9424,19 @@
           <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E248" t="inlineStr"/>
       <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8947,17 +9459,19 @@
           <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8980,17 +9494,19 @@
           <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9013,17 +9529,19 @@
           <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9046,17 +9564,19 @@
           <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9079,17 +9599,19 @@
           <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9112,17 +9634,19 @@
           <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9145,17 +9669,19 @@
           <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9178,17 +9704,19 @@
           <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9211,17 +9739,19 @@
           <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9244,17 +9774,19 @@
           <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9277,17 +9809,19 @@
           <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9310,21 +9844,23 @@
           <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
         <is>
           <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9347,21 +9883,23 @@
           <t>...कार या जीप?</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
         <is>
           <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9384,21 +9922,23 @@
           <t>...ट्रक या बस?</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
         <is>
           <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9421,17 +9961,19 @@
           <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9454,17 +9996,19 @@
           <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9482,6 +10026,8 @@
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9499,6 +10045,8 @@
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N256"/>
+  <dimension ref="A1:O256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>appearance</t>
         </is>
       </c>
     </row>
@@ -521,6 +526,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -553,6 +559,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -589,6 +596,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +633,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -661,6 +670,7 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -697,6 +707,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -729,6 +740,11 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -761,6 +777,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -809,6 +826,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -845,6 +863,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,6 +900,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -917,6 +937,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -957,6 +978,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -993,6 +1015,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1029,6 +1052,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1069,6 +1093,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1109,6 +1134,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1157,6 +1183,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1193,6 +1220,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1229,6 +1257,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1277,6 +1306,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1317,6 +1347,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1365,6 +1396,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1413,6 +1445,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1465,6 +1498,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1485,6 +1519,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1517,6 +1552,11 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1549,6 +1589,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1585,6 +1626,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1621,6 +1663,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1657,6 +1700,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1705,6 +1749,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1749,6 +1794,7 @@
           <t>code != ${occupation}</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1789,6 +1835,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1825,6 +1872,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1873,6 +1921,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1921,6 +1970,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1957,6 +2007,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1997,6 +2048,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2033,6 +2085,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2073,6 +2126,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2109,6 +2163,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2149,6 +2204,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2185,6 +2241,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2205,6 +2262,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2237,6 +2295,11 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2269,6 +2332,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2305,6 +2369,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2341,6 +2406,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2377,6 +2443,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2413,6 +2480,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2449,6 +2517,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2485,6 +2554,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2521,6 +2591,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2557,6 +2628,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2593,6 +2665,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2629,6 +2702,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2665,6 +2739,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2701,6 +2776,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2737,6 +2813,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2773,6 +2850,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2809,6 +2887,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2849,6 +2928,7 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2889,6 +2969,7 @@
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2929,6 +3010,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2969,6 +3051,7 @@
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3009,6 +3092,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3049,6 +3133,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3089,6 +3174,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3129,6 +3215,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3169,6 +3256,7 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3209,6 +3297,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3249,6 +3338,7 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3289,6 +3379,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3329,6 +3420,7 @@
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3381,6 +3473,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3417,6 +3510,7 @@
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3453,6 +3547,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3493,6 +3588,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3529,6 +3625,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3565,6 +3662,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3617,6 +3715,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3669,6 +3768,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3689,6 +3789,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3721,6 +3822,11 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3753,6 +3859,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3789,6 +3896,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3825,6 +3933,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3861,6 +3970,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3897,6 +4007,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3933,6 +4044,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3973,6 +4085,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4013,6 +4126,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4053,6 +4167,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4089,6 +4204,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4125,6 +4241,7 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4165,6 +4282,7 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4205,6 +4323,7 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4245,6 +4364,7 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4281,6 +4401,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4317,6 +4438,7 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4353,6 +4475,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4389,6 +4512,7 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4425,6 +4549,7 @@
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4445,6 +4570,7 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4477,6 +4603,11 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4509,6 +4640,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4545,6 +4677,7 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4581,6 +4714,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4621,6 +4755,7 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4657,6 +4792,7 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4697,6 +4833,7 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4733,6 +4870,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4773,6 +4911,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4809,6 +4948,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4849,6 +4989,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4885,6 +5026,7 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4925,6 +5067,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4961,6 +5104,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5001,6 +5145,7 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5037,6 +5182,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5077,6 +5223,7 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5113,6 +5260,7 @@
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5153,6 +5301,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5189,6 +5338,7 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5229,6 +5379,7 @@
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5265,6 +5416,7 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5305,6 +5457,7 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5341,6 +5494,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5381,6 +5535,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5417,6 +5572,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5453,6 +5609,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5489,6 +5646,7 @@
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5525,6 +5683,7 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5545,6 +5704,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5577,6 +5737,11 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5609,6 +5774,7 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5645,6 +5811,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5681,6 +5848,7 @@
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5717,6 +5885,7 @@
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5753,6 +5922,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5789,6 +5959,7 @@
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5825,6 +5996,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5861,6 +6033,7 @@
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5897,6 +6070,7 @@
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5949,6 +6123,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5989,6 +6164,7 @@
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6025,6 +6201,7 @@
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6061,6 +6238,7 @@
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6097,6 +6275,7 @@
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6133,6 +6312,7 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6169,6 +6349,7 @@
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6205,6 +6386,7 @@
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6241,6 +6423,7 @@
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6277,6 +6460,7 @@
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6313,6 +6497,7 @@
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6349,6 +6534,7 @@
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6385,6 +6571,7 @@
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6421,6 +6608,7 @@
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6457,6 +6645,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6493,6 +6682,7 @@
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6529,6 +6719,7 @@
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6565,6 +6756,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6601,6 +6793,7 @@
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6637,6 +6830,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6657,6 +6851,7 @@
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6689,6 +6884,11 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6721,6 +6921,7 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6757,6 +6958,7 @@
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6797,6 +6999,7 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6833,6 +7036,7 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6873,6 +7077,7 @@
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6913,6 +7118,7 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6953,6 +7159,7 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6989,6 +7196,7 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7029,6 +7237,7 @@
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7069,6 +7278,7 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7117,6 +7327,7 @@
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7165,6 +7376,7 @@
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7205,6 +7417,7 @@
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7241,6 +7454,7 @@
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7277,6 +7491,7 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7313,6 +7528,7 @@
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7349,6 +7565,7 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7397,6 +7614,7 @@
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7417,6 +7635,7 @@
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7449,6 +7668,11 @@
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7481,6 +7705,7 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7517,6 +7742,7 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7557,6 +7783,7 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7597,6 +7824,7 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7633,6 +7861,7 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7669,6 +7898,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7705,6 +7935,7 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7741,6 +7972,7 @@
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7781,6 +8013,7 @@
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7821,6 +8054,7 @@
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7841,6 +8075,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7873,6 +8108,11 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7905,6 +8145,7 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7941,6 +8182,7 @@
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7981,6 +8223,7 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8029,6 +8272,7 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8077,6 +8321,7 @@
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8125,6 +8370,7 @@
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8173,6 +8419,7 @@
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8221,6 +8468,7 @@
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8269,6 +8517,7 @@
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8317,6 +8566,7 @@
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8365,6 +8615,7 @@
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8413,6 +8664,7 @@
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8461,6 +8713,7 @@
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8481,6 +8734,7 @@
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8513,6 +8767,11 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8545,6 +8804,7 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8581,6 +8841,7 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8617,6 +8878,7 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8637,6 +8899,7 @@
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8669,6 +8932,11 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8701,6 +8969,7 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8737,6 +9006,7 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8785,6 +9055,7 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8825,6 +9096,7 @@
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8865,6 +9137,7 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8905,6 +9178,7 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8945,6 +9219,7 @@
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8985,6 +9260,7 @@
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9025,6 +9301,7 @@
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9065,6 +9342,7 @@
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9105,6 +9383,7 @@
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9145,6 +9424,7 @@
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9185,6 +9465,7 @@
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9221,6 +9502,7 @@
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9241,6 +9523,7 @@
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9273,6 +9556,11 @@
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9305,6 +9593,7 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9341,6 +9630,7 @@
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9377,6 +9667,7 @@
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9413,6 +9704,7 @@
       <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9449,6 +9741,7 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9485,6 +9778,7 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9521,6 +9815,7 @@
       <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9557,6 +9852,7 @@
       <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9593,6 +9889,7 @@
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9629,6 +9926,7 @@
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9665,6 +9963,7 @@
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9701,6 +10000,7 @@
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9737,6 +10037,7 @@
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9777,6 +10078,7 @@
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9817,6 +10119,7 @@
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9857,6 +10160,7 @@
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9893,6 +10197,7 @@
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9929,6 +10234,7 @@
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9949,6 +10255,7 @@
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9969,6 +10276,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10022,12 +10330,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yatra work (main occupation)</t>
+          <t>Yatra work, or getting ready for the season</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>यात्रा का काम (मुख्य)</t>
+          <t>यात्रा का काम, या उसकी तैयारी</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O256"/>
+  <dimension ref="A1:O257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,31 +601,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>consent</t>
+          <t>consent_script</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Read the consent script. Do you agree to take part? (1 yes, 0 no; stop if no)</t>
+          <t>We are doing a study on the livelihoods of people who work on the Yatra route. I would like to ask you some questions about your work, your household and your spending.
+Taking part is your choice. You can stop at any time, and you can skip any question you do not want to answer. Nothing you tell me will be linked to your name, and nothing you say will affect your work here or any government benefit.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>क्या आप इस बातचीत में शामिल होना चाहते हैं?</t>
+          <t>हम यात्रा मार्ग पर काम करने वाले लोगों के रोज़गार पर एक अध्ययन कर रहे हैं। मैं आपसे आपके काम, आपके घर और आपके ख़र्च के बारे में कुछ सवाल पूछना चाहूँगा/चाहूँगी।
+इसमें शामिल होना आपकी मर्ज़ी है। आप कभी भी रोक सकते हैं, और जिस सवाल का जवाब नहीं देना चाहते उसे छोड़ सकते हैं। आप जो बताएँगे वह आपके नाम से नहीं जोड़ा जाएगा, और उससे यहाँ आपके काम या किसी सरकारी सुविधा पर कोई असर नहीं पड़ेगा।</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -638,74 +636,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>background-geopoint</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gps_location</t>
+          <t>consent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GPS location of the interview (captured silently).</t>
+          <t>Do you agree to take part?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GPS location of the interview (captured silently).</t>
+          <t>क्या आप इसमें शामिल होना चाहते हैं?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>${consent}</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>background-geopoint</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>main_survey</t>
+          <t>gps_location</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Main survey</t>
+          <t>GPS location of the interview (captured silently).</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Main survey</t>
+          <t>GPS location of the interview (captured silently).</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>${consent} = 1</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>${consent}</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
     </row>
@@ -717,54 +715,54 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>grp_A</t>
+          <t>main_survey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Module A: Respondent and household</t>
+          <t>Main survey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Module A: Respondent and household</t>
+          <t>Main survey</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>${consent} = 1</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>intro_A</t>
+          <t>grp_A</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>First, a few things about you and the people who live in your household.</t>
+          <t>Module A: Respondent and household</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>सबसे पहले आपके बारे में और आपके घर में रहने वाले लोगों के बारे में कुछ बातें पूछूँगा।</t>
+          <t>Module A: Respondent and household</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -777,52 +775,40 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>intro_A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How old are you? (completed years)</t>
+          <t>First, a few things about you and the people who live in your household.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>आपकी उम्र कितनी है? (पूरे साल)</t>
+          <t>सबसे पहले आपके बारे में और आपके घर में रहने वाले लोगों के बारे में कुछ बातें पूछूँगा।</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>. &gt;= 10 and . &lt;= 90</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Age must be between 10 and 90.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>उम्र 10 से 90 के बीच होनी चाहिए।</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -831,22 +817,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Record sex; ask if unsure: are you male or female?</t>
+          <t>How old are you? (completed years)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>आप पुरुष हैं या महिला?</t>
+          <t>आपकी उम्र कितनी है? (पूरे साल)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -857,9 +843,21 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>. &gt;= 10 and . &lt;= 90</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Age must be between 10 and 90.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>उम्र 10 से 90 के बीच होनी चाहिए।</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -868,22 +866,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one hohrel</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hoh_relation</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Who is the head of your household -- is it you, or someone else? If someone else, how are they related to you?</t>
+          <t>Record sex; ask if unsure: are you male or female?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>आपके घर का मुखिया कौन है — आप खुद, या कोई और? अगर कोई और है, तो वे आपके क्या लगते हैं?</t>
+          <t>आप पुरुष हैं या महिला?</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -905,22 +903,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one nativelang</t>
+          <t>select_one hohrel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>native_language</t>
+          <t>hoh_relation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your native language, the language you first learned at home?</t>
+          <t>Who is the head of your household -- is it you, or someone else? If someone else, how are they related to you?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>आपकी मातृभाषा कौन सी है — वह भाषा जो आपने घर में सबसे पहले सीखी?</t>
+          <t>आपके घर का मुखिया कौन है — आप खुद, या कोई और? अगर कोई और है, तो वे आपके क्या लगते हैं?</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -942,22 +940,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nativelang</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>native_language_other</t>
+          <t>native_language</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Which language is it? Write down exactly what they say.</t>
+          <t>What is your native language, the language you first learned at home?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>वह कौन सी भाषा है? जैसा वे कहें वैसा ही लिख लीजिए।</t>
+          <t>आपकी मातृभाषा कौन सी है — वह भाषा जो आपने घर में सबसे पहले सीखी?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -967,11 +965,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>${native_language} = 96 or ${native_language} = 97</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -983,22 +977,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one marital</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>native_language_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Are you currently married, never married, or widowed/divorced/separated?</t>
+          <t>Which language is it? Write down exactly what they say.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>क्या आपकी शादी हुई है, नहीं हुई है, या आप विधवा/विधुर या अलग हैं?</t>
+          <t>वह कौन सी भाषा है? जैसा वे कहें वैसा ही लिख लीजिए।</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1008,7 +1002,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>${native_language} = 96 or ${native_language} = 97</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1020,22 +1018,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one marital</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>knows_years_schooling</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Do you know exactly how many years of schooling you completed, counting from class 1?</t>
+          <t>Are you currently married, never married, or widowed/divorced/separated?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>क्या आपको ठीक-ठीक याद है कि आपने कितने साल पढ़ाई की, कक्षा 1 से गिनकर?</t>
+          <t>क्या आपकी शादी हुई है, नहीं हुई है, या आप विधवा/विधुर या अलग हैं?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1057,22 +1055,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>years_schooling</t>
+          <t>knows_years_schooling</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How many years of schooling did you complete in total? (0 if none)</t>
+          <t>Do you know exactly how many years of schooling you completed, counting from class 1?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>आपने कुल कितने साल पढ़ाई की? (अगर बिल्कुल नहीं पढ़े तो 0)</t>
+          <t>क्या आपको ठीक-ठीक याद है कि आपने कितने साल पढ़ाई की, कक्षा 1 से गिनकर?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1082,11 +1080,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>${knows_years_schooling} = 1</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1098,22 +1092,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one edu2</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>education_level_cat</t>
+          <t>years_schooling</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Which is closest: no formal education; some schooling but did not finish primary; finished primary but not secondary; or finished secondary or higher?</t>
+          <t>How many years of schooling did you complete in total? (0 if none)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>इनमें से कौन सा सबसे नज़दीक है: बिल्कुल नहीं पढ़े; थोड़ा पढ़े पर प्राइमरी पूरी नहीं की; प्राइमरी पूरी की पर दसवीं नहीं; या दसवीं या उससे ज़्यादा?</t>
+          <t>आपने कुल कितने साल पढ़ाई की? (अगर बिल्कुल नहीं पढ़े तो 0)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1125,7 +1119,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>${knows_years_schooling} = 0</t>
+          <t>${knows_years_schooling} = 1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1139,22 +1133,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one edu2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hhsize</t>
+          <t>education_level_cat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How many members live in your household, including you?</t>
+          <t>Which is closest: no formal education; some schooling but did not finish primary; finished primary but not secondary; or finished secondary or higher?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>आपके घर में आपको मिलाकर कुल कितने लोग रहते हैं?</t>
+          <t>इनमें से कौन सा सबसे नज़दीक है: बिल्कुल नहीं पढ़े; थोड़ा पढ़े पर प्राइमरी पूरी नहीं की; प्राइमरी पूरी की पर दसवीं नहीं; या दसवीं या उससे ज़्यादा?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1164,22 +1158,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Household size must be between 1 and 30.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>घर के लोग 1 से 30 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>${knows_years_schooling} = 0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1188,22 +1174,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>any_member_6yr_schooling</t>
+          <t>hhsize</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Counting everyone in your household aged 10 or above, has at least one of them finished six years of schooling or more?</t>
+          <t>How many members live in your household, including you?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>आपके घर में 10 साल या उससे बड़े सभी लोगों में से, क्या कम से कम एक ने छह साल या उससे ज़्यादा पढ़ाई पूरी की है?</t>
+          <t>आपके घर में आपको मिलाकर कुल कितने लोग रहते हैं?</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1214,9 +1200,21 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Household size must be between 1 and 30.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>घर के लोग 1 से 30 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1225,22 +1223,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one famstruct</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>family_structure</t>
+          <t>any_member_6yr_schooling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Is your family nuclear -- just you, your spouse and unmarried children -- or joint, living with parents, married siblings or other extended family? (Say single-member if you live alone.)</t>
+          <t>Counting everyone in your household aged 10 or above, has at least one of them finished six years of schooling or more?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>आपका परिवार छोटा है — सिर्फ़ आप, पति/पत्नी और बिन ब्याहे बच्चे — या बड़ा, यानी माँ-बाप, भाई-भाभी या और रिश्तेदार साथ रहते हैं? (अगर अकेले रहते हैं तो वह बताइए।)</t>
+          <t>आपके घर में 10 साल या उससे बड़े सभी लोगों में से, क्या कम से कम एक ने छह साल या उससे ज़्यादा पढ़ाई पूरी की है?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1262,22 +1260,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one famstruct</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>n_earners</t>
+          <t>family_structure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How many of them, including you, earn money?</t>
+          <t>Is your family nuclear -- just you, your spouse and unmarried children -- or joint, living with parents, married siblings or other extended family? (Say single-member if you live alone.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>इनमें से कितने लोग, आपको मिलाकर, पैसा कमाते हैं?</t>
+          <t>आपका परिवार छोटा है — सिर्फ़ आप, पति/पत्नी और बिन ब्याहे बच्चे — या बड़ा, यानी माँ-बाप, भाई-भाभी या और रिश्तेदार साथ रहते हैं? (अगर अकेले रहते हैं तो वह बताइए।)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1288,21 +1286,9 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1311,22 +1297,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>main_income_earner</t>
+          <t>n_earners</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Among those who earn money, are you the main income earner in your household?</t>
+          <t>How many of them, including you, earn money?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>जो लोग कमाते हैं, उनमें सबसे ज़्यादा कमाने वाले आप ही हैं?</t>
+          <t>इनमें से कितने लोग, आपको मिलाकर, पैसा कमाते हैं?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1336,14 +1322,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>${n_earners} &gt; 1</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1352,22 +1346,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>n_children_u15</t>
+          <t>main_income_earner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How many of them are children under 15?</t>
+          <t>Among those who earn money, are you the main income earner in your household?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>इनमें 15 साल से छोटे बच्चे कितने हैं?</t>
+          <t>जो लोग कमाते हैं, उनमें सबसे ज़्यादा कमाने वाले आप ही हैं?</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1377,22 +1371,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Cannot be more than the household size minus the respondent.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>${n_earners} &gt; 1</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -1406,17 +1392,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>n_children_6_14</t>
+          <t>n_children_u15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How many of them are children aged 6 to 14?</t>
+          <t>How many of them are children under 15?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>इनमें 6 से 14 साल के बच्चे कितने हैं?</t>
+          <t>इनमें 15 साल से छोटे बच्चे कितने हैं?</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1429,17 +1415,17 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
+          <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cannot be more than the number of children under 15.</t>
+          <t>Cannot be more than the household size minus the respondent.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
+          <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1455,17 +1441,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>n_children_out_school</t>
+          <t>n_children_6_14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How many of these children do not go to school now?</t>
+          <t>How many of them are children aged 6 to 14?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>इन बच्चों में कितने अभी स्कूल नहीं जाते?</t>
+          <t>इनमें 6 से 14 साल के बच्चे कितने हैं?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1475,24 +1461,20 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>${n_children_6_14} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
+          <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Cannot be more than the number of children aged 6 to 14.</t>
+          <t>Cannot be more than the number of children under 15.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
+          <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1503,19 +1485,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>n_children_out_school</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>How many of these children do not go to school now?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>इन बच्चों में कितने अभी स्कूल नहीं जाते?</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>${n_children_6_14} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of children aged 6 to 14.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -1524,24 +1538,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>grp_B</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Module B: Work and work history</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Module B: Work and work history</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
@@ -1552,31 +1554,27 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>intro_B</t>
+          <t>grp_B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Now about the work you do here on the Yatra route, and the work you did before this.</t>
+          <t>Module B: Work and work history</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>अब उस काम के बारे में जो आप यहाँ यात्रा मार्ग पर करते हैं, और उससे पहले जो काम करते थे।</t>
+          <t>Module B: Work and work history</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1589,36 +1587,36 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one occ</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>intro_B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>What is your main work during the Yatra season? Ask what they do and code the closest group; do not read the list aloud unless needed.</t>
+          <t>Now about the work you do here on the Yatra route, and the work you did before this.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आपका मुख्य काम क्या है?</t>
+          <t>अब उस काम के बारे में जो आप यहाँ यात्रा मार्ग पर करते हैं, और उससे पहले जो काम करते थे।</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
@@ -1631,22 +1629,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one occ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>occupation_detail</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>In your own words, what exactly is your main work here? Write down what they say -- what they actually do, and who for. Do not tick a box for this one.</t>
+          <t>What is your main work during the Yatra season? Ask what they do and code the closest group; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>अपने शब्दों में बताइए, यहाँ आपका मुख्य काम ठीक-ठीक क्या है? आप करते क्या हैं, और किसके लिए?</t>
+          <t>यात्रा के मौसम में आपका मुख्य काम क्या है?</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1668,22 +1666,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one emptype</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>employment_type</t>
+          <t>occupation_detail</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>In this main work, are you: working on your own account without hired workers; running a business with hired workers; a regular monthly wage-earner; or a daily/casual wage-earner?</t>
+          <t>In your own words, what exactly is your main work here? Write down what they say -- what they actually do, and who for. Do not tick a box for this one.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>इस काम में आप क्या हैं: अपना काम खुद करते हैं और कोई नौकर नहीं रखते; अपना काम है और दूसरों को काम पर रखते हैं; महीने की पक्की तनख़्वाह पाते हैं; या दिहाड़ी पर काम करते हैं?</t>
+          <t>अपने शब्दों में बताइए, यहाँ आपका मुख्य काम ठीक-ठीक क्या है? आप करते क्या हैं, और किसके लिए?</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1705,22 +1703,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one emptype</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>n_other_activities</t>
+          <t>employment_type</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
+          <t>In this main work, are you: working on your own account without hired workers; running a business with hired workers; a regular monthly wage-earner; or a daily/casual wage-earner?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
+          <t>इस काम में आप क्या हैं: अपना काम खुद करते हैं और कोई नौकर नहीं रखते; अपना काम है और दूसरों को काम पर रखते हैं; महीने की पक्की तनख़्वाह पाते हैं; या दिहाड़ी पर काम करते हैं?</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1731,21 +1729,9 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 6.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0 से 6 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -1754,22 +1740,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_multiple occ</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>other_activity_types</t>
+          <t>n_other_activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
+          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
+          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1779,42 +1765,46 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>${n_other_activities} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 6.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0 से 6 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>code != ${occupation}</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple occ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>other_activity_types</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
+          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
+          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1834,7 +1824,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>code != ${occupation}</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1845,17 +1839,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>years_in_yatra_work</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>How many Yatra seasons have you worked in this kind of work?</t>
+          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>आप कितने यात्रा सीज़न से यह काम कर रहे हैं?</t>
+          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1865,7 +1859,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>${n_other_activities} &gt; 0</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1882,17 +1880,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hours_day_yatra</t>
+          <t>years_in_yatra_work</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
+          <t>How many Yatra seasons have you worked in this kind of work?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
+          <t>आप कितने यात्रा सीज़न से यह काम कर रहे हैं?</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1903,21 +1901,9 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Hours a day must be between 1 and 18.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -1931,17 +1917,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>days_week_yatra</t>
+          <t>hours_day_yatra</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>How many days a week do you usually work in the season?</t>
+          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1954,17 +1940,17 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -1975,22 +1961,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>days_week_yatra</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>How many days a week do you usually work in the season?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2001,9 +1987,21 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -2012,22 +2010,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2037,11 +2035,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2058,17 +2052,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2078,7 +2072,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2090,22 +2088,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one prevreason</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2115,11 +2113,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2131,22 +2125,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one prevreason</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2156,7 +2150,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2168,22 +2166,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one trtype</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>training_type</t>
+          <t>training_received</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>What kind of course or training was it?</t>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2193,11 +2191,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>${training_received} = 1</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2209,30 +2203,34 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one trtype</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>training_type_other</t>
+          <t>training_type</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>What was it? Write what they say.</t>
+          <t>What kind of course or training was it?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>वह किस तरह का कोर्स या ट्रेनिंग थी?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>${training_type} = 9</t>
+          <t>${training_received} = 1</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2246,16 +2244,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>training_type_other</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>What was it? Write what they say.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>वह क्या थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>${training_type} = 9</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2267,24 +2281,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>grp_C</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -2295,31 +2297,27 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>intro_C</t>
+          <t>grp_C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing and where you were living, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे और कहाँ रह रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2332,36 +2330,36 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>intro_C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity?</t>
+          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing and where you were living, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे और कहाँ रह रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2379,17 +2377,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity?</t>
+          <t>In May, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2416,17 +2414,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity?</t>
+          <t>In June, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2453,17 +2451,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity?</t>
+          <t>In July, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2490,17 +2488,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity?</t>
+          <t>In August, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2527,17 +2525,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity?</t>
+          <t>In September, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2564,17 +2562,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity?</t>
+          <t>In October, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2601,17 +2599,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity?</t>
+          <t>In November, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2633,36 +2631,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>calc_months_no_work</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>In December, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -2675,17 +2673,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>calc_offseason_work</t>
+          <t>calc_months_no_work</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2697,7 +2695,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -2707,36 +2705,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>calc_offseason_work</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -2749,17 +2747,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity?</t>
+          <t>In January, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2786,17 +2784,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity?</t>
+          <t>In February, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2823,17 +2821,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity?</t>
+          <t>In March, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2855,22 +2853,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one recall</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>In April, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2892,22 +2890,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one recall</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2917,11 +2915,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2938,17 +2932,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2960,7 +2954,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -2979,17 +2973,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -3001,7 +2995,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3020,17 +3014,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3042,7 +3036,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3061,17 +3055,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3083,7 +3077,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3102,17 +3096,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3124,7 +3118,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3143,17 +3137,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3165,7 +3159,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3184,17 +3178,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3206,7 +3200,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3225,17 +3219,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3247,7 +3241,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3266,17 +3260,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3288,7 +3282,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3307,17 +3301,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3329,7 +3323,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3348,17 +3342,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3370,7 +3364,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3389,17 +3383,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3411,7 +3405,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 0</t>
+          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3430,17 +3424,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3455,21 +3449,9 @@
           <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 100</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 100 out of every 100 rupees.</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -3483,17 +3465,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3503,10 +3485,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>${knows_monthly_income} = 0</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 100 out of every 100 rupees.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
@@ -3520,17 +3518,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3552,22 +3550,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>select_one remitmode</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3577,11 +3575,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3593,22 +3587,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one remitmode</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3618,7 +3612,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3635,17 +3633,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3672,17 +3670,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3692,26 +3690,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>${calc_offseason_work} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Hours a day must be between 1 and 18.</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -3725,17 +3707,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3752,17 +3734,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -3773,19 +3755,51 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>days_week_offseason</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>In those months, how many days a week do you usually work?</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>${calc_offseason_work} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
@@ -3794,24 +3808,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>grp_D</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Module D: Migration</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Module D: Migration</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -3822,31 +3824,27 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>intro_D</t>
+          <t>grp_D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
+          <t>Module D: Migration</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
+          <t>Module D: Migration</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3859,36 +3857,36 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one origin</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>intro_D</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Where is your permanent home?</t>
+          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>आपका पक्का घर कहाँ है?</t>
+          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -3901,22 +3899,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one state</t>
+          <t>select_one origin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
+          <t>Where is your permanent home?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+          <t>आपका पक्का घर कहाँ है?</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3938,22 +3936,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one ruralurban</t>
+          <t>select_one state</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>home_state</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Is that home in a village, or in a town or city?</t>
+          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
+          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3975,22 +3973,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one ruralurban</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
+          <t>Is that home in a village, or in a town or city?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
+          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4017,17 +4015,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
+          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
+          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4049,22 +4047,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
+          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
+          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4074,11 +4072,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>${hh_at_home_place} = 1</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -4095,17 +4089,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>n_here_season</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>How many years have you been coming here for the Yatra season?</t>
+          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4117,7 +4111,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${hh_at_home_place} = 1</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4131,22 +4125,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_one comereason</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>years_coming_here</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>What was the main reason you first came here to work?</t>
+          <t>How many years have you been coming here for the Yatra season?</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
+          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4158,7 +4152,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>${origin} != 1</t>
+          <t>${resp_returns_at_closure} = 1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4172,22 +4166,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one comereason</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>came_here_reason</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
+          <t>What was the main reason you first came here to work?</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4197,7 +4191,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>${origin} != 1</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4209,32 +4207,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do there? Write what they say.</t>
+          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>${worked_away_in_closure} = 1</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4246,34 +4244,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>left_here_month</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>In the past year, which month did you last leave here and go to your home place?</t>
+          <t>Where did you go, and what work did you do there? Write what they say.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${worked_away_in_closure} = 1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4292,17 +4286,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>returned_here_month</t>
+          <t>left_here_month</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>And which month did you come back here?</t>
+          <t>In the past year, which month did you last leave here and go to your home place?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>और किस महीने आप वापस यहाँ आए?</t>
+          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4328,22 +4322,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>months_away_for_work</t>
+          <t>returned_here_month</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
+          <t>And which month did you come back here?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
+          <t>और किस महीने आप वापस यहाँ आए?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4355,7 +4349,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>${worked_away_in_closure} = 1</t>
+          <t>${resp_returns_at_closure} = 1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4369,22 +4363,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>worked_other_places</t>
+          <t>months_away_for_work</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Before you started coming here, had you gone anywhere else for work?</t>
+          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4394,7 +4388,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>${worked_away_in_closure} = 1</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4406,32 +4404,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>other_places_detail</t>
+          <t>worked_other_places</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do? Write what they say.</t>
+          <t>Before you started coming here, had you gone anywhere else for work?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>${worked_other_places} = 1</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -4443,32 +4441,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>other_places_detail</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
+          <t>Where did you go, and what work did you do? Write what they say.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>${worked_other_places} = 1</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4480,22 +4478,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one referral</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Who mainly helped you get this work, or arranged it for you?</t>
+          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4517,32 +4515,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one referral</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>migration_referral_other</t>
+          <t>migration_referral</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Who was it? Write what they say.</t>
+          <t>Who mainly helped you get this work, or arranged it for you?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>${migration_referral} = 7</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4554,16 +4552,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>migration_referral_other</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Who was it? Write what they say.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>${migration_referral} = 7</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -4575,24 +4589,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>grp_E</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
@@ -4603,31 +4605,27 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>intro_E</t>
+          <t>grp_E</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Now about what your household usually spends in a month. For each thing I will ask twice -- once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed -- because spending is often quite different in the two. Rough figures are fine.</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4640,36 +4638,36 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>intro_E</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
+          <t>Now about what your household usually spends in a month. For each thing I will ask twice -- once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed -- because spending is often quite different in the two. Rough figures are fine.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
+          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -4682,22 +4680,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4724,17 +4722,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4744,11 +4742,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -4765,17 +4759,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4785,7 +4779,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -4802,17 +4800,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4822,11 +4820,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -4843,17 +4837,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4863,7 +4857,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -4880,17 +4878,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4900,11 +4898,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -4921,17 +4915,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4941,7 +4935,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -4958,17 +4956,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4978,11 +4976,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -4999,17 +4993,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5019,7 +5013,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -5036,17 +5034,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -5056,11 +5054,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -5077,17 +5071,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -5097,7 +5091,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -5114,17 +5112,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -5134,11 +5132,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5155,17 +5149,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5175,7 +5169,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5192,17 +5190,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -5212,11 +5210,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5233,17 +5227,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -5253,7 +5247,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5270,17 +5268,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -5290,11 +5288,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5311,17 +5305,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -5331,7 +5325,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -5348,17 +5346,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5368,11 +5366,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -5389,17 +5383,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5409,7 +5403,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5426,17 +5424,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5446,11 +5444,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -5467,17 +5461,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5487,7 +5481,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5504,17 +5502,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5524,11 +5522,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5545,17 +5539,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5565,7 +5559,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -5582,17 +5580,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5619,17 +5617,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5656,17 +5654,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5688,15 +5686,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>cons_durables_12m</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
@@ -5709,24 +5723,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>grp_F</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
@@ -5737,31 +5739,27 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>intro_F</t>
+          <t>grp_F</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Now some questions about your house and the things your household has.</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5774,36 +5772,36 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_one floor</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>intro_F</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>Now some questions about your house and the things your household has.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
+          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
@@ -5816,22 +5814,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one roof</t>
+          <t>select_one floor</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5853,22 +5851,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one wall</t>
+          <t>select_one roof</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5890,22 +5888,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>select_one house</t>
+          <t>select_one wall</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>house_type</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Would you describe your usual home as kaccha (mud/thatch, temporary), semi-pucca (part-concrete) or pucca (solid, permanent)?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5927,22 +5925,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one house</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>house_type</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>Would you describe your usual home as kaccha (mud/thatch, temporary), semi-pucca (part-concrete) or pucca (solid, permanent)?</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>अपने असली घर को आप क्या कहेंगे: कच्चा (मिट्टी/फूस का, कामचलाऊ), अधपक्का, या पक्का (मज़बूत, स्थायी)?</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5964,22 +5962,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -6001,22 +5999,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>select_one water</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6038,22 +6036,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one water</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6075,22 +6073,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6100,26 +6098,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>${water_on_premises} = 0</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 300</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Minutes must be between 0 and 300.</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -6128,22 +6110,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_one fetcher</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>water_fetched_by</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Who in the household usually goes to fetch it?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>घर में आम तौर पर पानी कौन लाता है?</t>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6158,9 +6140,21 @@
           <t>${water_on_premises} = 0</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 300</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Minutes must be between 0 and 300.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
@@ -6169,22 +6163,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>select_one fuel</t>
+          <t>select_one fetcher</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetched_by</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>Who in the household usually goes to fetch it?</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>घर में आम तौर पर पानी कौन लाता है?</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6194,7 +6188,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>${water_on_premises} = 0</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -6206,22 +6204,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one fuel</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6248,17 +6246,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -6285,17 +6283,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -6322,17 +6320,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6359,17 +6357,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6396,17 +6394,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6433,17 +6431,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6470,17 +6468,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6507,17 +6505,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6539,22 +6537,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+          <t>...फ़्रिज?</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6576,22 +6574,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6618,17 +6616,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6655,17 +6653,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6692,17 +6690,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6729,17 +6727,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6766,17 +6764,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6798,32 +6796,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>${owns_work_equipment} = 1</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -6835,16 +6833,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>work_equipment_detail</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>${owns_work_equipment} = 1</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
@@ -6856,24 +6870,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>grp_G</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
@@ -6884,31 +6886,27 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>intro_G</t>
+          <t>grp_G</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Now about savings, loans, insurance and government schemes.</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6921,36 +6919,36 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>intro_G</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>Now about savings, loans, insurance and government schemes.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
+          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
@@ -6968,17 +6966,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>has_jandhan_account</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Is any of these a Jan Dhan account?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>क्या उनमें से कोई जन धन खाता है?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6988,11 +6986,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>${has_bank_account} = 1</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -7009,17 +7003,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_jandhan_account</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Is any of these a Jan Dhan account?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या उनमें से कोई जन धन खाता है?</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7029,7 +7023,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>${has_bank_account} = 1</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
@@ -7041,22 +7039,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_one credit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7066,11 +7064,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>${took_loan_12m} = 1</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
@@ -7082,22 +7076,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one credit</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7123,22 +7117,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7164,30 +7158,34 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>${pays_interest} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -7201,34 +7199,30 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>${took_loan_12m} = 1</t>
+          <t>${pays_interest} = 1</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -7242,22 +7236,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>select_one collat</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7269,7 +7263,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>${loan_against_asset} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -7283,22 +7277,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one collat</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7308,22 +7302,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>${loan_against_asset} = 1</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
@@ -7337,17 +7323,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7381,22 +7367,22 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7406,14 +7392,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>${land_cultivable_acres} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
@@ -7422,22 +7416,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>select_multiple govtscheme</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7447,7 +7441,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>${land_cultivable_acres} &gt; 0</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
@@ -7459,32 +7457,32 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple govtscheme</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>selected(${govt_schemes}, '9')</t>
-        </is>
-      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
@@ -7496,32 +7494,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>selected(${govt_schemes}, '9')</t>
+        </is>
+      </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
@@ -7538,17 +7536,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7570,22 +7568,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7596,21 +7594,9 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
@@ -7619,19 +7605,47 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>n_can_transact_online</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
@@ -7640,24 +7654,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>grp_H</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
@@ -7668,31 +7670,27 @@
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>intro_H</t>
+          <t>grp_H</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Now a few questions about health in your household. You may leave out any of these.</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -7705,36 +7703,36 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>intro_H</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Now a few questions about health in your household. You may leave out any of these.</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
@@ -7747,22 +7745,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>select_one coping</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7772,11 +7770,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>${morbidity_15d} = 1</t>
-        </is>
-      </c>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
@@ -7788,22 +7782,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one coping</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7829,22 +7823,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7854,7 +7848,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>${morbidity_15d} = 1</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -7871,17 +7869,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7908,17 +7906,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7945,17 +7943,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7977,22 +7975,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -8002,11 +8000,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>${birth_last_5y} = 1</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -8023,17 +8017,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -8059,16 +8053,36 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>skilled_birth_attendant</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>${birth_last_5y} = 1</t>
+        </is>
+      </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
@@ -8080,24 +8094,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>grp_I</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
@@ -8108,31 +8110,27 @@
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>intro_I</t>
+          <t>grp_I</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -8145,36 +8143,36 @@
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>select_multiple distress</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>intro_I</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
@@ -8187,22 +8185,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>select_multiple coping</t>
+          <t>select_multiple distress</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -8212,11 +8210,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
@@ -8228,22 +8222,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple coping</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -8253,22 +8247,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr"/>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
@@ -8282,17 +8268,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -8331,17 +8317,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -8380,17 +8366,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -8429,17 +8415,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -8478,17 +8464,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -8527,17 +8513,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -8576,17 +8562,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8625,17 +8611,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8674,17 +8660,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8718,19 +8704,47 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>cope_restrict_adult_offseason_wk</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H214" t="inlineStr"/>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
@@ -8739,24 +8753,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>grp_J</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr"/>
@@ -8767,31 +8769,27 @@
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>intro_J</t>
+          <t>grp_J</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8804,36 +8802,36 @@
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>select_one stance</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>intro_J</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
@@ -8846,22 +8844,22 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one stance</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8883,15 +8881,31 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>trek_dependent</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
@@ -8904,24 +8918,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>grp_K</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
@@ -8932,31 +8934,27 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>grp_K</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -8969,36 +8967,36 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
@@ -9011,44 +9009,32 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
-        </is>
-      </c>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
@@ -9060,26 +9046,34 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9087,7 +9081,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -9101,22 +9095,22 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -9128,7 +9122,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -9142,22 +9136,22 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -9183,22 +9177,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -9224,22 +9218,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -9270,17 +9264,17 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -9311,17 +9305,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -9352,17 +9346,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -9374,7 +9368,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -9388,22 +9382,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9415,7 +9409,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+          <t>${job_situation} &lt;= 7</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -9434,17 +9428,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -9456,7 +9450,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -9470,22 +9464,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -9495,7 +9489,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
@@ -9507,15 +9505,31 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr"/>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>first_job_ever</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Was your current work the first paid job you ever had?</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
@@ -9528,24 +9542,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>grp_L</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
@@ -9556,31 +9558,27 @@
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>grp_L</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -9593,36 +9591,36 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
@@ -9640,17 +9638,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9677,17 +9675,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -9714,17 +9712,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9751,17 +9749,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9788,17 +9786,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9825,17 +9823,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9862,17 +9860,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9899,17 +9897,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9936,17 +9934,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9973,17 +9971,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10010,17 +10008,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10042,22 +10040,22 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10067,11 +10065,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
@@ -10088,17 +10082,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10129,17 +10123,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10170,17 +10164,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10190,7 +10184,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr"/>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
@@ -10207,17 +10205,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10239,15 +10237,31 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr"/>
-      <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>calc_at_work</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>In your work, do you work out prices or costs?</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
@@ -10277,6 +10291,27 @@
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -8166,9 +8166,21 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
@@ -8204,7 +8216,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -8249,7 +8261,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -8290,7 +8302,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -8331,7 +8343,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>count-selected(${distress_event_last365d}) &gt; 0</t>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -10406,7 +10418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11547,20 +11559,20 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Serious illness or death of an earning member</t>
+          <t>Nothing of this kind happened</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>कमाने वाले की गंभीर बीमारी या मौत</t>
+          <t>ऐसा कुछ नहीं हुआ</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -11570,20 +11582,20 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Crop failure or livestock loss</t>
+          <t>Serious illness or death of an earning member</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>फ़सल या जानवर का नुक़सान</t>
+          <t>कमाने वाले की गंभीर बीमारी या मौत</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -11593,20 +11605,20 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Damage from a natural disaster (flood, landslide, fire)</t>
+          <t>Crop failure or livestock loss</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>किसी आपदा से नुक़सान (बाढ़, भूस्खलन, आग)</t>
+          <t>फ़सल या जानवर का नुक़सान</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -11616,20 +11628,20 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Loss of business, goods or assets</t>
+          <t>Damage from a natural disaster (flood, landslide, fire)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>धंधे, सामान या संपत्ति का नुक़सान</t>
+          <t>किसी आपदा से नुक़सान (बाढ़, भूस्खलन, आग)</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -11639,20 +11651,20 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Road or bridge blocked, route closed</t>
+          <t>Loss of business, goods or assets</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>रास्ता या पुल बंद हो गया</t>
+          <t>धंधे, सामान या संपत्ति का नुक़सान</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -11662,20 +11674,20 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Yatra stopped early or badly disrupted</t>
+          <t>Road or bridge blocked, route closed</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>यात्रा जल्दी बंद हुई या बुरी तरह बाधित हुई</t>
+          <t>रास्ता या पुल बंद हो गया</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
@@ -11685,20 +11697,20 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sharp fall in customers or prices</t>
+          <t>Yatra stopped early or badly disrupted</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ग्राहक या दाम बहुत गिर गए</t>
+          <t>यात्रा जल्दी बंद हुई या बुरी तरह बाधित हुई</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -11708,43 +11720,43 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lost the work or the work stopped</t>
+          <t>Sharp fall in customers or prices</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>काम छूट गया या काम बंद हो गया</t>
+          <t>ग्राहक या दाम बहुत गिर गए</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>No formal education</t>
+          <t>Lost the work or the work stopped</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>बिल्कुल नहीं पढ़े</t>
+          <t>काम छूट गया या काम बंद हो गया</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
@@ -11754,20 +11766,20 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Some schooling, did not complete primary</t>
+          <t>No formal education</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>थोड़ा पढ़े, प्राइमरी पूरी नहीं</t>
+          <t>बिल्कुल नहीं पढ़े</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -11777,20 +11789,20 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Completed primary but not secondary</t>
+          <t>Some schooling, did not complete primary</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>प्राइमरी पूरी, दसवीं नहीं</t>
+          <t>थोड़ा पढ़े, प्राइमरी पूरी नहीं</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -11800,20 +11812,20 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Completed secondary or higher</t>
+          <t>Completed primary but not secondary</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>दसवीं या उससे ज़्यादा</t>
+          <t>प्राइमरी पूरी, दसवीं नहीं</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -11823,43 +11835,43 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Completed secondary or higher</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>दसवीं या उससे ज़्यादा</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Own-account (self-employed, no hired workers)</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>अपना काम, कोई नौकर नहीं</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
@@ -11869,20 +11881,20 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Employer/business owner (self-employed)</t>
+          <t>Own-account (self-employed, no hired workers)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>मालिक, दूसरों को काम पर रखते हैं</t>
+          <t>अपना काम, कोई नौकर नहीं</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -11892,20 +11904,20 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Regular wage or salary</t>
+          <t>Employer/business owner (self-employed)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>महीने की पक्की तनख़्वाह</t>
+          <t>मालिक, दूसरों को काम पर रखते हैं</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -11915,20 +11927,20 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Casual or daily wage labour</t>
+          <t>Regular wage or salary</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
+          <t>महीने की पक्की तनख़्वाह</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -11938,43 +11950,43 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Unpaid family worker</t>
+          <t>Casual or daily wage labour</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>घर के काम में बिना पैसे के हाथ बँटाते हैं</t>
+          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Unpaid family worker</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>रमन</t>
+          <t>घर के काम में बिना पैसे के हाथ बँटाते हैं</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -11984,20 +11996,20 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rishit</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ऋषित</t>
+          <t>रमन</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -12007,20 +12019,20 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tanmay</t>
+          <t>Rishit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>तन्मय</t>
+          <t>ऋषित</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -12030,43 +12042,43 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Anuj</t>
+          <t>Tanmay</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>अनुज</t>
+          <t>तन्मय</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>famstruct</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nuclear (you, spouse and unmarried children only)</t>
+          <t>Anuj</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>छोटा परिवार (आप, पति/पत्नी और बिन ब्याहे बच्चे)</t>
+          <t>अनुज</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -12076,20 +12088,20 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Joint (living with parents, married siblings or other extended family)</t>
+          <t>Nuclear (you, spouse and unmarried children only)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>बड़ा परिवार (माँ-बाप, ब्याहे भाई-बहन या और रिश्तेदार साथ)</t>
+          <t>छोटा परिवार (आप, पति/पत्नी और बिन ब्याहे बच्चे)</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -12099,43 +12111,43 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Single-member household</t>
+          <t>Joint (living with parents, married siblings or other extended family)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>अकेले रहते हैं</t>
+          <t>बड़ा परिवार (माँ-बाप, ब्याहे भाई-बहन या और रिश्तेदार साथ)</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>famstruct</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mud/kaccha</t>
+          <t>Single-member household</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>मिट्टी/कच्चा</t>
+          <t>अकेले रहते हैं</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -12145,20 +12157,20 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cement/mud-cement</t>
+          <t>Mud/kaccha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>सीमेंट या सीमेंट-मिट्टी</t>
+          <t>मिट्टी/कच्चा</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -12168,43 +12180,43 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tile/mosaic/marble</t>
+          <t>Cement/mud-cement</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>टाइल/मोज़ेक/मार्बल</t>
+          <t>सीमेंट या सीमेंट-मिट्टी</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LPG or cylinder gas</t>
+          <t>Tile/mosaic/marble</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LPG या सिलेंडर गैस</t>
+          <t>टाइल/मोज़ेक/मार्बल</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -12214,20 +12226,20 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piped natural gas</t>
+          <t>LPG or cylinder gas</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>पाइप से आने वाली गैस</t>
+          <t>LPG या सिलेंडर गैस</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -12237,20 +12249,20 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Piped natural gas</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>बिजली</t>
+          <t>पाइप से आने वाली गैस</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -12260,20 +12272,20 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Biogas (gobar gas plant)</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>गोबर गैस (बायोगैस)</t>
+          <t>बिजली</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -12283,20 +12295,20 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>Biogas (gobar gas plant)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>मिट्टी का तेल</t>
+          <t>गोबर गैस (बायोगैस)</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -12306,20 +12318,20 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Firewood</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>लकड़ी</t>
+          <t>मिट्टी का तेल</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -12329,20 +12341,20 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dung cakes (gobar)</t>
+          <t>Firewood</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>गोबर के उपले</t>
+          <t>लकड़ी</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -12352,20 +12364,20 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Crop residue, straw or shrubs</t>
+          <t>Dung cakes (gobar)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>फ़सल के डंठल, पुआल या झाड़ियाँ</t>
+          <t>गोबर के उपले</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
@@ -12375,20 +12387,20 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Charcoal</t>
+          <t>Crop residue, straw or shrubs</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>लकड़ी का कोयला</t>
+          <t>फ़सल के डंठल, पुआल या झाड़ियाँ</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87">
@@ -12398,43 +12410,43 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Coal or lignite</t>
+          <t>Charcoal</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>पत्थर का कोयला</t>
+          <t>लकड़ी का कोयला</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>govtscheme</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ration card / PDS food grain</t>
+          <t>Coal or lignite</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>राशन कार्ड / सरकारी राशन</t>
+          <t>पत्थर का कोयला</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -12444,20 +12456,20 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MGNREGA work or job card</t>
+          <t>Ration card / PDS food grain</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>मनरेगा का काम या जॉब कार्ड</t>
+          <t>राशन कार्ड / सरकारी राशन</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -12467,20 +12479,20 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Old-age, widow or disability pension</t>
+          <t>MGNREGA work or job card</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>बुढ़ापा, विधवा या दिव्यांग पेंशन</t>
+          <t>मनरेगा का काम या जॉब कार्ड</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -12490,20 +12502,20 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PM-KISAN (farmer cash transfer)</t>
+          <t>Old-age, widow or disability pension</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>पीएम-किसान (किसान को पैसा)</t>
+          <t>बुढ़ापा, विधवा या दिव्यांग पेंशन</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -12513,20 +12525,20 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ujjwala LPG connection</t>
+          <t>PM-KISAN (farmer cash transfer)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>उज्ज्वला गैस कनेक्शन</t>
+          <t>पीएम-किसान (किसान को पैसा)</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -12536,20 +12548,20 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PM-SYM or Atal Pension Yojana</t>
+          <t>Ujjwala LPG connection</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>पीएम-श्रम योगी मानधन या अटल पेंशन योजना</t>
+          <t>उज्ज्वला गैस कनेक्शन</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -12559,20 +12571,20 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ayushman Bharat / health insurance card</t>
+          <t>PM-SYM or Atal Pension Yojana</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>आयुष्मान भारत / इलाज का कार्ड</t>
+          <t>पीएम-श्रम योगी मानधन या अटल पेंशन योजना</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
@@ -12582,20 +12594,20 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Housing scheme (PMAY or state)</t>
+          <t>Ayushman Bharat / health insurance card</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>आवास योजना (पीएमएवाई या राज्य की)</t>
+          <t>आयुष्मान भारत / इलाज का कार्ड</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
@@ -12605,20 +12617,20 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Some other scheme</t>
+          <t>Housing scheme (PMAY or state)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>कोई और योजना</t>
+          <t>आवास योजना (पीएमएवाई या राज्य की)</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -12628,43 +12640,43 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>None of these</t>
+          <t>Some other scheme</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>इनमें से कोई नहीं</t>
+          <t>कोई और योजना</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>govtscheme</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Self (respondent is the head)</t>
+          <t>None of these</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>मैं खुद मुखिया हूँ</t>
+          <t>इनमें से कोई नहीं</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99">
@@ -12674,20 +12686,20 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Self (respondent is the head)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>पति</t>
+          <t>मैं खुद मुखिया हूँ</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -12697,20 +12709,20 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>पत्नी</t>
+          <t>पति</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -12720,20 +12732,20 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>पिता</t>
+          <t>पत्नी</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -12743,20 +12755,20 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>माता</t>
+          <t>पिता</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -12766,20 +12778,20 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>बेटा</t>
+          <t>माता</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -12789,20 +12801,20 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>बेटी</t>
+          <t>बेटा</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
@@ -12812,20 +12824,20 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>भाई</t>
+          <t>बेटी</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -12835,20 +12847,20 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>बहन</t>
+          <t>भाई</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
@@ -12858,20 +12870,20 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Other male relative</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>कोई और पुरुष रिश्तेदार</t>
+          <t>बहन</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108">
@@ -12881,20 +12893,20 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Other female relative</t>
+          <t>Other male relative</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>कोई और महिला रिश्तेदार</t>
+          <t>कोई और पुरुष रिश्तेदार</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109">
@@ -12904,20 +12916,20 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Other, non-relative (male)</t>
+          <t>Other female relative</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, पुरुष</t>
+          <t>कोई और महिला रिश्तेदार</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110">
@@ -12927,43 +12939,43 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other, non-relative (female)</t>
+          <t>Other, non-relative (male)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, महिला</t>
+          <t>रिश्तेदार नहीं, पुरुष</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>jobperm</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Other, non-relative (female)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>पक्का</t>
+          <t>रिश्तेदार नहीं, महिला</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
@@ -12973,20 +12985,20 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seasonal or temporary</t>
+          <t>Permanent</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>मौसमी या कुछ समय का</t>
+          <t>पक्का</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -12996,20 +13008,20 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Occasional or casual</t>
+          <t>Seasonal or temporary</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>कभी-कभार का</t>
+          <t>मौसमी या कुछ समय का</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -13019,20 +13031,20 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>On probation</t>
+          <t>Occasional or casual</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>परखने की अवधि पर</t>
+          <t>कभी-कभार का</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -13042,43 +13054,43 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fixed-term</t>
+          <t>On probation</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>तय समय के लिए</t>
+          <t>परखने की अवधि पर</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>jobsit</t>
+          <t>jobperm</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Works for pay full-time</t>
+          <t>Fixed-term</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>पूरे समय पैसे के लिए काम</t>
+          <t>तय समय के लिए</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -13088,20 +13100,20 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Works for pay part-time or occasional jobs</t>
+          <t>Works for pay full-time</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>कुछ समय या कभी-कभार का काम</t>
+          <t>पूरे समय पैसे के लिए काम</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -13111,20 +13123,20 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Studies and works</t>
+          <t>Works for pay part-time or occasional jobs</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>पढ़ाई के साथ काम</t>
+          <t>कुछ समय या कभी-कभार का काम</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -13134,20 +13146,20 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Only studies</t>
+          <t>Studies and works</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>सिर्फ़ पढ़ाई</t>
+          <t>पढ़ाई के साथ काम</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -13157,20 +13169,20 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Being trained for work only</t>
+          <t>Only studies</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>सिर्फ़ काम की ट्रेनिंग</t>
+          <t>सिर्फ़ पढ़ाई</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -13180,20 +13192,20 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Retired or pensioned</t>
+          <t>Being trained for work only</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>रिटायर या पेंशन पर</t>
+          <t>सिर्फ़ काम की ट्रेनिंग</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -13203,20 +13215,20 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Unpaid household tasks or caring for others</t>
+          <t>Retired or pensioned</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>घर का बिना पैसे का काम या देखभाल</t>
+          <t>रिटायर या पेंशन पर</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -13226,20 +13238,20 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Unemployed, actively seeking work</t>
+          <t>Unpaid household tasks or caring for others</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>काम नहीं है, ढूँढ रहे हैं</t>
+          <t>घर का बिना पैसे का काम या देखभाल</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -13249,20 +13261,20 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sick or disabled, cannot work</t>
+          <t>Unemployed, actively seeking work</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>बीमारी या विकलांगता से काम नहीं कर सकते</t>
+          <t>काम नहीं है, ढूँढ रहे हैं</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
@@ -13272,20 +13284,20 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Neither studying, working nor seeking work</t>
+          <t>Sick or disabled, cannot work</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>न पढ़ाई, न काम, न ढूँढ रहे हैं</t>
+          <t>बीमारी या विकलांगता से काम नहीं कर सकते</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -13295,43 +13307,43 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Does not know</t>
+          <t>Neither studying, working nor seeking work</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>न पढ़ाई, न काम, न ढूँढ रहे हैं</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>97</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>jobsit</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Currently married</t>
+          <t>Does not know</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>शादीशुदा</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="128">
@@ -13341,20 +13353,20 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Never married</t>
+          <t>Currently married</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>शादी नहीं हुई</t>
+          <t>शादीशुदा</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -13364,43 +13376,43 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Widowed/divorced/separated</t>
+          <t>Never married</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>विधवा/विधुर या अलग</t>
+          <t>शादी नहीं हुई</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Widowed/divorced/separated</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>जनवरी</t>
+          <t>विधवा/विधुर या अलग</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -13410,20 +13422,20 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>फ़रवरी</t>
+          <t>जनवरी</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -13433,20 +13445,20 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>मार्च</t>
+          <t>फ़रवरी</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -13456,20 +13468,20 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>अप्रैल</t>
+          <t>मार्च</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -13479,20 +13491,20 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>मई</t>
+          <t>अप्रैल</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -13502,20 +13514,20 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>जून</t>
+          <t>मई</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -13525,20 +13537,20 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>June</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>जुलाई</t>
+          <t>जून</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137">
@@ -13548,20 +13560,20 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>अगस्त</t>
+          <t>जुलाई</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
@@ -13571,20 +13583,20 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>August</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>सितंबर</t>
+          <t>अगस्त</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139">
@@ -13594,20 +13606,20 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>अक्टूबर</t>
+          <t>सितंबर</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
@@ -13617,20 +13629,20 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>नवंबर</t>
+          <t>अक्टूबर</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="141">
@@ -13640,43 +13652,43 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>दिसंबर</t>
+          <t>नवंबर</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Garhwali</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>गढ़वाली</t>
+          <t>दिसंबर</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
@@ -13686,20 +13698,20 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Kumaoni</t>
+          <t>Garhwali</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>कुमाऊँनी</t>
+          <t>गढ़वाली</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -13709,20 +13721,20 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kumaoni</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>हिंदी</t>
+          <t>कुमाऊँनी</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -13732,20 +13744,20 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Nepali</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>नेपाली</t>
+          <t>हिंदी</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -13755,20 +13767,20 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bhojpuri</t>
+          <t>Nepali</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>भोजपुरी</t>
+          <t>नेपाली</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="147">
@@ -13778,20 +13790,20 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Assamese</t>
+          <t>Bhojpuri</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>असमिया</t>
+          <t>भोजपुरी</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
@@ -13801,20 +13813,20 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Assamese</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>बांग्ला</t>
+          <t>असमिया</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149">
@@ -13824,20 +13836,20 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bodo</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>बोडो</t>
+          <t>बांग्ला</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
@@ -13847,20 +13859,20 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dogri</t>
+          <t>Bodo</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>डोगरी</t>
+          <t>बोडो</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -13870,20 +13882,20 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Dogri</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>गुजराती</t>
+          <t>डोगरी</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152">
@@ -13893,20 +13905,20 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>कन्नड़</t>
+          <t>गुजराती</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153">
@@ -13916,20 +13928,20 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kashmiri</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>कश्मीरी</t>
+          <t>कन्नड़</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154">
@@ -13939,20 +13951,20 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Konkani</t>
+          <t>Kashmiri</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>कोंकणी</t>
+          <t>कश्मीरी</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155">
@@ -13962,20 +13974,20 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Maithili</t>
+          <t>Konkani</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>मैथिली</t>
+          <t>कोंकणी</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156">
@@ -13985,20 +13997,20 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Maithili</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>मलयालम</t>
+          <t>मैथिली</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
@@ -14008,20 +14020,20 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Manipuri (Meitei)</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>मणिपुरी (मैतेई)</t>
+          <t>मलयालम</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158">
@@ -14031,20 +14043,20 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Marathi</t>
+          <t>Manipuri (Meitei)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>मराठी</t>
+          <t>मणिपुरी (मैतेई)</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159">
@@ -14054,20 +14066,20 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Odia</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ओड़िया</t>
+          <t>मराठी</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160">
@@ -14077,20 +14089,20 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Punjabi</t>
+          <t>Odia</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>पंजाबी</t>
+          <t>ओड़िया</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="161">
@@ -14100,20 +14112,20 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Punjabi</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>संस्कृत</t>
+          <t>पंजाबी</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162">
@@ -14123,20 +14135,20 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Santali</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>संताली</t>
+          <t>संस्कृत</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163">
@@ -14146,20 +14158,20 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sindhi</t>
+          <t>Santali</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>सिंधी</t>
+          <t>संताली</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164">
@@ -14169,20 +14181,20 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Sindhi</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>तमिल</t>
+          <t>सिंधी</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165">
@@ -14192,20 +14204,20 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>तेलुगु</t>
+          <t>तमिल</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="166">
@@ -14215,20 +14227,20 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>उर्दू</t>
+          <t>तेलुगु</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="167">
@@ -14238,20 +14250,20 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Other Indian language</t>
+          <t>Urdu</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>कोई और भारतीय भाषा</t>
+          <t>उर्दू</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168">
@@ -14261,43 +14273,43 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Other / foreign language</t>
+          <t>Other Indian language</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>कोई और / विदेशी भाषा</t>
+          <t>कोई और भारतीय भाषा</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pony/mule worker (works the animals, does not own them)</t>
+          <t>Other / foreign language</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
+          <t>कोई और / विदेशी भाषा</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="170">
@@ -14307,20 +14319,20 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Pony/mule owner (owns the animals)</t>
+          <t>Pony/mule worker (works the animals, does not own them)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर का मालिक</t>
+          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -14330,20 +14342,20 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
+          <t>Pony/mule owner (owns the animals)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
+          <t>घोड़े/खच्चर का मालिक</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -14353,20 +14365,20 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
+          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
+          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -14376,20 +14388,20 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
+          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
+          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
@@ -14399,20 +14411,20 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
+          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
+          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175">
@@ -14422,20 +14434,20 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
+          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
+          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176">
@@ -14445,20 +14457,20 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Shop OWNER (goods, not prepared food)</t>
+          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
+          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
@@ -14468,20 +14480,20 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hotel / lodge WORKER</t>
+          <t>Shop OWNER (goods, not prepared food)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>होटल / लॉज में काम</t>
+          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178">
@@ -14491,20 +14503,20 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hotel / lodge OWNER</t>
+          <t>Hotel / lodge WORKER</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>होटल / लॉज का मालिक</t>
+          <t>होटल / लॉज में काम</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
@@ -14514,20 +14526,20 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Driver (any motor vehicle)</t>
+          <t>Hotel / lodge OWNER</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>ड्राइवर (कोई भी गाड़ी)</t>
+          <t>होटल / लॉज का मालिक</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180">
@@ -14537,20 +14549,20 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Driver (any motor vehicle)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>गाइड</t>
+          <t>ड्राइवर (कोई भी गाड़ी)</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
@@ -14560,20 +14572,20 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Wage labourer (construction, loading, odd jobs)</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
+          <t>गाइड</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182">
@@ -14583,43 +14595,43 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Wage labourer (construction, loading, odd jobs)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Local (same district)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>यहीं का (इसी ज़िले का)</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="184">
@@ -14629,20 +14641,20 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Other Uttarakhand district</t>
+          <t>Local (same district)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>उत्तराखंड का दूसरा ज़िला</t>
+          <t>यहीं का (इसी ज़िले का)</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -14652,20 +14664,20 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Other Indian state</t>
+          <t>Other Uttarakhand district</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>भारत का दूसरा राज्य</t>
+          <t>उत्तराखंड का दूसरा ज़िला</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -14675,43 +14687,43 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Other Indian state</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>नेपाल</t>
+          <t>भारत का दूसरा राज्य</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Yes, employer deducts it</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>हाँ, मालिक काटता है</t>
+          <t>नेपाल</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -14721,20 +14733,20 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Yes, contributes voluntarily</t>
+          <t>Yes, employer deducts it</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>हाँ, अपनी मर्ज़ी से</t>
+          <t>हाँ, मालिक काटता है</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -14744,43 +14756,43 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes, contributes voluntarily</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>हाँ, अपनी मर्ज़ी से</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Yes, can draw it here</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>हाँ, यहाँ मिल जाता है</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -14790,20 +14802,20 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>No, only at the home place</t>
+          <t>Yes, can draw it here</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
+          <t>हाँ, यहाँ मिल जाता है</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
@@ -14813,20 +14825,20 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Has never tried</t>
+          <t>No, only at the home place</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>कभी कोशिश नहीं की</t>
+          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193">
@@ -14836,43 +14848,43 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Does not know</t>
+          <t>Has never tried</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>कभी कोशिश नहीं की</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Better income</t>
+          <t>Does not know</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ज़्यादा कमाई</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="195">
@@ -14882,20 +14894,20 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Lost the previous work</t>
+          <t>Better income</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>पहला काम छूट गया</t>
+          <t>ज़्यादा कमाई</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -14905,20 +14917,20 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Work ended with the season</t>
+          <t>Lost the previous work</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>मौसम के साथ काम ख़त्म हो गया</t>
+          <t>पहला काम छूट गया</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -14928,20 +14940,20 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Family reasons</t>
+          <t>Work ended with the season</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>घर की वजह से</t>
+          <t>मौसम के साथ काम ख़त्म हो गया</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198">
@@ -14951,20 +14963,20 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Health or injury</t>
+          <t>Family reasons</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>सेहत या चोट</t>
+          <t>घर की वजह से</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="199">
@@ -14974,43 +14986,43 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Health or injury</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>कोई और वजह</t>
+          <t>सेहत या चोट</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Month by month</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>हर महीने का अलग-अलग</t>
+          <t>कोई और वजह</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201">
@@ -15020,43 +15032,43 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>One total for the whole year</t>
+          <t>Month by month</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>पूरे साल का एक जोड़</t>
+          <t>हर महीने का अलग-अलग</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>A family member already working here</t>
+          <t>One total for the whole year</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>यहाँ पहले से काम कर रहा घरवाला</t>
+          <t>पूरे साल का एक जोड़</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -15066,20 +15078,20 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>A friend or someone from the village</t>
+          <t>A family member already working here</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>दोस्त या गाँव का कोई आदमी</t>
+          <t>यहाँ पहले से काम कर रहा घरवाला</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -15089,20 +15101,20 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>A thekedar or contractor I now work for</t>
+          <t>A friend or someone from the village</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
+          <t>दोस्त या गाँव का कोई आदमी</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
@@ -15112,20 +15124,20 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>An agent or middleman who placed me (usually for a fee)</t>
+          <t>A thekedar or contractor I now work for</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
+          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206">
@@ -15135,20 +15147,20 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>No one; I found it myself</t>
+          <t>An agent or middleman who placed me (usually for a fee)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>कोई नहीं, ख़ुद ढूँढा</t>
+          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207">
@@ -15158,20 +15170,20 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>The employer called me directly</t>
+          <t>No one; I found it myself</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>मालिक ने सीधे बुलाया</t>
+          <t>कोई नहीं, ख़ुद ढूँढा</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208">
@@ -15181,43 +15193,43 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Someone else</t>
+          <t>The employer called me directly</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>मालिक ने सीधे बुलाया</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>From my own phone (UPI or net banking)</t>
+          <t>Someone else</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210">
@@ -15227,20 +15239,20 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>In person at a bank branch or bank mitra / CSP</t>
+          <t>From my own phone (UPI or net banking)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
+          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -15250,20 +15262,20 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Money order or post office</t>
+          <t>In person at a bank branch or bank mitra / CSP</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>मनीऑर्डर या डाकघर से</t>
+          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -15273,20 +15285,20 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sent with someone going home</t>
+          <t>Money order or post office</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>घर जा रहे किसी के हाथ</t>
+          <t>मनीऑर्डर या डाकघर से</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213">
@@ -15296,20 +15308,20 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Carried it myself</t>
+          <t>Sent with someone going home</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ख़ुद लेकर गए</t>
+          <t>घर जा रहे किसी के हाथ</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
@@ -15319,20 +15331,20 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Through an agent or middleman</t>
+          <t>Carried it myself</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
+          <t>ख़ुद लेकर गए</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215">
@@ -15342,43 +15354,43 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Through an agent or middleman</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>कोई और तरीक़ा</t>
+          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Thatch/wood/mud</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>फूस/लकड़ी/मिट्टी</t>
+          <t>कोई और तरीक़ा</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217">
@@ -15388,20 +15400,20 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tin/GI sheet</t>
+          <t>Thatch/wood/mud</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>टीन/चादर</t>
+          <t>फूस/लकड़ी/मिट्टी</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -15411,43 +15423,43 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Concrete/RCC</t>
+          <t>Tin/GI sheet</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>छत (कंक्रीट/RCC)</t>
+          <t>टीन/चादर</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Village (rural)</t>
+          <t>Concrete/RCC</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>गाँव में</t>
+          <t>छत (कंक्रीट/RCC)</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -15457,43 +15469,43 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Town or city (urban)</t>
+          <t>Village (rural)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>शहर या क़स्बे में</t>
+          <t>गाँव में</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Town or city (urban)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>शहर या क़स्बे में</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -15503,26 +15515,26 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -15530,12 +15542,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Kedarnath (Gaurikund to Kedarnath)</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -15549,43 +15561,43 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
+          <t>Kedarnath (Gaurikund to Kedarnath)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
+          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>समर्थन में</t>
+          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -15595,20 +15607,20 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>तटस्थ</t>
+          <t>समर्थन में</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -15618,20 +15630,20 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>विरोध में</t>
+          <t>तटस्थ</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228">
@@ -15641,43 +15653,43 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>विरोध में</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="230">
@@ -15687,20 +15699,20 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -15710,20 +15722,20 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
@@ -15733,20 +15745,20 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
@@ -15756,20 +15768,20 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234">
@@ -15779,20 +15791,20 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
@@ -15802,20 +15814,20 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>गोवा</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236">
@@ -15825,20 +15837,20 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -15848,20 +15860,20 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>हरियाणा</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="238">
@@ -15871,20 +15883,20 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="239">
@@ -15894,20 +15906,20 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>झारखंड</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="240">
@@ -15917,20 +15929,20 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241">
@@ -15940,20 +15952,20 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="242">
@@ -15963,20 +15975,20 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="243">
@@ -15986,20 +15998,20 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="244">
@@ -16009,20 +16021,20 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>मणिपुर</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="245">
@@ -16032,20 +16044,20 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>मेघालय</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="246">
@@ -16055,20 +16067,20 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247">
@@ -16078,20 +16090,20 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>नागालैंड</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248">
@@ -16101,20 +16113,20 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249">
@@ -16124,20 +16136,20 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250">
@@ -16147,20 +16159,20 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251">
@@ -16170,20 +16182,20 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>सिक्किम</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="252">
@@ -16193,20 +16205,20 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253">
@@ -16216,20 +16228,20 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="254">
@@ -16239,20 +16251,20 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="255">
@@ -16262,20 +16274,20 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>उत्तराखंड</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="256">
@@ -16285,20 +16297,20 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>उत्तराखंड</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="257">
@@ -16308,20 +16320,20 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="258">
@@ -16331,20 +16343,20 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="259">
@@ -16354,20 +16366,20 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="260">
@@ -16377,20 +16389,20 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="261">
@@ -16400,20 +16412,20 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>दिल्ली</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="262">
@@ -16423,20 +16435,20 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="263">
@@ -16446,20 +16458,20 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>लद्दाख</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="264">
@@ -16469,20 +16481,20 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="265">
@@ -16492,43 +16504,43 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Outside India</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>भारत से बाहर</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>Outside India</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>भारत से बाहर</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
     </row>
     <row r="267">
@@ -16538,20 +16550,20 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -16561,43 +16573,43 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="270">
@@ -16607,20 +16619,20 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -16630,20 +16642,20 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -16653,43 +16665,43 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274">
@@ -16699,20 +16711,20 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -16722,43 +16734,43 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -16768,20 +16780,20 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -16791,20 +16803,20 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -16814,20 +16826,20 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="280">
@@ -16837,20 +16849,20 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -16860,20 +16872,20 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282">
@@ -16883,20 +16895,20 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283">
@@ -16906,20 +16918,20 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
@@ -16929,43 +16941,43 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="286">
@@ -16975,20 +16987,20 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>No difficulty</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>कोई दिक़्क़त नहीं</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -16998,20 +17010,20 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Some difficulty</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>थोड़ी दिक़्क़त</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
@@ -17021,43 +17033,43 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>A lot of difficulty</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>बहुत दिक़्क़त</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>Cannot do it at all</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>बिलकुल नहीं कर पाते</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -17067,20 +17079,20 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Yes, through work</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>हाँ, काम की तरफ़ से</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -17090,20 +17102,20 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Only private or other insurance</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
@@ -17113,43 +17125,43 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>कोई नहीं</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="294">
@@ -17159,43 +17171,43 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>हाँ</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
@@ -17205,20 +17217,20 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -17228,19 +17240,42 @@
         </is>
       </c>
       <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
         <v>97</v>
       </c>
-      <c r="C297" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>पता नहीं</t>
         </is>
       </c>
-      <c r="E297" t="n">
+      <c r="E298" t="n">
         <v>97</v>
       </c>
     </row>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O259"/>
+  <dimension ref="A1:O258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8189,22 +8189,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>select_one distress</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>shock_worst</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Of those, which one was hardest for your household?</t>
+          <t>Thinking of whichever of those hit you hardest -- about how much did your household lose in earnings, or have to spend because of it? (Rs)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>इनमें से आपके घर के लिए सबसे मुश्किल कौन सा रहा?</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -8224,32 +8224,28 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>selected(${distress_event_last365d}, code)</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Because of that, about how much did your household lose in earnings, or have to spend? (Rs)</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
+          <t>और वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -8275,22 +8271,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>select_multiple coping</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>In which month did that happen?</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>वह किस महीने हुआ था?</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -8316,22 +8312,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>select_multiple coping</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -8341,14 +8337,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
@@ -8362,17 +8366,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -8411,17 +8415,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -8460,17 +8464,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -8509,17 +8513,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -8558,17 +8562,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8607,17 +8611,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8656,17 +8660,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8705,17 +8709,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8754,17 +8758,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8798,47 +8802,19 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>cope_restrict_adult_offseason_wk</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
@@ -8847,12 +8823,24 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr"/>
-      <c r="D217" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>grp_J</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Module J: Ropeway</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Module J: Ropeway</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
@@ -8863,27 +8851,31 @@
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>grp_J</t>
+          <t>intro_J</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Module J: Ropeway</t>
+          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Module J: Ropeway</t>
+          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8896,36 +8888,36 @@
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one stance</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>intro_J</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
@@ -8938,22 +8930,22 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>select_one stance</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -8975,31 +8967,15 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>select_one yn</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>trek_dependent</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
@@ -9012,12 +8988,24 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>grp_K</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr"/>
@@ -9028,27 +9016,31 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>grp_K</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -9061,36 +9053,36 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
@@ -9103,32 +9095,44 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr"/>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 3</t>
+        </is>
+      </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
@@ -9140,34 +9144,26 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
-        </is>
-      </c>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9175,7 +9171,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -9189,22 +9185,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -9216,7 +9212,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -9230,22 +9226,22 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -9271,22 +9267,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -9312,22 +9308,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -9358,17 +9354,17 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -9399,17 +9395,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9440,17 +9436,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -9462,7 +9458,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>${job_situation} &lt;= 7</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -9476,22 +9472,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -9503,7 +9499,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -9522,17 +9518,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -9544,7 +9540,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -9558,22 +9554,22 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -9583,11 +9579,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
-        </is>
-      </c>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
@@ -9599,31 +9591,15 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>first_job_ever</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Was your current work the first paid job you ever had?</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G237" t="inlineStr"/>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
@@ -9636,12 +9612,24 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr"/>
-      <c r="D238" t="inlineStr"/>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>grp_L</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Module L: Tasks and skills (short block)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Module L: Tasks and skills (short block)</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
@@ -9652,27 +9640,31 @@
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>grp_L</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9685,36 +9677,36 @@
       <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
+          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
@@ -9732,17 +9724,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
@@ -9769,17 +9761,17 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9806,17 +9798,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9843,17 +9835,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9880,17 +9872,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9917,17 +9909,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9954,17 +9946,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9991,17 +9983,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10028,17 +10020,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10065,17 +10057,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10102,17 +10094,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10134,22 +10126,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10159,7 +10151,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr"/>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
@@ -10176,17 +10172,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10217,17 +10213,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10258,17 +10254,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -10278,11 +10274,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10299,17 +10291,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>calc_at_work</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>In your work, do you work out prices or costs?</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -10331,31 +10323,15 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>select_one yn</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>calc_at_work</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>In your work, do you work out prices or costs?</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G257" t="inlineStr"/>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
@@ -10385,27 +10361,6 @@
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr"/>
-      <c r="O259" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O258"/>
+  <dimension ref="A1:O261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing and where you were living, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
+          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे और कहाँ रह रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
+          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -2932,17 +2932,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -3014,17 +3014,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3055,17 +3055,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3096,17 +3096,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3137,17 +3137,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3178,17 +3178,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3219,17 +3219,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3260,17 +3260,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -3342,17 +3342,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
+          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in? (If it is outside India, say so.)</t>
+          <t>Which state is your permanent home in?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3920,7 +3920,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>${origin} = 3</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -6492,22 +6496,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one landunit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>land_unit</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>How much CULTIVABLE land does your household own or cultivate, in acres? Do not count the land the house stands on. (0 if none)</t>
+          <t>In what unit do you count your land -- nali, bigha, acres or hectares?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6529,22 +6533,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6554,7 +6558,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>${land_unit} != 5</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -6571,17 +6579,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6608,17 +6616,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6645,17 +6653,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6682,17 +6690,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6719,17 +6727,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6751,32 +6759,32 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>${owns_work_equipment} = 1</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
@@ -6788,16 +6796,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr"/>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>work_equipment_detail</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>${owns_work_equipment} = 1</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -6809,24 +6833,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>grp_G</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
@@ -6837,31 +6849,27 @@
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>intro_G</t>
+          <t>grp_G</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Now about savings, loans, insurance and government schemes.</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -6874,36 +6882,36 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>intro_G</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>Now about savings, loans, insurance and government schemes.</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
+          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
@@ -6921,17 +6929,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6953,22 +6961,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>select_one credit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6978,11 +6986,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>${took_loan_12m} = 1</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -6994,22 +6998,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one credit</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7035,22 +7039,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one loanpurpose</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_purpose</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>What did you take it for?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
+          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7076,30 +7080,34 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>How much did you borrow in total? (Rs)</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>${pays_interest} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -7113,22 +7121,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7154,22 +7162,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>select_one collat</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7181,7 +7189,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>${loan_against_asset} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -7195,47 +7203,35 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>${pays_interest} = 1</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
@@ -7244,22 +7240,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -7269,22 +7265,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>${took_loan_12m} = 1</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
@@ -7293,22 +7281,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one collat</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7320,7 +7308,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>${land_cultivable_acres} &gt; 0</t>
+          <t>${loan_against_asset} = 1</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -7334,22 +7322,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>select_multiple govtscheme</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7360,9 +7348,21 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
@@ -7371,35 +7371,47 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>selected(${govt_schemes}, '9')</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
@@ -7408,22 +7420,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>select_one portable</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7435,7 +7447,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>selected(${govt_schemes}, '1')</t>
+          <t>${land_cultivable_acres} &gt; 0</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -7449,22 +7461,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_multiple govtscheme</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7475,9 +7487,21 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>not(selected(., '10') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
@@ -7486,32 +7510,32 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>selected(${govt_schemes}, '9')</t>
+        </is>
+      </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
@@ -7523,22 +7547,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one portable</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -7548,22 +7572,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>selected(${govt_schemes}, '1')</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
@@ -7572,15 +7588,31 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>smartphone_owned</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Do you own a smartphone?</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
@@ -7593,27 +7625,31 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>grp_H</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Module H: Health</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Module H: Health</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
@@ -7621,40 +7657,52 @@
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>intro_H</t>
+          <t>n_can_transact_online</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Now a few questions about health in your household. You may leave out any of these.</t>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
@@ -7663,31 +7711,15 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>select_one yn</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>morbidity_15d</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
@@ -7700,77 +7732,65 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>select_one coping</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>grp_H</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>${morbidity_15d} = 1</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>intro_H</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>Now a few questions about health in your household. You may leave out any of these.</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>${morbidity_15d} = 1</t>
-        </is>
-      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
@@ -7782,22 +7802,22 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>select_one wgdiff</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -7819,22 +7839,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one coping</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7844,7 +7864,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>${morbidity_15d} = 1</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -7856,22 +7880,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7881,7 +7905,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>${morbidity_15d} = 1</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
@@ -7893,22 +7921,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one wgdiff</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7935,17 +7963,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -7967,22 +7995,22 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -7992,11 +8020,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>${birth_last_5y} = 1</t>
-        </is>
-      </c>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -8008,22 +8032,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -8033,11 +8057,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>${birth_last_5y} = 1</t>
-        </is>
-      </c>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
@@ -8049,15 +8069,31 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>birth_last_5y</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>In the last five years, did any woman in your household give birth?</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
@@ -8070,65 +8106,77 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>grp_I</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Module I: Food security, shocks and coping</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Module I: Food security, shocks and coping</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>${birth_last_5y} = 1</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>intro_I</t>
+          <t>skilled_birth_attendant</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>${birth_last_5y} = 1</t>
+        </is>
+      </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
@@ -8140,47 +8188,19 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>select_multiple distress</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>distress_event_last365d</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
@@ -8189,77 +8209,65 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>grp_I</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Thinking of whichever of those hit you hardest -- about how much did your household lose in earnings, or have to spend because of it? (Rs)</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>इनमें से जो सबसे भारी पड़ा — उसकी वजह से आपके घर की कितनी कमाई गई, या कितना ख़र्च करना पड़ा? (रुपये)</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>intro_I</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>And in which month did that one happen?</t>
+          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>और वह किस महीने हुआ था?</t>
+          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
@@ -8271,22 +8279,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>select_multiple coping</t>
+          <t>select_multiple distress</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -8296,14 +8304,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
@@ -8317,17 +8333,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>Thinking of whichever of those hit you hardest -- what did it cost your household in all? Count both earnings lost and money spent because of it. (Rs)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उससे आपके घर का कुल कितना नुक़सान हुआ? कमाई का घाटा और ख़र्च, दोनों मिलाकर। (रुपये)</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -8337,22 +8353,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
@@ -8361,22 +8369,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>और वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -8386,22 +8394,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
@@ -8410,22 +8410,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple coping</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -8435,22 +8435,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
@@ -8464,17 +8456,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -8513,17 +8505,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -8562,17 +8554,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8611,17 +8603,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8660,17 +8652,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8709,17 +8701,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8758,17 +8750,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8802,19 +8794,47 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr"/>
-      <c r="D216" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>cope_reduce_portion_offseason_wk</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
@@ -8823,68 +8843,96 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>grp_J</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Module J: Ropeway</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Module J: Ropeway</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H217" t="inlineStr"/>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>intro_J</t>
+          <t>cope_restrict_adult_offseason_wk</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
@@ -8893,31 +8941,15 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>select_one stance</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>ropeway_stance</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G219" t="inlineStr"/>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
@@ -8930,31 +8962,27 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>grp_J</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G220" t="inlineStr"/>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
@@ -8962,17 +8990,33 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>intro_J</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr"/>
@@ -8988,27 +9032,31 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>select_one stance</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>grp_K</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
@@ -9016,36 +9064,36 @@
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>trek_dependent</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
@@ -9058,31 +9106,15 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>job_situation</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
@@ -9095,85 +9127,65 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>grp_K</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
-        </is>
-      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
@@ -9185,22 +9197,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -9210,11 +9222,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
@@ -9226,26 +9234,34 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9267,22 +9283,22 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="E229" t="inlineStr"/>
@@ -9294,7 +9310,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -9308,22 +9324,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -9349,22 +9365,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -9376,7 +9392,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -9390,22 +9406,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9417,7 +9433,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -9436,17 +9452,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -9458,7 +9474,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -9472,22 +9488,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -9499,7 +9515,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -9513,22 +9529,22 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -9540,7 +9556,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -9559,17 +9575,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -9579,7 +9595,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>${job_situation} &lt;= 7</t>
+        </is>
+      </c>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
@@ -9591,16 +9611,36 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>more_hours_day</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>On a working day, how many MORE hours would you like to work?</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
@@ -9612,64 +9652,72 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>grp_L</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Module L: Tasks and skills (short block)</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+        </is>
+      </c>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>first_job_ever</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
+          <t>Was your current work the first paid job you ever had?</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
@@ -9682,31 +9730,15 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>select_one task3</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>tk_load</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Do you load, unload, stack or count goods? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
@@ -9719,31 +9751,27 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>grp_L</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Do you drive a motor vehicle? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
@@ -9751,36 +9779,36 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Do you operate an engine or machine? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
@@ -9798,17 +9826,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Do you do electrical or wiring work? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
@@ -9835,17 +9863,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Do you check equipment or the route for safety? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9872,17 +9900,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Do you sell goods or services? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9909,17 +9937,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Do you handle cash and payments? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9946,17 +9974,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Do you cook or prepare food or drink? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -9983,17 +10011,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Do you serve guests or customers? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10020,17 +10048,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Do you clean rooms or public areas? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10057,17 +10085,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Do you guide or explain things to visitors? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10094,17 +10122,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Do you coordinate work by phone, radio or signals? (1 regularly in my main Yatra work; 2 not in my main work, but done before elsewhere; 3 never)</t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10126,22 +10154,22 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10151,11 +10179,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
@@ -10167,22 +10191,22 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10192,11 +10216,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
@@ -10208,22 +10228,22 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10233,11 +10253,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
@@ -10254,17 +10270,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -10274,7 +10290,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10291,17 +10311,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -10311,7 +10331,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
@@ -10323,16 +10347,36 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>drove_heavy</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>... a truck or bus?</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>...ट्रक या बस?</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
@@ -10344,15 +10388,31 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>read_at_work</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
@@ -10361,6 +10421,85 @@
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>calc_at_work</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>In your work, do you work out prices or costs?</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10373,7 +10512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10414,12 +10553,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Own house here</t>
+          <t>At my own usual home (I live here)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>यहाँ अपना घर है</t>
+          <t>अपने ही घर में (मैं यहीं रहता हूँ)</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13304,7 +13443,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -13312,12 +13451,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Currently married</t>
+          <t>Nali</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>शादीशुदा</t>
+          <t>नाली</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -13327,7 +13466,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -13335,12 +13474,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Never married</t>
+          <t>Bigha</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>शादी नहीं हुई</t>
+          <t>बीघा</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -13350,7 +13489,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -13358,12 +13497,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Widowed/divorced/separated</t>
+          <t>Acres</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>विधवा/विधुर या अलग</t>
+          <t>एकड़</t>
         </is>
       </c>
       <c r="E130" t="n">
@@ -13373,599 +13512,599 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Hectares</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>जनवरी</t>
+          <t>हेक्टेयर</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>No land</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>फ़रवरी</t>
+          <t>ज़मीन नहीं है</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>Medical or hospital costs</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>मार्च</t>
+          <t>इलाज या अस्पताल का ख़र्च</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Buying an animal, vehicle or equipment for work</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>अप्रैल</t>
+          <t>काम के लिए जानवर, गाड़ी या औज़ार ख़रीदने</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>Shop stock or business</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>मई</t>
+          <t>दुकान का सामान या धंधा</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Food or daily household needs</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>जून</t>
+          <t>खाने या घर की रोज़ की ज़रूरत</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>A wedding, funeral or ceremony</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>जुलाई</t>
+          <t>शादी, मृत्यु-भोज या कोई समारोह</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>House building or repair</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>अगस्त</t>
+          <t>मकान बनाने या मरम्मत</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>सितंबर</t>
+          <t>पढ़ाई</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Repaying another loan</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>अक्टूबर</t>
+          <t>पुराना क़र्ज़ चुकाने</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>Something else</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>नवंबर</t>
+          <t>कोई और काम</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Currently married</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>दिसंबर</t>
+          <t>शादीशुदा</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Garhwali</t>
+          <t>Never married</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>गढ़वाली</t>
+          <t>शादी नहीं हुई</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Kumaoni</t>
+          <t>Widowed/divorced/separated</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>कुमाऊँनी</t>
+          <t>विधवा/विधुर या अलग</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>हिंदी</t>
+          <t>जनवरी</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nepali</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>नेपाली</t>
+          <t>फ़रवरी</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bhojpuri</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>भोजपुरी</t>
+          <t>मार्च</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Assamese</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>असमिया</t>
+          <t>अप्रैल</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>बांग्ला</t>
+          <t>मई</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bodo</t>
+          <t>June</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>बोडो</t>
+          <t>जून</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dogri</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>डोगरी</t>
+          <t>जुलाई</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>August</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>गुजराती</t>
+          <t>अगस्त</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>कन्नड़</t>
+          <t>सितंबर</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kashmiri</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>कश्मीरी</t>
+          <t>अक्टूबर</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Konkani</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>कोंकणी</t>
+          <t>नवंबर</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Maithili</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>मैथिली</t>
+          <t>दिसंबर</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157">
@@ -13975,20 +14114,20 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Garhwali</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>मलयालम</t>
+          <t>गढ़वाली</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -13998,20 +14137,20 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Manipuri (Meitei)</t>
+          <t>Kumaoni</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>मणिपुरी (मैतेई)</t>
+          <t>कुमाऊँनी</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -14021,20 +14160,20 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Marathi</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>मराठी</t>
+          <t>हिंदी</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160">
@@ -14044,20 +14183,20 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Odia</t>
+          <t>Nepali</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ओड़िया</t>
+          <t>नेपाली</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
@@ -14067,20 +14206,20 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Punjabi</t>
+          <t>Bhojpuri</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>पंजाबी</t>
+          <t>भोजपुरी</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
@@ -14090,20 +14229,20 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Assamese</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>संस्कृत</t>
+          <t>असमिया</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
@@ -14113,20 +14252,20 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Santali</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>संताली</t>
+          <t>बांग्ला</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -14136,20 +14275,20 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Sindhi</t>
+          <t>Bodo</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>सिंधी</t>
+          <t>बोडो</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -14159,20 +14298,20 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Dogri</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>तमिल</t>
+          <t>डोगरी</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="166">
@@ -14182,20 +14321,20 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>तेलुगु</t>
+          <t>गुजराती</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167">
@@ -14205,20 +14344,20 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>उर्दू</t>
+          <t>कन्नड़</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168">
@@ -14228,20 +14367,20 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Other Indian language</t>
+          <t>Kashmiri</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>कोई और भारतीय भाषा</t>
+          <t>कश्मीरी</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
@@ -14251,348 +14390,348 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Other / foreign language</t>
+          <t>Konkani</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>कोई और / विदेशी भाषा</t>
+          <t>कोंकणी</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>97</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Pony/mule worker (works the animals, does not own them)</t>
+          <t>Maithili</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
+          <t>मैथिली</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Pony/mule owner (owns the animals)</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर का मालिक</t>
+          <t>मलयालम</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
+          <t>Manipuri (Meitei)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
+          <t>मणिपुरी (मैतेई)</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
+          <t>मराठी</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
+          <t>Odia</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
+          <t>ओड़िया</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
+          <t>Punjabi</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
+          <t>पंजाबी</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
+          <t>संस्कृत</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Shop OWNER (goods, not prepared food)</t>
+          <t>Santali</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
+          <t>संताली</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hotel / lodge WORKER</t>
+          <t>Sindhi</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>होटल / लॉज में काम</t>
+          <t>सिंधी</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hotel / lodge OWNER</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>होटल / लॉज का मालिक</t>
+          <t>तमिल</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Driver (any motor vehicle)</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ड्राइवर (कोई भी गाड़ी)</t>
+          <t>तेलुगु</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Urdu</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>गाइड</t>
+          <t>उर्दू</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Wage labourer (construction, loading, odd jobs)</t>
+          <t>Other Indian language</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
+          <t>कोई और भारतीय भाषा</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other / foreign language</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>कोई और / विदेशी भाषा</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -14600,12 +14739,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Local (same district)</t>
+          <t>Pony/mule worker (works the animals, does not own them)</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>यहीं का (इसी ज़िले का)</t>
+          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -14615,7 +14754,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -14623,12 +14762,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Other Uttarakhand district</t>
+          <t>Pony/mule owner (owns the animals)</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>उत्तराखंड का दूसरा ज़िला</t>
+          <t>घोड़े/खच्चर का मालिक</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -14638,7 +14777,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -14646,12 +14785,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Other Indian state</t>
+          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>भारत का दूसरा राज्य</t>
+          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -14661,7 +14800,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -14669,12 +14808,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>नेपाल</t>
+          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -14684,674 +14823,674 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Yes, employer deducts it</t>
+          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>हाँ, मालिक काटता है</t>
+          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Yes, contributes voluntarily</t>
+          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>हाँ, अपनी मर्ज़ी से</t>
+          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>pension</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Yes, can draw it here</t>
+          <t>Shop OWNER (goods, not prepared food)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>हाँ, यहाँ मिल जाता है</t>
+          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>No, only at the home place</t>
+          <t>Hotel / lodge WORKER</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
+          <t>होटल / लॉज में काम</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Has never tried</t>
+          <t>Hotel / lodge OWNER</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>कभी कोशिश नहीं की</t>
+          <t>होटल / लॉज का मालिक</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>portable</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>97</v>
+        <v>11</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Does not know</t>
+          <t>Driver (any motor vehicle)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>ड्राइवर (कोई भी गाड़ी)</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>97</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Better income</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ज़्यादा कमाई</t>
+          <t>गाइड</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Lost the previous work</t>
+          <t>Wage labourer (construction, loading, odd jobs)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>पहला काम छूट गया</t>
+          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Work ended with the season</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>मौसम के साथ काम ख़त्म हो गया</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Family reasons</t>
+          <t>Local (same district)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>घर की वजह से</t>
+          <t>यहीं का (इसी ज़िले का)</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Health or injury</t>
+          <t>Other Uttarakhand district</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>सेहत या चोट</t>
+          <t>उत्तराखंड का दूसरा ज़िला</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other Indian state</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>कोई और वजह</t>
+          <t>भारत का दूसरा राज्य</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Month by month</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>हर महीने का अलग-अलग</t>
+          <t>नेपाल</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>One total for the whole year</t>
+          <t>Yes, employer deducts it</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>पूरे साल का एक जोड़</t>
+          <t>हाँ, मालिक काटता है</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>A family member already working here</t>
+          <t>Yes, contributes voluntarily</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>यहाँ पहले से काम कर रहा घरवाला</t>
+          <t>हाँ, अपनी मर्ज़ी से</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>pension</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>A friend or someone from the village</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>दोस्त या गाँव का कोई आदमी</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>A thekedar or contractor I now work for</t>
+          <t>Yes, can draw it here</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
+          <t>हाँ, यहाँ मिल जाता है</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>An agent or middleman who placed me (usually for a fee)</t>
+          <t>No, only at the home place</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
+          <t>नहीं, सिर्फ़ अपने घर वाली जगह पर</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>No one; I found it myself</t>
+          <t>Has never tried</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>कोई नहीं, ख़ुद ढूँढा</t>
+          <t>कभी कोशिश नहीं की</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>portable</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>The employer called me directly</t>
+          <t>Does not know</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>मालिक ने सीधे बुलाया</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Someone else</t>
+          <t>Better income</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>ज़्यादा कमाई</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>From my own phone (UPI or net banking)</t>
+          <t>Lost the previous work</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
+          <t>पहला काम छूट गया</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>In person at a bank branch or bank mitra / CSP</t>
+          <t>Work ended with the season</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
+          <t>मौसम के साथ काम ख़त्म हो गया</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Money order or post office</t>
+          <t>Family reasons</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>मनीऑर्डर या डाकघर से</t>
+          <t>घर की वजह से</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sent with someone going home</t>
+          <t>Health or injury</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>घर जा रहे किसी के हाथ</t>
+          <t>सेहत या चोट</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Carried it myself</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>ख़ुद लेकर गए</t>
+          <t>कोई और वजह</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Through an agent or middleman</t>
+          <t>Month by month</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
+          <t>हर महीने का अलग-अलग</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>recall</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>One total for the whole year</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>कोई और तरीक़ा</t>
+          <t>पूरे साल का एक जोड़</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -15359,12 +15498,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Thatch/wood/mud</t>
+          <t>A family member already working here</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>फूस/लकड़ी/मिट्टी</t>
+          <t>यहाँ पहले से काम कर रहा घरवाला</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -15374,7 +15513,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -15382,12 +15521,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tin/GI sheet</t>
+          <t>A friend or someone from the village</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>टीन/चादर</t>
+          <t>दोस्त या गाँव का कोई आदमी</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -15397,7 +15536,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -15405,12 +15544,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Concrete/RCC</t>
+          <t>A thekedar or contractor I now work for</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>छत (कंक्रीट/RCC)</t>
+          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -15420,99 +15559,99 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Village (rural)</t>
+          <t>An agent or middleman who placed me (usually for a fee)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>गाँव में</t>
+          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Town or city (urban)</t>
+          <t>No one; I found it myself</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>शहर या क़स्बे में</t>
+          <t>कोई नहीं, ख़ुद ढूँढा</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>The employer called me directly</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>मालिक ने सीधे बुलाया</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Someone else</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -15520,12 +15659,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Kedarnath (Gaurikund to Kedarnath)</t>
+          <t>From my own phone (UPI or net banking)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
+          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -15535,7 +15674,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -15543,12 +15682,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
+          <t>In person at a bank branch or bank mitra / CSP</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
+          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
         </is>
       </c>
       <c r="E225" t="n">
@@ -15558,415 +15697,415 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Money order or post office</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>समर्थन में</t>
+          <t>मनीऑर्डर या डाकघर से</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Sent with someone going home</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>तटस्थ</t>
+          <t>घर जा रहे किसी के हाथ</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Carried it myself</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>विरोध में</t>
+          <t>ख़ुद लेकर गए</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Through an agent or middleman</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>कोई और तरीक़ा</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Thatch/wood/mud</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>फूस/लकड़ी/मिट्टी</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Tin/GI sheet</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>टीन/चादर</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Concrete/RCC</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>छत (कंक्रीट/RCC)</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Village (rural)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>गाँव में</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Town or city (urban)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>शहर या क़स्बे में</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Kedarnath (Gaurikund to Kedarnath)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>समर्थन में</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>तटस्थ</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>विरोध में</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>14</v>
+        <v>98</v>
       </c>
     </row>
     <row r="244">
@@ -15976,20 +16115,20 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -15999,20 +16138,20 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -16022,20 +16161,20 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -16045,20 +16184,20 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
@@ -16068,20 +16207,20 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
@@ -16091,20 +16230,20 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>गोवा</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250">
@@ -16114,20 +16253,20 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="251">
@@ -16137,20 +16276,20 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>हरियाणा</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="252">
@@ -16160,20 +16299,20 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="253">
@@ -16183,20 +16322,20 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>झारखंड</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254">
@@ -16206,20 +16345,20 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255">
@@ -16229,20 +16368,20 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="256">
@@ -16252,20 +16391,20 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Uttarakhand</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>उत्तराखंड</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="257">
@@ -16275,20 +16414,20 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="258">
@@ -16298,20 +16437,20 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>मणिपुर</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="259">
@@ -16321,20 +16460,20 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>मेघालय</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="260">
@@ -16344,20 +16483,20 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="261">
@@ -16367,20 +16506,20 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>नागालैंड</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="262">
@@ -16390,20 +16529,20 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263">
@@ -16413,20 +16552,20 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264">
@@ -16436,20 +16575,20 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="265">
@@ -16459,20 +16598,20 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>सिक्किम</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="266">
@@ -16482,755 +16621,1077 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Outside India</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>भारत से बाहर</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Uttarakhand</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>उत्तराखंड</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>दिल्ली</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>लद्दाख</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Outside India</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>भारत से बाहर</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Yes, through work</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>हाँ, काम की तरफ़ से</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Only private or other insurance</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>कोई नहीं</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>workins</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>yn</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>yndk</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>8</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>River, stream, pond or canal</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>नदी, गाड़, तालाब या नहर</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>9</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Tanker truck or cart with drum</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>wgdiff</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>No difficulty</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>कोई दिक़्क़त नहीं</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>wgdiff</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>2</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Some difficulty</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>थोड़ी दिक़्क़त</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>wgdiff</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>3</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>A lot of difficulty</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>बहुत दिक़्क़त</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>wgdiff</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>4</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Cannot do it at all</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>बिलकुल नहीं कर पाते</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Yes, through work</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>हाँ, काम की तरफ़ से</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>2</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Only private or other insurance</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>3</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>कोई नहीं</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>workins</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>4</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Don't know</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>पता नहीं</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>yn</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
           <t>yndk</t>
         </is>
       </c>
-      <c r="B298" t="n">
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>नहीं</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>हाँ</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>yndk</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
         <v>97</v>
       </c>
-      <c r="C298" t="inlineStr">
+      <c r="C312" t="inlineStr">
         <is>
           <t>Don't know</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>पता नहीं</t>
         </is>
       </c>
-      <c r="E298" t="n">
+      <c r="E312" t="n">
         <v>97</v>
       </c>
     </row>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O261"/>
+  <dimension ref="A1:O262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,32 +747,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>main_survey</t>
+          <t>form_build</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Main survey</t>
+          <t>Recorded automatically.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Main survey</t>
+          <t>Recorded automatically.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>${consent} = 1</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -789,54 +789,54 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>grp_A</t>
+          <t>main_survey</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Module A: Respondent and household</t>
+          <t>Main survey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Module A: Respondent and household</t>
+          <t>Main survey</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>${consent} = 1</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>intro_A</t>
+          <t>grp_A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>First, a few things about you and the people who live in your household.</t>
+          <t>Module A: Respondent and household</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>सबसे पहले आपके बारे में और आपके घर में रहने वाले लोगों के बारे में कुछ बातें पूछूँगा।</t>
+          <t>Module A: Respondent and household</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -849,52 +849,40 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>intro_A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How old are you? (completed years)</t>
+          <t>First, a few things about you and the people who live in your household.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>आपकी उम्र कितनी है? (पूरे साल)</t>
+          <t>सबसे पहले आपके बारे में और आपके घर में रहने वाले लोगों के बारे में कुछ बातें पूछूँगा।</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>. &gt;= 10 and . &lt;= 90</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Age must be between 10 and 90.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>उम्र 10 से 90 के बीच होनी चाहिए।</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -903,22 +891,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one sex</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Record sex; ask if unsure: are you male or female?</t>
+          <t>How old are you? (completed years)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>आप पुरुष हैं या महिला?</t>
+          <t>आपकी उम्र कितनी है? (पूरे साल)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -929,9 +917,21 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>. &gt;= 10 and . &lt;= 90</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Age must be between 10 and 90.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>उम्र 10 से 90 के बीच होनी चाहिए।</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -940,22 +940,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one hohrel</t>
+          <t>select_one sex</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hoh_relation</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Who is the head of your household -- is it you, or someone else? If someone else, how are they related to you?</t>
+          <t>Record sex; ask if unsure: are you male or female?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>आपके घर का मुखिया कौन है — आप खुद, या कोई और? अगर कोई और है, तो वे आपके क्या लगते हैं?</t>
+          <t>आप पुरुष हैं या महिला?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -977,22 +977,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one nativelang</t>
+          <t>select_one hohrel</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>native_language</t>
+          <t>hoh_relation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is your native language, the language you first learned at home?</t>
+          <t>Who is the head of your household -- is it you, or someone else? If someone else, how are they related to you?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>आपकी मातृभाषा कौन सी है — वह भाषा जो आपने घर में सबसे पहले सीखी?</t>
+          <t>आपके घर का मुखिया कौन है — आप खुद, या कोई और? अगर कोई और है, तो वे आपके क्या लगते हैं?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1014,22 +1014,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one nativelang</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>native_language_other</t>
+          <t>native_language</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Which language is it? Write down exactly what they say.</t>
+          <t>What is your native language, the language you first learned at home?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>वह कौन सी भाषा है? जैसा वे कहें वैसा ही लिख लीजिए।</t>
+          <t>आपकी मातृभाषा कौन सी है — वह भाषा जो आपने घर में सबसे पहले सीखी?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1039,11 +1039,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>${native_language} = 96 or ${native_language} = 97</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1055,22 +1051,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one marital</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>marital_status</t>
+          <t>native_language_other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Are you currently married, never married, or widowed/divorced/separated?</t>
+          <t>Which language is it? Write down exactly what they say.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>क्या आपकी शादी हुई है, नहीं हुई है, या आप विधवा/विधुर या अलग हैं?</t>
+          <t>वह कौन सी भाषा है? जैसा वे कहें वैसा ही लिख लीजिए।</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1080,7 +1076,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>${native_language} = 96 or ${native_language} = 97</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1092,22 +1092,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one marital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>knows_years_schooling</t>
+          <t>marital_status</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you know exactly how many years of schooling you completed, counting from class 1?</t>
+          <t>Are you currently married, never married, or widowed/divorced/separated?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>क्या आपको ठीक-ठीक याद है कि आपने कितने साल पढ़ाई की, कक्षा 1 से गिनकर?</t>
+          <t>क्या आपकी शादी हुई है, नहीं हुई है, या आप विधवा/विधुर या अलग हैं?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1129,22 +1129,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>years_schooling</t>
+          <t>knows_years_schooling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How many years of schooling did you complete in total? (0 if none)</t>
+          <t>Do you know exactly how many years of schooling you completed, counting from class 1?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>आपने कुल कितने साल पढ़ाई की? (अगर बिल्कुल नहीं पढ़े तो 0)</t>
+          <t>क्या आपको ठीक-ठीक याद है कि आपने कितने साल पढ़ाई की, कक्षा 1 से गिनकर?</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1154,11 +1154,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>${knows_years_schooling} = 1</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1170,22 +1166,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one edu2</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>education_level_cat</t>
+          <t>years_schooling</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Which is closest: no formal education; some schooling but did not finish primary; finished primary but not secondary; or finished secondary or higher?</t>
+          <t>How many years of schooling did you complete in total? (0 if none)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>इनमें से कौन सा सबसे नज़दीक है: बिल्कुल नहीं पढ़े; थोड़ा पढ़े पर प्राइमरी पूरी नहीं की; प्राइमरी पूरी की पर दसवीं नहीं; या दसवीं या उससे ज़्यादा?</t>
+          <t>आपने कुल कितने साल पढ़ाई की? (अगर बिल्कुल नहीं पढ़े तो 0)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1197,12 +1193,24 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>${knows_years_schooling} = 0</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>${knows_years_schooling} = 1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${age} - 4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Years of schooling cannot be more than the respondent's age allows.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Years of schooling cannot be more than the respondent's age allows.</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -1211,22 +1219,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one edu2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hhsize</t>
+          <t>education_level_cat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How many members live in your household, including you?</t>
+          <t>Which is closest: no formal education; some schooling but did not finish primary; finished primary but not secondary; or finished secondary or higher?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>आपके घर में आपको मिलाकर कुल कितने लोग रहते हैं?</t>
+          <t>इनमें से कौन सा सबसे नज़दीक है: बिल्कुल नहीं पढ़े; थोड़ा पढ़े पर प्राइमरी पूरी नहीं की; प्राइमरी पूरी की पर दसवीं नहीं; या दसवीं या उससे ज़्यादा?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1236,22 +1244,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Household size must be between 1 and 30.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>घर के लोग 1 से 30 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>${knows_years_schooling} = 0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -1260,22 +1260,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>any_member_6yr_schooling</t>
+          <t>hhsize</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Counting everyone in your household aged 10 or above, has at least one of them finished six years of schooling or more?</t>
+          <t>How many members live in your household, including you?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>आपके घर में 10 साल या उससे बड़े सभी लोगों में से, क्या कम से कम एक ने छह साल या उससे ज़्यादा पढ़ाई पूरी की है?</t>
+          <t>आपके घर में आपको मिलाकर कुल कितने लोग रहते हैं?</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1286,9 +1286,21 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Household size must be between 1 and 30.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>घर के लोग 1 से 30 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1297,22 +1309,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one famstruct</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>family_structure</t>
+          <t>any_member_6yr_schooling</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Is your family nuclear -- just you, your spouse and unmarried children -- or joint, living with parents, married siblings or other extended family? (Say single-member if you live alone.)</t>
+          <t>Counting everyone in your household aged 10 or above, has at least one of them finished six years of schooling or more?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>आपका परिवार छोटा है — सिर्फ़ आप, पति/पत्नी और बिन ब्याहे बच्चे — या बड़ा, यानी माँ-बाप, भाई-भाभी या और रिश्तेदार साथ रहते हैं? (अगर अकेले रहते हैं तो वह बताइए।)</t>
+          <t>आपके घर में 10 साल या उससे बड़े सभी लोगों में से, क्या कम से कम एक ने छह साल या उससे ज़्यादा पढ़ाई पूरी की है?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1334,22 +1346,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one famstruct</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>n_earners</t>
+          <t>family_structure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How many of them, including you, earn money?</t>
+          <t>Is your family nuclear -- just you, your spouse and unmarried children -- or joint, living with parents, married siblings or other extended family? (Say single-member if you live alone.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>इनमें से कितने लोग, आपको मिलाकर, पैसा कमाते हैं?</t>
+          <t>आपका परिवार छोटा है — सिर्फ़ आप, पति/पत्नी और बिन ब्याहे बच्चे — या बड़ा, यानी माँ-बाप, भाई-भाभी या और रिश्तेदार साथ रहते हैं? (अगर अकेले रहते हैं तो वह बताइए।)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1360,21 +1372,9 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -1383,22 +1383,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>main_income_earner</t>
+          <t>n_earners</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Among those who earn money, are you the main income earner in your household?</t>
+          <t>How many of them, including you, earn money?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>जो लोग कमाते हैं, उनमें सबसे ज़्यादा कमाने वाले आप ही हैं?</t>
+          <t>इनमें से कितने लोग, आपको मिलाकर, पैसा कमाते हैं?</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1408,14 +1408,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>${n_earners} &gt; 1</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -1424,22 +1432,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>n_children_u15</t>
+          <t>main_income_earner</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How many of them are children under 15?</t>
+          <t>Among those who earn money, are you the main income earner in your household?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>इनमें 15 साल से छोटे बच्चे कितने हैं?</t>
+          <t>जो लोग कमाते हैं, उनमें सबसे ज़्यादा कमाने वाले आप ही हैं?</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1449,22 +1457,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Cannot be more than the household size minus the respondent.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>${n_earners} &gt; 1</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>n_children_6_14</t>
+          <t>n_children_u15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How many of them are children aged 6 to 14?</t>
+          <t>How many of them are children under 15?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>इनमें 6 से 14 साल के बच्चे कितने हैं?</t>
+          <t>इनमें 15 साल से छोटे बच्चे कितने हैं?</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1501,17 +1501,17 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
+          <t>. &gt;= 0 and . &lt;= ${hhsize} - 1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Cannot be more than the number of children under 15.</t>
+          <t>Cannot be more than the household size minus the respondent.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
+          <t>घर के लोगों में से आपको छोड़कर, उससे ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>n_children_out_school</t>
+          <t>n_children_6_14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How many of these children do not go to school now?</t>
+          <t>How many of them are children aged 6 to 14?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>इन बच्चों में कितने अभी स्कूल नहीं जाते?</t>
+          <t>इनमें 6 से 14 साल के बच्चे कितने हैं?</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1547,24 +1547,20 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>${n_children_6_14} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
+          <t>. &gt;= 0 and . &lt;= ${n_children_u15}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Cannot be more than the number of children aged 6 to 14.</t>
+          <t>Cannot be more than the number of children under 15.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
+          <t>15 साल से छोटे बच्चों से ज़्यादा नहीं हो सकता।</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -1575,19 +1571,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>n_children_out_school</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>How many of these children do not go to school now?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>इन बच्चों में कितने अभी स्कूल नहीं जाते?</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>${n_children_6_14} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${n_children_6_14}</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of children aged 6 to 14.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>6 से 14 साल के बच्चों से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1596,24 +1624,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>grp_B</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Module B: Work and work history</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Module B: Work and work history</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
@@ -1624,31 +1640,27 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>intro_B</t>
+          <t>grp_B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Now about the work you do here on the Yatra route, and the work you did before this.</t>
+          <t>Module B: Work and work history</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>अब उस काम के बारे में जो आप यहाँ यात्रा मार्ग पर करते हैं, और उससे पहले जो काम करते थे।</t>
+          <t>Module B: Work and work history</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1661,36 +1673,36 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one occ</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>occupation</t>
+          <t>intro_B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>What is your main work during the Yatra season? Ask what they do and code the closest group; do not read the list aloud unless needed.</t>
+          <t>Now about the work you do here on the Yatra route, and the work you did before this.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आपका मुख्य काम क्या है?</t>
+          <t>अब उस काम के बारे में जो आप यहाँ यात्रा मार्ग पर करते हैं, और उससे पहले जो काम करते थे।</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1703,22 +1715,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one occ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>occupation_detail</t>
+          <t>occupation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>In your own words, what exactly is your main work here? Write down what they say -- what they actually do, and who for. Do not tick a box for this one.</t>
+          <t>What is your main work during the Yatra season? Ask what they do and code the closest group; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>अपने शब्दों में बताइए, यहाँ आपका मुख्य काम ठीक-ठीक क्या है? आप करते क्या हैं, और किसके लिए?</t>
+          <t>यात्रा के मौसम में आपका मुख्य काम क्या है?</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1740,22 +1752,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one emptype</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>employment_type</t>
+          <t>occupation_detail</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>In this main work, are you: working on your own account without hired workers; running a business with hired workers; a regular monthly wage-earner; or a daily/casual wage-earner?</t>
+          <t>In your own words, what exactly is your main work here? Write down what they say -- what they actually do, and who for. Do not tick a box for this one.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>इस काम में आप क्या हैं: अपना काम खुद करते हैं और कोई नौकर नहीं रखते; अपना काम है और दूसरों को काम पर रखते हैं; महीने की पक्की तनख़्वाह पाते हैं; या दिहाड़ी पर काम करते हैं?</t>
+          <t>अपने शब्दों में बताइए, यहाँ आपका मुख्य काम ठीक-ठीक क्या है? आप करते क्या हैं, और किसके लिए?</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1777,22 +1789,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one emptype</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>n_other_activities</t>
+          <t>employment_type</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
+          <t>In this main work, are you: working on your own account without hired workers; running a business with hired workers; a regular monthly wage-earner; or a daily/casual wage-earner?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
+          <t>इस काम में आप क्या हैं: अपना काम खुद करते हैं और कोई नौकर नहीं रखते; अपना काम है और दूसरों को काम पर रखते हैं; महीने की पक्की तनख़्वाह पाते हैं; या दिहाड़ी पर काम करते हैं?</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -1803,21 +1815,9 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 6.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0 से 6 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
@@ -1826,22 +1826,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_multiple occ</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>other_activity_types</t>
+          <t>n_other_activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
+          <t>Besides your main work, how many OTHER paid activities or income-generating activities do you have? (0 if none. For example, a shop owner who also rents out a pony and drives in the off-season would say 2.)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
+          <t>अपने मुख्य काम के अलावा, आप और कितने काम करते हैं जिनसे पैसा आता है? (अगर कोई नहीं तो 0। जैसे, दुकान वाला जो घोड़ा भी किराये पर देता है और जाड़ों में गाड़ी चलाता है, वह 2 बताएगा।)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -1851,42 +1851,46 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>${n_other_activities} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 6.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0 से 6 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>code != ${occupation}</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple occ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>other_activity_income_pm</t>
+          <t>other_activity_types</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
+          <t>Which ones are they? Check every one that applies. Ask and code the closest group for each; do not read the list aloud unless needed.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
+          <t>वे कौन-कौन से काम हैं? जो-जो लागू हो, सब बताइए।</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1906,7 +1910,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>code != ${occupation}</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1917,17 +1925,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>years_in_yatra_work</t>
+          <t>other_activity_income_pm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>How many Yatra seasons have you worked in this kind of work?</t>
+          <t>Taking all of that other work together, about how much do you usually earn from it in a month? (Rs)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>आप कितने यात्रा सीज़न से यह काम कर रहे हैं?</t>
+          <t>वह सारा दूसरा काम मिलाकर, महीने में लगभग कितना कमा लेते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -1937,10 +1945,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>${n_other_activities} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -1954,17 +1978,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>hours_day_yatra</t>
+          <t>years_in_yatra_work</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
+          <t>How many Yatra seasons have you worked in this kind of work?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
+          <t>आप कितने यात्रा सीज़न से यह काम कर रहे हैं?</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1977,17 +2001,17 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
+          <t>. &gt;= 0 and . &lt;= ${age} - 10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Hours a day must be between 1 and 18.</t>
+          <t>More Yatra seasons than the respondent's age allows.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
+          <t>More Yatra seasons than the respondent's age allows.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2003,17 +2027,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>days_week_yatra</t>
+          <t>hours_day_yatra</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>How many days a week do you usually work in the season?</t>
+          <t>In the Yatra season, on a normal working day, how many hours do you work in total, across all your work?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>यात्रा के मौसम में, आम दिन में आप कुल कितने घंटे काम करते हैं, सारे कामों को मिलाकर?</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2026,17 +2050,17 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2047,22 +2071,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>prev_occ_change</t>
+          <t>days_week_yatra</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>In the last ten years, did you change your main kind of work?</t>
+          <t>How many days a week do you usually work in the season?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
+          <t>सीज़न में आप हफ़्ते में कितने दिन काम करते हैं?</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2073,9 +2097,21 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -2084,22 +2120,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>prev_occ</t>
+          <t>prev_occ_change</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
+          <t>In the last ten years, did you change your main kind of work?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>इससे पहले आपका मुख्य काम क्या था?</t>
+          <t>पिछले दस साल में, क्या आपने अपना मुख्य काम बदला?</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2109,11 +2145,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2130,17 +2162,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>target_occ</t>
+          <t>prev_occ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
+          <t>What was your previous main work? Write down exactly what they say, in their words -- do not pick from a list.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
+          <t>इससे पहले आपका मुख्य काम क्या था?</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2150,7 +2182,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2162,22 +2198,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one prevreason</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>prev_occ_reason</t>
+          <t>target_occ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>What was the main reason you changed?</t>
+          <t>If you could not continue this work at all, what work would you move to instead? Write down exactly what they say, in their words -- do not pick from a list, and do not prompt with examples.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>काम बदलने की मुख्य वजह क्या थी?</t>
+          <t>अगर यह काम बिल्कुल बंद हो जाए, तो आप कौन सा काम करेंगे?</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2187,11 +2223,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>${prev_occ_change} = 1</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2203,22 +2235,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one prevreason</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>training_received</t>
+          <t>prev_occ_reason</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+          <t>What was the main reason you changed?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+          <t>काम बदलने की मुख्य वजह क्या थी?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2228,7 +2260,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>${prev_occ_change} = 1</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2240,15 +2276,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>training_received</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Apart from school and college, have you ever completed any training course or apprenticeship?</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>स्कूल और कॉलेज की पढ़ाई छोड़कर, क्या आपने कभी कोई ट्रेनिंग या सीखने का कोर्स पूरा किया है?</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
@@ -2261,24 +2313,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>grp_C</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Module C: Monthly calendar of work and income; remittances</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
@@ -2289,31 +2329,27 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>intro_C</t>
+          <t>grp_C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
+          <t>Module C: Monthly calendar of work and income; remittances</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2326,36 +2362,36 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>status_m5</t>
+          <t>intro_C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>In May, what was your main work or activity?</t>
+          <t>Now I want to go through the last twelve months, one month at a time. For each month I will ask what work you were mainly doing, and then what you usually earned. It is easiest to start with the Yatra months and fill the rest afterwards.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अब मैं पिछले बारह महीनों के बारे में, एक-एक महीना करके पूछूँगा। हर महीने के लिए पूछूँगा कि आप मुख्य रूप से क्या काम कर रहे थे, और फिर यह कि आमतौर पर कितना कमाया। सबसे आसान यह रहता है कि पहले यात्रा वाले महीने भर लें, बाक़ी बाद में।</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
@@ -2373,17 +2409,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>status_m6</t>
+          <t>status_m5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>In June, what was your main work or activity?</t>
+          <t>In May, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2410,17 +2446,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>status_m7</t>
+          <t>status_m6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>In July, what was your main work or activity?</t>
+          <t>In June, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जून में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2447,17 +2483,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>status_m8</t>
+          <t>status_m7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>In August, what was your main work or activity?</t>
+          <t>In July, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जुलाई में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -2484,17 +2520,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>status_m9</t>
+          <t>status_m8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>In September, what was your main work or activity?</t>
+          <t>In August, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अगस्त में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2521,17 +2557,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>status_m10</t>
+          <t>status_m9</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>In October, what was your main work or activity?</t>
+          <t>In September, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>सितंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -2558,17 +2594,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>status_m11</t>
+          <t>status_m10</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>In November, what was your main work or activity?</t>
+          <t>In October, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>अक्टूबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2595,17 +2631,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>status_m12</t>
+          <t>status_m11</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>In December, what was your main work or activity?</t>
+          <t>In November, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>नवंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2627,36 +2663,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>calc_months_no_work</t>
+          <t>status_m12</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>In December, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>months with no paid work (hidden)</t>
+          <t>दिसंबर में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
@@ -2669,17 +2705,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>calc_offseason_work</t>
+          <t>calc_months_no_work</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>months of other paid work (hidden)</t>
+          <t>months with no paid work (hidden)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2691,7 +2727,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+          <t>if(${status_m1}=8,1,0) + if(${status_m2}=8,1,0) + if(${status_m3}=8,1,0) + if(${status_m4}=8,1,0) + if(${status_m5}=8,1,0) + if(${status_m6}=8,1,0) + if(${status_m7}=8,1,0) + if(${status_m8}=8,1,0) + if(${status_m9}=8,1,0) + if(${status_m10}=8,1,0) + if(${status_m11}=8,1,0) + if(${status_m12}=8,1,0)</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -2701,36 +2737,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>select_one activity</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>status_m1</t>
+          <t>calc_offseason_work</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>In January, what was your main work or activity?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>months of other paid work (hidden)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>if(${status_m1}&gt;=2 and ${status_m1}&lt;=7,1,0) + if(${status_m2}&gt;=2 and ${status_m2}&lt;=7,1,0) + if(${status_m3}&gt;=2 and ${status_m3}&lt;=7,1,0) + if(${status_m4}&gt;=2 and ${status_m4}&lt;=7,1,0) + if(${status_m5}&gt;=2 and ${status_m5}&lt;=7,1,0) + if(${status_m6}&gt;=2 and ${status_m6}&lt;=7,1,0) + if(${status_m7}&gt;=2 and ${status_m7}&lt;=7,1,0) + if(${status_m8}&gt;=2 and ${status_m8}&lt;=7,1,0) + if(${status_m9}&gt;=2 and ${status_m9}&lt;=7,1,0) + if(${status_m10}&gt;=2 and ${status_m10}&lt;=7,1,0) + if(${status_m11}&gt;=2 and ${status_m11}&lt;=7,1,0) + if(${status_m12}&gt;=2 and ${status_m12}&lt;=7,1,0)</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
@@ -2743,17 +2779,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>status_m2</t>
+          <t>status_m1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>In February, what was your main work or activity?</t>
+          <t>In January, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>जनवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2780,17 +2816,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>status_m3</t>
+          <t>status_m2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>In March, what was your main work or activity?</t>
+          <t>In February, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>फ़रवरी में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -2817,17 +2853,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>status_m4</t>
+          <t>status_m3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>In April, what was your main work or activity?</t>
+          <t>In March, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
+          <t>मार्च में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -2849,22 +2885,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>select_one recall</t>
+          <t>select_one activity</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>knows_monthly_income</t>
+          <t>status_m4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
+          <t>In April, what was your main work or activity?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
+          <t>अप्रैल में आपका मुख्य काम या काम-धंधा क्या था?</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -2886,22 +2922,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one recall</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>income_m5</t>
+          <t>knows_monthly_income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
+          <t>Can you tell me roughly what you earned in each month of the past year, or would it be easier to give one total for the whole year?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>क्या आप हर महीने की कमाई अलग-अलग बता सकते हैं, या पूरे साल का एक जोड़ बताना आसान रहेगा?</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -2911,11 +2947,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2932,17 +2964,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>income_m6</t>
+          <t>income_m5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in May, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2954,12 +2986,24 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m5} != 8</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -2973,17 +3017,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>income_m7</t>
+          <t>income_m6</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in June, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जून में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -2995,12 +3039,24 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m6} != 8</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -3014,17 +3070,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>income_m8</t>
+          <t>income_m7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in July, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जुलाई में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -3036,12 +3092,24 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m7} != 8</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3055,17 +3123,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>income_m9</t>
+          <t>income_m8</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in August, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अगस्त में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
@@ -3077,12 +3145,24 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m8} != 8</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -3096,17 +3176,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>income_m10</t>
+          <t>income_m9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in September, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>सितंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -3118,12 +3198,24 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m9} != 8</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
@@ -3137,17 +3229,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>income_m11</t>
+          <t>income_m10</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in October, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>अक्टूबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
@@ -3159,12 +3251,24 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m10} != 8</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3178,17 +3282,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>income_m12</t>
+          <t>income_m11</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in November, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>नवंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
@@ -3200,12 +3304,24 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m11} != 8</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -3219,17 +3335,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>income_m1</t>
+          <t>income_m12</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in December, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>दिसंबर में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3241,12 +3357,24 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m12} != 8</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -3260,17 +3388,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>income_m2</t>
+          <t>income_m1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in January, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>जनवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3282,12 +3410,24 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m1} != 8</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -3301,17 +3441,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>income_m3</t>
+          <t>income_m2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in February, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>फ़रवरी में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3323,12 +3463,24 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m2} != 8</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -3342,17 +3494,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>income_m4</t>
+          <t>income_m3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in March, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
+          <t>मार्च में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3364,12 +3516,24 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m3} != 8</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -3383,17 +3547,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>income_annual_total</t>
+          <t>income_m4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
+          <t>How much did you earn from all your work in April, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
+          <t>अप्रैल में सारे काम से ख़र्चा निकालकर आपने कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3405,12 +3569,24 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>${knows_monthly_income} = 0</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+          <t>${knows_monthly_income} = 1 and ${status_m4} != 8</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earnings cannot be negative.</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
@@ -3424,17 +3600,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>pct_income_yatra</t>
+          <t>income_annual_total</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
+          <t>Thinking of the whole past year, about how much did you earn in total from all your work, after costs? (Rs)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
+          <t>पूरे पिछले साल को मिलाकर, सारे काम से ख़र्चा निकालकर आपने कुल कितना कमाया? (रुपये)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -3449,21 +3625,9 @@
           <t>${knows_monthly_income} = 0</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 100</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 100 out of every 100 rupees.</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
@@ -3477,17 +3641,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>remit_out_yatra_pm</t>
+          <t>pct_income_yatra</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
+          <t>Out of every 100 rupees you earned in the whole year, how many came from your Yatra work? (The rest is counted as coming from your other work.)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>पूरे साल में आपने जो 100 रुपये कमाए, उनमें से कितने यात्रा के काम से आए? (बाकी दूसरे काम का माना जाएगा।)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -3497,10 +3661,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>${knows_monthly_income} = 0</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 100 out of every 100 rupees.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>हर 100 रुपये में से 0 से 100 के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
@@ -3514,17 +3694,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>remit_out_offseason_pm</t>
+          <t>remit_out_yatra_pm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually send to family or others living elsewhere? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप घर या कहीं और रहने वालों को कितना पैसा भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -3546,22 +3726,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>select_one remitmode</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>remit_mode</t>
+          <t>remit_out_offseason_pm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>How do you usually send it?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually send? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना भेजते हैं? (रुपये, न भेजते हों तो 0)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -3571,11 +3751,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3587,22 +3763,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one remitmode</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>remit_in_yatra_pm</t>
+          <t>remit_mode</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
+          <t>How do you usually send it?</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>आप पैसा आम तौर पर कैसे भेजते हैं?</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3612,7 +3788,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>${remit_out_yatra_pm} &gt; 0 or ${remit_out_offseason_pm} &gt; 0</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3629,17 +3809,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>remit_in_offseason_pm</t>
+          <t>remit_in_yatra_pm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
+          <t>In a normal month during the Yatra season, how much money do you usually receive from family or others? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
+          <t>यात्रा के मौसम के आम महीने में, घरवालों या किसी और से आपको कितना पैसा मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3666,17 +3846,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>hours_day_offseason</t>
+          <t>remit_in_offseason_pm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
+          <t>In a normal month when the Yatra is closed, how much do you usually receive? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में कितना मिलता है? (रुपये, न मिलता हो तो 0)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3686,26 +3866,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>${calc_offseason_work} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 18</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Hours a day must be between 1 and 18.</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
@@ -3719,17 +3883,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>days_week_offseason</t>
+          <t>hours_day_offseason</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>In those months, how many days a week do you usually work?</t>
+          <t>In the months when the Yatra is closed and you are doing other work, on a normal working day, how many hours do you work in total?</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+          <t>जिन महीनों में यात्रा बंद रहती है और आप कोई दूसरा काम करते हैं, उनमें आम दिन में आप कुल कितने घंटे काम करते हैं?</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3746,17 +3910,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 7</t>
+          <t>. &gt;= 1 and . &lt;= 18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Days a week must be between 1 and 7.</t>
+          <t>Hours a day must be between 1 and 18.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+          <t>दिन के घंटे 1 से 18 के बीच होने चाहिए।</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -3767,19 +3931,51 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>days_week_offseason</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>In those months, how many days a week do you usually work?</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>उन महीनों में आप हफ़्ते में कितने दिन काम करते हैं?</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>${calc_offseason_work} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Days a week must be between 1 and 7.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>हफ़्ते के दिन 1 से 7 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
@@ -3788,24 +3984,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>grp_D</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Module D: Migration</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Module D: Migration</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
@@ -3816,31 +4000,27 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>intro_D</t>
+          <t>grp_D</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
+          <t>Module D: Migration</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
+          <t>Module D: Migration</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -3853,36 +4033,36 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>select_one origin</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>intro_D</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Where is your permanent home?</t>
+          <t>Now a few questions about where your home is, and what you do when the Yatra closes for the season.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>आपका पक्का घर कहाँ है?</t>
+          <t>अब कुछ सवाल इस बारे में कि आपका घर कहाँ है, और यात्रा का मौसम ख़त्म होने पर आप क्या करते हैं।</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
@@ -3895,22 +4075,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>select_one state</t>
+          <t>select_one origin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>home_state</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Which state is your permanent home in?</t>
+          <t>Where is your permanent home?</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
+          <t>आपका पक्का घर कहाँ है?</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -3920,11 +4100,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>${origin} = 3</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -3936,22 +4112,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>select_one ruralurban</t>
+          <t>select_one state</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>home_rural_urban</t>
+          <t>home_state</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Is that home in a village, or in a town or city?</t>
+          <t>Which state is your permanent home in?</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
+          <t>वह घर किस राज्य में है? (अगर भारत से बाहर है तो वह बताइए।)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3961,7 +4137,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>${origin} = 3</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -3973,22 +4153,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one ruralurban</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>resp_returns_at_closure</t>
+          <t>home_rural_urban</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
+          <t>Is that home in a village, or in a town or city?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
+          <t>वह घर गाँव में है, या क़स्बे या शहर में?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4015,17 +4195,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>hh_at_home_place</t>
+          <t>resp_returns_at_closure</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
+          <t>When the Yatra closes for the season, do YOU go to your home place?</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
+          <t>जब यात्रा का मौसम ख़त्म हो जाता है, तो क्या आप अपने घर चले जाते हैं?</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4047,22 +4227,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>n_here_season</t>
+          <t>hh_at_home_place</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
+          <t>And do the rest of your household live at your home place all year, or are they here with you during the season?</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
+          <t>और आपके बाक़ी घरवाले — वे साल भर आपके घर वाली जगह पर ही रहते हैं, या सीज़न में आपके साथ यहाँ रहते हैं?</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4072,11 +4252,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>${hh_at_home_place} = 1</t>
-        </is>
-      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -4093,17 +4269,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>years_coming_here</t>
+          <t>n_here_season</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>How many years have you been coming here for the Yatra season?</t>
+          <t>During the Yatra season, how many people are you feeding and spending on here, counting yourself?</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
+          <t>यात्रा के मौसम में आप यहाँ कितने लोगों का खाना-ख़र्चा चलाते हैं, अपने आप को गिनकर?</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4115,7 +4291,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${hh_at_home_place} = 1</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4129,22 +4305,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>select_one comereason</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>came_here_reason</t>
+          <t>years_coming_here</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>What was the main reason you first came here to work?</t>
+          <t>How many years have you been coming here for the Yatra season?</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
+          <t>आप कितने सालों से यात्रा के मौसम में यहाँ आ रहे हैं?</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4156,7 +4332,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>${origin} != 1</t>
+          <t>${resp_returns_at_closure} = 1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4170,22 +4346,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one comereason</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>worked_away_in_closure</t>
+          <t>came_here_reason</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
+          <t>What was the main reason you first came here to work?</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>आप सबसे पहले यहाँ काम करने किस मुख्य वजह से आए थे?</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4195,7 +4371,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>${origin} != 1</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4207,32 +4387,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>closure_work_detail</t>
+          <t>worked_away_in_closure</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do there? Write what they say.</t>
+          <t>Last year, in the months when the Yatra was closed, did you go somewhere else for work?</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>पिछले साल, जिन महीनों में यात्रा बंद थी, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>${worked_away_in_closure} = 1</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4244,34 +4424,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>left_here_month</t>
+          <t>closure_work_detail</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>In the past year, which month did you last leave here and go to your home place?</t>
+          <t>Where did you go, and what work did you do there? Write what they say.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>${resp_returns_at_closure} = 1</t>
+          <t>${worked_away_in_closure} = 1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -4290,17 +4466,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>returned_here_month</t>
+          <t>left_here_month</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>And which month did you come back here?</t>
+          <t>In the past year, which month did you last leave here and go to your home place?</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>और किस महीने आप वापस यहाँ आए?</t>
+          <t>पिछले साल आप यहाँ से आख़िरी बार किस महीने अपने घर गए थे?</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4326,22 +4502,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>months_away_for_work</t>
+          <t>returned_here_month</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
+          <t>And which month did you come back here?</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
+          <t>और किस महीने आप वापस यहाँ आए?</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
@@ -4353,7 +4529,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>${worked_away_in_closure} = 1</t>
+          <t>${resp_returns_at_closure} = 1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -4367,22 +4543,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>worked_other_places</t>
+          <t>months_away_for_work</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Before you started coming here, had you gone anywhere else for work?</t>
+          <t>In those months away, how many months did you spend working somewhere other than your home place?</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
+          <t>बाहर रहे उन महीनों में, कितने महीने आपने अपने घर से हटकर कहीं और काम किया?</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4392,7 +4568,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>${worked_away_in_closure} = 1</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4404,32 +4584,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>other_places_detail</t>
+          <t>worked_other_places</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Where did you go, and what work did you do? Write what they say.</t>
+          <t>Before you started coming here, had you gone anywhere else for work?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यहाँ आना शुरू करने से पहले, क्या आप काम के लिए कहीं और गए थे?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>${worked_other_places} = 1</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -4441,32 +4621,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>would_move_for_work</t>
+          <t>other_places_detail</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
+          <t>Where did you go, and what work did you do? Write what they say.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
+          <t>कहाँ गए थे, और वहाँ क्या काम किया? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>${worked_other_places} = 1</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4478,22 +4658,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>select_one referral</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>migration_referral</t>
+          <t>would_move_for_work</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Who mainly helped you get this work, or arranged it for you?</t>
+          <t>If this work here ended, would you go away from your home place to look for work in the coming year?</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
+          <t>अगर यहाँ का यह काम बंद हो जाए, तो क्या आप आने वाले साल में काम ढूँढने अपने घर से बाहर जाएँगे?</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -4515,32 +4695,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one referral</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>migration_referral_other</t>
+          <t>migration_referral</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Who was it? Write what they say.</t>
+          <t>Who mainly helped you get this work, or arranged it for you?</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>यहाँ आने या यह काम पकड़ने में मुख्य रूप से किसने मदद की या रास्ता दिखाया: यहाँ पहले से रह रहा कोई घरवाला; कोई दोस्त या जान-पहचान वाला; कोई ठेकेदार या एजेंट; कोई नेता या समाज का बड़ा आदमी; कोई नहीं, आपने खुद ढूँढा; मालिक ने सीधे बुलाया; या कोई और?</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>${migration_referral} = 7</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4552,16 +4732,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>migration_referral_other</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Who was it? Write what they say.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>वे कौन थे? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>${migration_referral} = 7</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -4573,24 +4769,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>grp_E</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Module E: Household consumption</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
@@ -4601,31 +4785,27 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>intro_E</t>
+          <t>grp_E</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Now about what your household usually spends in a month. For each thing I will ask twice -- once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed -- because spending is often quite different in the two. Rough figures are fine.</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
+          <t>Module E: Household consumption</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -4638,36 +4818,36 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>spend_differs_by_season</t>
+          <t>intro_E</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
+          <t>Now about what your household usually spends in a month. For each thing I will ask twice -- once for a normal month during the Yatra season, and once for a normal month when the Yatra is closed -- because spending is often quite different in the two. Rough figures are fine.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
+          <t>अब यह कि आपके घर का एक महीने में आमतौर पर कितना ख़र्च होता है। हर चीज़ के लिए मैं दो बार पूछूँगा — एक बार यात्रा के मौसम के आम महीने के लिए, और एक बार उस महीने के लिए जब यात्रा बंद रहती है — क्योंकि दोनों में ख़र्च अक्सर काफ़ी अलग होता है। अंदाज़े का हिसाब ही ठीक है।</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
@@ -4680,22 +4860,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cons_staples_yatra_pm</t>
+          <t>spend_differs_by_season</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>Leaving aside money you send home -- is what your household spends in a normal month during the Yatra season different from what it spends when the Yatra is closed?</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>घर भेजे जाने वाले पैसे को छोड़कर — यात्रा के मौसम में आपके घर का महीने का ख़र्च, और जब यात्रा बंद रहती है तब का ख़र्च, क्या अलग-अलग होता है?</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -4722,17 +4902,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>cons_staples_offseason_pm</t>
+          <t>cons_staples_yatra_pm</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -4742,11 +4922,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
@@ -4763,17 +4939,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>cons_perishables_yatra_pm</t>
+          <t>cons_staples_offseason_pm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on cereals (rice, wheat, other grains), pulses, sugar and salt, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर अनाज (चावल, गेहूँ, दूसरा अनाज), दाल, चीनी और नमक पर, ख़रीदा हुआ या अपने घर का कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -4783,7 +4959,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -4800,17 +4980,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>cons_perishables_offseason_pm</t>
+          <t>cons_perishables_yatra_pm</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -4820,11 +5000,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -4841,17 +5017,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>cons_food_own_yatra_pm</t>
+          <t>cons_perishables_offseason_pm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on milk and milk products, vegetables, fruit, egg/fish/meat, cooking oil, spices, and tea or coffee, bought or from your own stock? (Rs)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दूध और दूध की चीज़ें, सब्ज़ी, फल, अंडा/मछली/मांस, तेल, मसाले, और चाय पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -4861,7 +5037,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -4878,17 +5058,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cons_food_own_offseason_pm</t>
+          <t>cons_food_own_yatra_pm</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
+          <t>If you (and anyone staying with you here) had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month during the Yatra season? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
+          <t>अगर आप (और जो यहाँ आपके साथ रहते हैं) अपना खाना ख़ुद न उगाते, न पालते और न किसी से मिलता, तो यात्रा के मौसम के आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -4898,11 +5078,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -4919,17 +5095,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>cons_food_out_yatra_pm</t>
+          <t>cons_food_own_offseason_pm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>If your household had not grown, raised or been given any of your food, about how much would it have cost to buy in a normal month when the Yatra is closed? (Rs, 0 if you buy everything)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>अगर आपका घर अपना खाना ख़ुद न उगाता, न पालता और न किसी से मिलता, तो जब यात्रा बंद रहती है उस आम महीने में उसे ख़रीदने में लगभग कितना लगता? (रुपये, सब ख़रीदते हों तो 0)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -4939,7 +5115,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -4956,17 +5136,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>cons_food_out_offseason_pm</t>
+          <t>cons_food_out_yatra_pm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -4976,11 +5156,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -4997,17 +5173,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cons_fuel_yatra_pm</t>
+          <t>cons_food_out_offseason_pm</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on meals, tea and snacks eaten outside the home, including any an employer gave free, at their market value? (Rs)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बाहर खाए गए खाने, चाय और नाश्ते पर, मालिक ने मुफ़्त दिया हो तो उसकी क़ीमत मिलाकर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -5017,7 +5193,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
@@ -5034,17 +5214,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cons_fuel_offseason_pm</t>
+          <t>cons_fuel_yatra_pm</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -5054,11 +5234,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -5075,17 +5251,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cons_routine_misc_yatra_pm</t>
+          <t>cons_fuel_offseason_pm</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on fuel and light: cooking fuel, firewood, electricity, kerosene, candles? (Rs)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर ईंधन और रोशनी पर: खाना बनाने की गैस, लकड़ी, बिजली, मिट्टी का तेल, मोमबत्ती कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
@@ -5095,7 +5271,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -5112,17 +5292,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cons_routine_misc_offseason_pm</t>
+          <t>cons_routine_misc_yatra_pm</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -5132,11 +5312,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5153,17 +5329,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>cons_transport_comm_yatra_pm</t>
+          <t>cons_routine_misc_offseason_pm</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on soap, toiletries, cleaning goods and other small household items? (Rs)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर साबुन, नहाने-धोने का सामान, सफ़ाई का सामान और घर की दूसरी छोटी चीज़ों पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -5173,7 +5349,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5190,17 +5370,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>cons_transport_comm_offseason_pm</t>
+          <t>cons_transport_comm_yatra_pm</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -5210,11 +5390,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5231,17 +5407,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>cons_rent_yatra_pm</t>
+          <t>cons_transport_comm_offseason_pm</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on local transport (bus, shared jeep, auto) and phone or internet charges? (Rs)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर आने-जाने (बस, जीप, ऑटो) और फ़ोन या इंटरनेट पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -5251,7 +5427,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5268,17 +5448,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>cons_rent_offseason_pm</t>
+          <t>cons_rent_yatra_pm</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
@@ -5288,11 +5468,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5309,17 +5485,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_yatra_pm</t>
+          <t>cons_rent_offseason_pm</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on rent for the home (0 if owned, and 0 for any period spent living for free)? (Rs)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर घर के किराये पर (अपना घर हो तो 0, और मुफ़्त रहे हों तो भी 0) कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
@@ -5329,7 +5505,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -5346,17 +5526,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cons_med_nonhosp_offseason_pm</t>
+          <t>cons_med_nonhosp_yatra_pm</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -5366,11 +5546,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
@@ -5387,17 +5563,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>cons_packaged_food_yatra_pm</t>
+          <t>cons_med_nonhosp_offseason_pm</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on medicine, doctor's or clinic fees and tests, not counting a hospital stay? (Rs)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर दवाई, डॉक्टर या क्लीनिक की फ़ीस और जाँच पर, अस्पताल में भर्ती को छोड़कर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
@@ -5407,7 +5583,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5424,17 +5604,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>cons_packaged_food_offseason_pm</t>
+          <t>cons_packaged_food_yatra_pm</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -5444,11 +5624,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -5465,17 +5641,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_yatra_pm</t>
+          <t>cons_packaged_food_offseason_pm</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on biscuits, namkeen, chips, packaged snacks, cold drinks or bottled water? (Rs)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर बिस्किट, नमकीन, चिप्स, पैकेट वाले नाश्ते, कोल्ड ड्रिंक या बोतलबंद पानी पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5485,7 +5661,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5502,17 +5682,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>cons_pan_tobacco_offseason_pm</t>
+          <t>cons_pan_tobacco_yatra_pm</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
+          <t>In a normal month during the Yatra season, how much do you (and anyone staying with you here) spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
+          <t>यात्रा के मौसम के आम महीने में, आप (और जो यहाँ आपके साथ रहते हैं) पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करते हैं? (रुपये)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
@@ -5522,11 +5702,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>${spend_differs_by_season} = 1</t>
-        </is>
-      </c>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5543,17 +5719,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>cons_clothing_12m</t>
+          <t>cons_pan_tobacco_offseason_pm</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
+          <t>In a normal month when the Yatra is closed, how much does your household spend on pan, gutka, bidi, cigarettes, tobacco or alcohol? (Rs)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
+          <t>जब यात्रा बंद रहती है, उस आम महीने में आपका घर पान, गुटका, बीड़ी, सिगरेट, तंबाकू या शराब पर कितना ख़र्च करता है? (रुपये)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
@@ -5563,7 +5739,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>${spend_differs_by_season} = 1</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -5580,17 +5760,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>cons_education_12m</t>
+          <t>cons_clothing_12m</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
+          <t>In the last 12 months, how much did your household spend on clothes and footwear? (Rs)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
+          <t>पिछले 12 महीनों में आपके घर ने कपड़ों और जूते-चप्पल पर कितना ख़र्च किया? (रुपये)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -5617,17 +5797,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>cons_medical_hosp_12m</t>
+          <t>cons_education_12m</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
+          <t>In the last 12 months, how much on education: fees, books, uniforms, tuition? (Rs)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
+          <t>पिछले 12 महीनों में पढ़ाई पर कितना ख़र्च हुआ: फ़ीस, किताबें, ड्रेस, ट्यूशन? (रुपये)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
@@ -5654,17 +5834,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>cons_durables_12m</t>
+          <t>cons_medical_hosp_12m</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+          <t>In the last 12 months, how much did your household pay for any hospital admission or stay? (Rs, 0 if none)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+          <t>पिछले 12 महीनों में अस्पताल में भर्ती होने पर आपके घर का कितना ख़र्च हुआ? (रुपये, न हुआ हो तो 0)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -5686,15 +5866,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>cons_durables_12m</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>In the last 12 months, how much on durable goods: furniture, utensils, cooking appliances, phone, jewellery or ornaments, bicycle or vehicle parts? (Rs)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>पिछले 12 महीनों में सामान पर कितना ख़र्च हुआ: फ़र्नीचर, बर्तन, चूल्हा-मशीन, फ़ोन, गहने, साइकिल या गाड़ी के पुर्ज़े? (रुपये)</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
@@ -5707,24 +5903,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>grp_F</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Module F: Housing, amenities and assets</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
@@ -5735,31 +5919,27 @@
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>intro_F</t>
+          <t>grp_F</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Now some questions about your house and the things your household has.</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
+          <t>Module F: Housing, amenities and assets</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -5772,36 +5952,36 @@
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>select_one floor</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>floor_material</t>
+          <t>intro_F</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>What is the main material of the floor at your usual home?</t>
+          <t>Now some questions about your house and the things your household has.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
+          <t>अब आपके घर और घर में मौजूद सामान के बारे में कुछ सवाल।</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
@@ -5814,22 +5994,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one roof</t>
+          <t>select_one floor</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>roof_material</t>
+          <t>floor_material</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>What is the main material of the roof at your usual home?</t>
+          <t>What is the main material of the floor at your usual home?</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
+          <t>आपके असली घर में फ़र्श मुख्य रूप से किस चीज़ का है?</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -5851,22 +6031,22 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one wall</t>
+          <t>select_one roof</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>wall_material</t>
+          <t>roof_material</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>What are the walls of your usual home mainly made of?</t>
+          <t>What is the main material of the roof at your usual home?</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
+          <t>आपके असली घर की छत मुख्य रूप से किस चीज़ की है?</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -5888,22 +6068,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>select_one accomhere</t>
+          <t>select_one wall</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>accom_type_here</t>
+          <t>wall_material</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>While you are here for the season, where do you sleep?</t>
+          <t>What are the walls of your usual home mainly made of?</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
+          <t>आपके असली घर की दीवारें मुख्य रूप से किस चीज़ की बनी हैं?</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -5925,22 +6105,22 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one accomhere</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>accom_type_here</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Does your usual home have an electricity connection?</t>
+          <t>While you are here for the season, where do you sleep?</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
+          <t>सीज़न में यहाँ रहते हुए आप कहाँ सोते हैं?</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -5962,22 +6142,22 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>select_one toilet</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>toilet_type</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>What kind of toilet does your household use at your usual home?</t>
+          <t>Does your usual home have an electricity connection?</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
+          <t>क्या आपके असली घर में बिजली का कनेक्शन है?</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -5999,22 +6179,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>select_one water</t>
+          <t>select_one toilet</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>drinking_water</t>
+          <t>toilet_type</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>What is your main source of drinking water at your usual home?</t>
+          <t>What kind of toilet does your household use at your usual home?</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
+          <t>आपका घर अपने असली घर में किस तरह का शौचालय इस्तेमाल करता है?</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -6036,22 +6216,22 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one water</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>water_on_premises</t>
+          <t>drinking_water</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Is the drinking water available at the house itself?</t>
+          <t>What is your main source of drinking water at your usual home?</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
+          <t>आपके असली घर में पीने का पानी मुख्य रूप से कहाँ से आता है?</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -6073,22 +6253,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>water_fetch_minutes</t>
+          <t>water_on_premises</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
+          <t>Is the drinking water available at the house itself?</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
+          <t>क्या पीने का पानी घर पर ही मिल जाता है?</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -6098,26 +6278,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>${water_on_premises} = 0</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 300</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Minutes must be between 0 and 300.</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
-        </is>
-      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
@@ -6126,22 +6290,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>select_one fuel</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>cooking_fuel</t>
+          <t>water_fetch_minutes</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>What does your household mainly use to cook at your usual home?</t>
+          <t>How long does it take to go there, get the water and come back? (minutes, round trip)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
+          <t>वहाँ जाने, पानी भरने और लौटने में कुल कितना समय लगता है? (मिनट)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -6151,10 +6315,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>${water_on_premises} = 0</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 300</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Minutes must be between 0 and 300.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>मिनट 0 से 300 के बीच होने चाहिए।</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
@@ -6163,22 +6343,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one fuel</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>owns_tv</t>
+          <t>cooking_fuel</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Does your household own: a television?</t>
+          <t>What does your household mainly use to cook at your usual home?</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>क्या आपके घर में टीवी है?</t>
+          <t>आपके असली घर में खाना मुख्य रूप से किस चीज़ पर बनता है?</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -6205,17 +6385,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>owns_radio</t>
+          <t>owns_tv</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>... a radio?</t>
+          <t>Does your household own: a television?</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>...रेडियो?</t>
+          <t>क्या आपके घर में टीवी है?</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -6242,17 +6422,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>owns_bicycle</t>
+          <t>owns_radio</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>... a bicycle?</t>
+          <t>... a radio?</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>...साइकिल?</t>
+          <t>...रेडियो?</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -6279,17 +6459,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>owns_motorcycle</t>
+          <t>owns_bicycle</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>... a motorcycle or scooter?</t>
+          <t>... a bicycle?</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>...मोटरसाइकिल या स्कूटर?</t>
+          <t>...साइकिल?</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -6316,17 +6496,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>owns_car</t>
+          <t>owns_motorcycle</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>... a car, jeep or truck?</t>
+          <t>... a motorcycle or scooter?</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>...कार, जीप या ट्रक?</t>
+          <t>...मोटरसाइकिल या स्कूटर?</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -6353,17 +6533,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>owns_phone</t>
+          <t>owns_car</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>... a telephone of any kind, mobile or landline?</t>
+          <t>... a car, jeep or truck?</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
+          <t>...कार, जीप या ट्रक?</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -6390,17 +6570,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>owns_computer</t>
+          <t>owns_phone</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>... a computer or laptop?</t>
+          <t>... a telephone of any kind, mobile or landline?</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>...कंप्यूटर या लैपटॉप?</t>
+          <t>...कोई फ़ोन, मोबाइल या लैंडलाइन?</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -6427,17 +6607,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>owns_animal_cart</t>
+          <t>owns_computer</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>... a cart pulled by an animal?</t>
+          <t>... a computer or laptop?</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
+          <t>...कंप्यूटर या लैपटॉप?</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -6464,17 +6644,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>owns_fridge</t>
+          <t>owns_animal_cart</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>... a refrigerator?</t>
+          <t>... a cart pulled by an animal?</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>...फ़्रिज?</t>
+          <t>...जानवर से खींची जाने वाली गाड़ी?</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -6496,22 +6676,22 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>select_one landunit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>land_unit</t>
+          <t>owns_fridge</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>In what unit do you count your land -- nali, bigha, acres or hectares?</t>
+          <t>... a refrigerator?</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
+          <t>...फ़्रिज?</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -6533,22 +6713,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one landunit</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>land_cultivable_acres</t>
+          <t>land_unit</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
+          <t>In what unit do you count your land -- nali, bigha, acres or hectares?</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
+          <t>आप अपनी ज़मीन किस हिसाब से गिनते हैं — नाली, बीघा, एकड़ या हेक्टेयर?</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -6558,11 +6738,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>${land_unit} != 5</t>
-        </is>
-      </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -6574,22 +6750,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>owns_cow_buffalo</t>
+          <t>land_cultivable_acres</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Does your household own any cows or buffaloes?</t>
+          <t>And how much CULTIVABLE land is that? Do not count the land the house stands on.</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>क्या आपके घर में गाय या भैंस है?</t>
+          <t>आपके घर के पास कितनी जोतने लायक़ ज़मीन है, अपनी या जोतने की, एकड़ में? जिस ज़मीन पर घर बना है उसे मत गिनिए। (न हो तो 0)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -6599,10 +6775,26 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>${land_unit} != 5</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Land cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Land cannot be negative.</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
@@ -6616,17 +6808,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>owns_goat_sheep</t>
+          <t>owns_cow_buffalo</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Does your household own any goats or sheep?</t>
+          <t>Does your household own any cows or buffaloes?</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>क्या आपके घर में बकरी या भेड़ है?</t>
+          <t>क्या आपके घर में गाय या भैंस है?</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -6653,17 +6845,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>owns_pony_mule</t>
+          <t>owns_goat_sheep</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Does your household own any ponies or mules?</t>
+          <t>Does your household own any goats or sheep?</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
+          <t>क्या आपके घर में बकरी या भेड़ है?</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -6690,17 +6882,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>owns_shop_stall</t>
+          <t>owns_pony_mule</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Does your household own a shop or stall that you use to earn?</t>
+          <t>Does your household own any ponies or mules?</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर में घोड़ा या खच्चर है?</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -6727,17 +6919,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>owns_work_vehicle</t>
+          <t>owns_shop_stall</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
+          <t>Does your household own a shop or stall that you use to earn?</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
+          <t>क्या आपके घर की अपनी दुकान या खोखा है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -6764,17 +6956,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>owns_work_equipment</t>
+          <t>owns_work_vehicle</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Does your household own equipment or tools that you use to earn?</t>
+          <t>Does your household own a vehicle you use to earn (for example a jeep, truck or taxi)?</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
+          <t>क्या आपके घर की अपनी गाड़ी है जिससे आप कमाते हैं (जैसे जीप, ट्रक या टैक्सी)?</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -6796,32 +6988,32 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>work_equipment_detail</t>
+          <t>owns_work_equipment</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+          <t>Does your household own equipment or tools that you use to earn?</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+          <t>क्या आपके घर के पास काम के औज़ार या मशीन है जिससे आप कमाते हैं?</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>${owns_work_equipment} = 1</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -6833,16 +7025,32 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>work_equipment_detail</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>What are they? Write what they say. Leave blank if they cannot say.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>वे क्या हैं? जैसा वे बताएँ वैसा लिख लीजिए। न बता पाएँ तो खाली छोड़ दीजिए।</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>${owns_work_equipment} = 1</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
@@ -6854,24 +7062,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>grp_G</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Module G: Finance, insurance and schemes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
@@ -6882,31 +7078,27 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>intro_G</t>
+          <t>grp_G</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Now about savings, loans, insurance and government schemes.</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
+          <t>Module G: Finance, insurance and schemes</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6919,36 +7111,36 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>has_bank_account</t>
+          <t>intro_G</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Does anyone in your household have a bank account or a post office account?</t>
+          <t>Now about savings, loans, insurance and government schemes.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
+          <t>अब बचत, क़र्ज़, बीमा और सरकारी योजनाओं के बारे में।</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
@@ -6966,17 +7158,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>took_loan_12m</t>
+          <t>has_bank_account</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
+          <t>Does anyone in your household have a bank account or a post office account?</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
+          <t>क्या आपके घर में किसी का बैंक खाता या डाकघर का खाता है?</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -6998,22 +7190,22 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>select_one credit</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>credit_source</t>
+          <t>took_loan_12m</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Who was the main lender?</t>
+          <t>In the last 12 months, did you or anyone in your household borrow money?</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>मुख्य रूप से किससे उधार लिया?</t>
+          <t>पिछले 12 महीनों में क्या आपने या आपके घर के किसी सदस्य ने पैसा उधार लिया?</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -7023,11 +7215,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>${took_loan_12m} = 1</t>
-        </is>
-      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
@@ -7039,22 +7227,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>select_one loanpurpose</t>
+          <t>select_one credit</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>loan_purpose</t>
+          <t>credit_source</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>What did you take it for?</t>
+          <t>Who was the main lender?</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
+          <t>मुख्य रूप से किससे उधार लिया?</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -7080,22 +7268,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one loanpurpose</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>loan_amount_borrowed</t>
+          <t>loan_purpose</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>How much did you borrow in total? (Rs)</t>
+          <t>What did you take it for?</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
+          <t>वह क़र्ज़ आपने किस काम के लिए लिया था?</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -7126,17 +7314,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>loan_amount_borrowed</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>How much of that loan is still left to repay? (Rs)</t>
+          <t>How much did you borrow in total? (Rs)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
+          <t>आपने कुल कितना क़र्ज़ लिया था? (रुपये)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -7151,9 +7339,21 @@
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
@@ -7162,22 +7362,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>pays_interest</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Do you pay interest on it?</t>
+          <t>How much of that loan is still left to repay? (Rs)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>क्या आप उस पर ब्याज देते हैं?</t>
+          <t>उस क़र्ज़ में से अब भी कितना चुकाना बाक़ी है? (रुपये)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -7192,9 +7392,21 @@
           <t>${took_loan_12m} = 1</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
@@ -7203,30 +7415,34 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>loan_interest_per100_pm</t>
+          <t>pays_interest</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
+          <t>Do you pay interest on it?</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
+          <t>क्या आप उस पर ब्याज देते हैं?</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>${pays_interest} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -7240,34 +7456,30 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>loan_against_asset</t>
+          <t>loan_interest_per100_pm</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
+          <t>On every 100 rupees you borrowed, about how much interest do you pay in a month? (Rs; 0 if none, leave blank if not known)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
+          <t>आपने जो 100 रुपये उधार लिए, उन पर महीने का कितना ब्याज देते हैं? (रुपये; दर पता न हो तो खाली छोड़ दें)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>${took_loan_12m} = 1</t>
+          <t>${pays_interest} = 1</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -7281,22 +7493,22 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>select_one collat</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>loan_collateral</t>
+          <t>loan_against_asset</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>What did you have to give as security?</t>
+          <t>Did you have to give something as security for it -- an animal, a vehicle, jewellery, land or your business?</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>आपको क्या गिरवी रखना पड़ा?</t>
+          <t>क्या उसके बदले कुछ गिरवी रखना पड़ा — जानवर, गाड़ी, गहने, ज़मीन या आपका धंधा?</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -7308,7 +7520,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>${loan_against_asset} = 1</t>
+          <t>${took_loan_12m} = 1</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -7322,22 +7534,22 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one collat</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>n_health_insured</t>
+          <t>loan_collateral</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
+          <t>What did you have to give as security?</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
+          <t>आपको क्या गिरवी रखना पड़ा?</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -7347,22 +7559,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>${loan_against_asset} = 1</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
@@ -7376,17 +7580,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>n_life_insured</t>
+          <t>n_health_insured</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>How many people in your household have life insurance? (0 if none)</t>
+          <t>How many people in your household are covered by any health insurance or health scheme, including government ones? (0 if none)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
+          <t>आपके घर में कितने लोगों का कोई स्वास्थ्य बीमा या स्वास्थ्य योजना है, सरकारी भी मिलाकर? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -7420,22 +7624,22 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>has_crop_insurance</t>
+          <t>n_life_insured</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Is your crop insured?</t>
+          <t>How many people in your household have life insurance? (0 if none)</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>क्या आपकी फ़सल का बीमा है?</t>
+          <t>आपके घर में कितने लोगों का जीवन बीमा है? (कोई नहीं तो 0)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -7445,14 +7649,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>${land_cultivable_acres} &gt; 0</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
@@ -7461,22 +7673,22 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>select_multiple govtscheme</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>govt_schemes</t>
+          <t>has_crop_insurance</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
+          <t>Is your crop insured?</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
+          <t>क्या आपकी फ़सल का बीमा है?</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -7486,22 +7698,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>not(selected(., '10') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
-        </is>
-      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>${land_cultivable_acres} &gt; 0</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
@@ -7510,35 +7714,47 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple govtscheme</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>govt_scheme_other</t>
+          <t>govt_schemes</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Which scheme was that? Write what they say.</t>
+          <t>In the last 12 months, did your household get anything from any of these? Read the list out and check every one they say yes to.</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
+          <t>पिछले 12 महीनों में इनमें से किसी से आपके घर को कुछ मिला? सूची पढ़कर सुनाइए और जिन-जिन पर वे हाँ कहें, सब पर निशान लगाइए।</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>selected(${govt_schemes}, '9')</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>not(selected(., '10') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>'None of these' cannot be ticked with a scheme. Choose one or the other.</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
@@ -7547,34 +7763,30 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>select_one portable</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ration_portable_here</t>
+          <t>govt_scheme_other</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Can you draw your ration here, or only at your home place?</t>
+          <t>Which scheme was that? Write what they say.</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
+          <t>वह कौन सी योजना थी? जैसा वे बताएँ वैसा लिख लीजिए।</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>selected(${govt_schemes}, '1')</t>
+          <t>selected(${govt_schemes}, '9')</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -7588,22 +7800,22 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one portable</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>smartphone_owned</t>
+          <t>ration_portable_here</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Do you own a smartphone?</t>
+          <t>Can you draw your ration here, or only at your home place?</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
+          <t>क्या आप अपना राशन यहाँ ले सकते हैं, या सिर्फ़ अपने घर वाली जगह पर?</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -7613,7 +7825,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>selected(${govt_schemes}, '1')</t>
+        </is>
+      </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
@@ -7630,17 +7846,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>uses_digital_payment</t>
+          <t>smartphone_owned</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Do you ever use UPI or another way of paying by phone?</t>
+          <t>Do you own a smartphone?</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
+          <t>क्या आपके पास स्मार्टफ़ोन है?</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -7662,22 +7878,22 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>n_can_transact_online</t>
+          <t>uses_digital_payment</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+          <t>Do you ever use UPI or another way of paying by phone?</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+          <t>क्या आप कभी UPI या फ़ोन से पैसे का लेन-देन करते हैं?</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -7688,21 +7904,9 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Cannot be more than the number of people in the household.</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
-        </is>
-      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
@@ -7711,19 +7915,47 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr"/>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>n_can_transact_online</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>How many people in your household can make a payment by phone themselves, without help? (0 if none)</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>आपके घर में कितने लोग बिना किसी की मदद के फ़ोन से पैसे भेज सकते हैं? (कोई नहीं तो 0)</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${hhsize}</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Cannot be more than the number of people in the household.</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>घर के लोगों की संख्या से ज़्यादा नहीं हो सकता।</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
@@ -7732,24 +7964,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>grp_H</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Module H: Health</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
@@ -7760,31 +7980,27 @@
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>intro_H</t>
+          <t>grp_H</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Now a few questions about health in your household. You may leave out any of these.</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
+          <t>Module H: Health</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -7797,36 +8013,36 @@
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>morbidity_15d</t>
+          <t>intro_H</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>In the last 15 days, was anyone in your household ill?</t>
+          <t>Now a few questions about health in your household. You may leave out any of these.</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
+          <t>अब आपके घर में सेहत के बारे में कुछ सवाल। इनमें से कोई भी सवाल आप छोड़ सकते हैं।</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
@@ -7839,22 +8055,22 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>select_one coping</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>morbidity_coping_15d</t>
+          <t>morbidity_15d</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
+          <t>In the last 15 days, was anyone in your household ill?</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
+          <t>पिछले 15 दिनों में क्या आपके घर में कोई बीमार पड़ा?</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -7864,11 +8080,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>${morbidity_15d} = 1</t>
-        </is>
-      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -7880,22 +8092,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one coping</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>morbidity_cost_15d</t>
+          <t>morbidity_coping_15d</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
+          <t>How did the household mainly cope with the cost of this: used savings; borrowed money; sold or pawned assets; cut other consumption; got help from relatives or community; or something else?</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
+          <t>इसका ख़र्च आपके घर ने मुख्य रूप से कैसे उठाया: जमा पैसे से; उधार लेकर; कुछ बेचकर या गिरवी रखकर; बाकी ख़र्च घटाकर; रिश्तेदारों या गाँव वालों की मदद से; या किसी और तरह?</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -7921,22 +8133,22 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>select_one wgdiff</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>func_limitation</t>
+          <t>morbidity_cost_15d</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Do you have difficulty walking or climbing steps?</t>
+          <t>About how much did the household spend on this in the last 15 days (medicine, doctor or clinic fees, travel for care)? (Rs)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
+          <t>पिछले 15 दिनों में इस पर घर का लगभग कितना ख़र्च हुआ (दवाई, डॉक्टर या क्लीनिक की फ़ीस, आने-जाने का ख़र्च)? (रुपये)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -7946,7 +8158,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>${morbidity_15d} = 1</t>
+        </is>
+      </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -7958,22 +8174,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one wgdiff</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>hospitalization_365d</t>
+          <t>func_limitation</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
+          <t>Do you have difficulty walking or climbing steps?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
+          <t>क्या आपको चलने या सीढ़ियाँ चढ़ने में दिक़्क़त होती है?</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -8000,17 +8216,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>health_access_barrier_3m</t>
+          <t>hospitalization_365d</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
+          <t>In the last 12 months, was anyone in your household admitted to hospital overnight?</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
+          <t>पिछले 12 महीनों में क्या आपके घर का कोई रात भर के लिए अस्पताल में भर्ती हुआ?</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
@@ -8037,17 +8253,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>child_death_5y</t>
+          <t>health_access_barrier_3m</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>In the last five years, has any child or young person under 18 in your household died?</t>
+          <t>In the last 3 months, was there a time when someone in your household needed medical care but could not get it?</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
+          <t>पिछले 3 महीनों में क्या कभी ऐसा हुआ कि आपके घर में किसी को इलाज की ज़रूरत थी पर मिल नहीं पाया?</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -8074,17 +8290,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>birth_last_5y</t>
+          <t>child_death_5y</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>In the last five years, did any woman in your household give birth?</t>
+          <t>In the last five years, has any child or young person under 18 in your household died?</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
+          <t>पिछले पाँच साल में क्या आपके घर के 18 साल से छोटे किसी बच्चे या किशोर की मृत्यु हुई?</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -8106,22 +8322,22 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>anc_4_visits</t>
+          <t>birth_last_5y</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
+          <t>In the last five years, did any woman in your household give birth?</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
+          <t>पिछले पाँच साल में क्या आपके घर की किसी महिला ने बच्चे को जन्म दिया?</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -8131,11 +8347,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>${birth_last_5y} = 1</t>
-        </is>
-      </c>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
@@ -8152,17 +8364,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>skilled_birth_attendant</t>
+          <t>anc_4_visits</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+          <t>For the most recent birth, did she have at least four check-ups before the delivery?</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+          <t>सबसे हाल के जन्म के लिए, क्या डिलीवरी से पहले उनकी कम से कम चार बार जाँच हुई थी?</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -8188,16 +8400,36 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>skilled_birth_attendant</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Was that delivery done with the help of a doctor, nurse or trained midwife?</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>क्या वह डिलीवरी डॉक्टर, नर्स या प्रशिक्षित दाई की मदद से हुई थी?</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>${birth_last_5y} = 1</t>
+        </is>
+      </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -8209,24 +8441,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>grp_I</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Module I: Food security, shocks and coping</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
@@ -8237,31 +8457,27 @@
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>intro_I</t>
+          <t>grp_I</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
+          <t>Module I: Food security, shocks and coping</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -8274,52 +8490,40 @@
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>select_multiple distress</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>distress_event_last365d</t>
+          <t>intro_I</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
+          <t>Now about food, and about any difficult times in the last year and how your household managed.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
+          <t>अब खाने के बारे में, और पिछले साल आई किसी मुश्किल के बारे में कि आपके घर ने उसे कैसे सँभाला।</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
-        </is>
-      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
@@ -8328,22 +8532,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple distress</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>shock_loss_amount</t>
+          <t>distress_event_last365d</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Thinking of whichever of those hit you hardest -- what did it cost your household in all? Count both earnings lost and money spent because of it. (Rs)</t>
+          <t>In the last 12 months, did any of these happen -- to your household, or to the Yatra route you work on? Check every one that applies.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>इनमें से जो सबसे भारी पड़ा — उससे आपके घर का कुल कितना नुक़सान हुआ? कमाई का घाटा और ख़र्च, दोनों मिलाकर। (रुपये)</t>
+          <t>पिछले 12 महीनों में इनमें से क्या-क्या हुआ — आपके घर के साथ, या जिस यात्रा मार्ग पर आप काम करते हैं उस पर? जो-जो हुआ, सब चुनिए।</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -8353,14 +8557,22 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>not(selected(., '9') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>'Nothing of this kind happened' cannot be ticked with a shock. Choose one or the other.</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
@@ -8369,22 +8581,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>select_one month</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>shock_month</t>
+          <t>shock_loss_amount</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>And in which month did that one happen?</t>
+          <t>Thinking of whichever of those hit you hardest -- what did it cost your household in all? Count both earnings lost and money spent because of it. (Rs)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>और वह किस महीने हुआ था?</t>
+          <t>इनमें से जो सबसे भारी पड़ा — उससे आपके घर का कुल कितना नुक़सान हुआ? कमाई का घाटा और ख़र्च, दोनों मिलाकर। (रुपये)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -8399,9 +8611,21 @@
           <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>. &gt;= 0</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>An amount cannot be negative.</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
@@ -8410,22 +8634,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>select_multiple coping</t>
+          <t>select_one month</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>shock_coping</t>
+          <t>shock_month</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>How did your household manage? Check every one they used.</t>
+          <t>And in which month did that one happen?</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
+          <t>और वह किस महीने हुआ था?</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -8451,22 +8675,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_multiple coping</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_yatra_wk</t>
+          <t>shock_coping</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>How did your household manage? Check every one they used.</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>आपके घर ने कैसे सँभाला? उन्होंने जो-जो किया, सब चुनिए।</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -8476,22 +8700,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 7</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>Must be between 0 and 7 days.</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>0 से 7 दिन के बीच होना चाहिए।</t>
-        </is>
-      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>not(selected(${distress_event_last365d}, '9')) and count-selected(${distress_event_last365d}) &gt; 0</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
@@ -8505,17 +8721,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>cope_less_pref_food_offseason_wk</t>
+          <t>cope_less_pref_food_yatra_wk</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -8554,17 +8770,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>cope_borrow_food_yatra_wk</t>
+          <t>cope_less_pref_food_offseason_wk</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household rely on less expensive/less preferred food? (0-7 days)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन सस्ता या कम पसंद का खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -8603,17 +8819,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>cope_borrow_food_offseason_wk</t>
+          <t>cope_borrow_food_yatra_wk</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -8652,17 +8868,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_yatra_wk</t>
+          <t>cope_borrow_food_offseason_wk</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household borrow food and/or rely on help from friends/relatives? (0-7 days)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाना उधार लिया या दोस्तों/रिश्तेदारों की मदद ली? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -8701,17 +8917,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cope_reduce_meals_offseason_wk</t>
+          <t>cope_reduce_meals_yatra_wk</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -8750,17 +8966,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_yatra_wk</t>
+          <t>cope_reduce_meals_offseason_wk</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce the number of meals eaten per day? (0-7 days)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन दिन में कम बार खाना खाया? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -8799,17 +9015,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>cope_reduce_portion_offseason_wk</t>
+          <t>cope_reduce_portion_yatra_wk</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -8848,17 +9064,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_yatra_wk</t>
+          <t>cope_reduce_portion_offseason_wk</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household reduce portion size of meals? (0-7 days)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन खाने की मात्रा घटाई? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -8897,17 +9113,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>cope_restrict_adult_offseason_wk</t>
+          <t>cope_restrict_adult_yatra_wk</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+          <t>In a normal week during the Yatra season, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+          <t>यात्रा के मौसम के आम हफ़्ते में, खाने की या खाना ख़रीदने के पैसे की कमी से निपटने के लिए आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -8941,19 +9157,47 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr"/>
-      <c r="D219" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>cope_restrict_adult_offseason_wk</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>In a normal week when the Yatra is closed, to cope with a lack of food or money to buy it, how many days did your household restrict consumption of adults/mothers in order for young children to eat? (0-7 days)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>जब यात्रा बंद रहती है, उस आम हफ़्ते में आपके घर ने कितने दिन बड़ों ने कम खाया ताकि छोटे बच्चे खा सकें? (0-7 दिन)</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H219" t="inlineStr"/>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 7</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Must be between 0 and 7 days.</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>0 से 7 दिन के बीच होना चाहिए।</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
@@ -8962,24 +9206,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>grp_J</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>Module J: Ropeway</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr"/>
@@ -8990,31 +9222,27 @@
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>intro_J</t>
+          <t>grp_J</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
+          <t>Module J: Ropeway</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -9027,36 +9255,36 @@
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>select_one stance</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ropeway_stance</t>
+          <t>intro_J</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
+          <t>Now two questions about the ropeway that has been proposed between Gaurikund and Kedarnath.</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
+          <t>अब गौरीकुंड से केदारनाथ के बीच जो रोपवे प्रस्तावित है, उस पर दो सवाल।</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G222" t="inlineStr"/>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
@@ -9069,22 +9297,22 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one stance</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>trek_dependent</t>
+          <t>ropeway_stance</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Is your main Yatra work carrying, transporting or guiding people or goods on the Gaurikund to Kedarnath trek?</t>
+          <t>A ropeway is proposed between Gaurikund and Kedarnath. Are you in favour, neutral, or against?</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+          <t>गौरीकुंड से केदारनाथ तक रोपवे बनाने की बात चल रही है। आप इसके पक्ष में हैं, बीच में हैं, या ख़िलाफ़ हैं?</t>
         </is>
       </c>
       <c r="E223" t="inlineStr"/>
@@ -9094,7 +9322,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>${site} = 1</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
@@ -9106,15 +9338,31 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>trek_dependent</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Is your main work carrying, transporting or guiding people or goods on foot along the pilgrimage trek?</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>क्या आपका मुख्य यात्रा-काम गौरीकुंड से केदारनाथ के पैदल रास्ते पर लोगों या सामान को ले जाना, पहुँचाना या रास्ता दिखाना है?</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
@@ -9127,24 +9375,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>grp_K</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr"/>
@@ -9155,31 +9391,27 @@
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>intro_K</t>
+          <t>grp_K</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
+          <t>Module K: Job quality (Apablaza et al. 2026 questions)</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -9192,36 +9424,36 @@
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>select_one jobsit</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>job_situation</t>
+          <t>intro_K</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
+          <t>Now a set of questions about the conditions of your work -- hours, pay, contract and so on. These come from a standard list used in many countries, so one or two may not fit your situation. Say so and we will move on.</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+          <t>अब आपके काम के हालात पर कुछ सवाल — घंटे, मज़दूरी, ठेका वग़ैरह। ये एक बनी-बनाई सूची से हैं जो कई देशों में इस्तेमाल होती है, इसलिए एक-दो सवाल आपकी स्थिति पर शायद ठीक न बैठें। बता दीजिएगा, हम आगे बढ़ जाएँगे।</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
@@ -9234,44 +9466,32 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>select_one jobperm</t>
+          <t>select_one jobsit</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>job_permanence</t>
+          <t>job_situation</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
+          <t>Which best describes your situation during the last month: you work for pay full-time; you work for pay part-time or do occasional jobs; you study and work; you only study; you are only being trained for work; you are retired or pensioned; you do unpaid household tasks or care for others; you are unemployed and actively looking for work; you are sick or disabled and cannot work; or none of these?</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
-        </is>
-      </c>
+          <t>पिछले महीने आपकी हालत इनमें से किससे सबसे मिलती है: पूरे समय पैसे के लिए काम; कुछ समय या कभी-कभार का काम; पढ़ाई के साथ काम; सिर्फ़ पढ़ाई; सिर्फ़ काम की ट्रेनिंग; रिटायर या पेंशन पर; घर का बिना पैसे का काम या किसी की देखभाल; काम नहीं है और ढूँढ रहे हैं; बीमारी या विकलांगता से काम नहीं कर सकते; या इनमें से कुछ नहीं?</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>${job_situation} &lt;= 3</t>
-        </is>
-      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
@@ -9283,26 +9503,34 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>select_one contract</t>
+          <t>select_one jobperm</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>contract_status</t>
+          <t>job_permanence</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
+          <t>Is your job: permanent; seasonal or temporary; occasional or casual; on probation; or fixed-term?</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
+          <t>आपका काम कैसा है: पक्का; मौसमी या कुछ समय का; कभी-कभार का; परखने की अवधि पर; या तय समय के लिए?</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Both will sound seasonal here -- the Yatra closes for everyone. Ask about WITHIN the season. One employer keeps them on for a stretch = Seasonal or temporary. They take work day by day from whoever offers it = Occasional or casual. Self-employed: answer for how their own work runs. On probation and Fixed-term are rare here; do not reach for them.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>यहाँ दोनों ही मौसमी लगेंगे — यात्रा तो सबके लिए बंद होती है। मौसम के अंदर की बात पूछिए। एक ही मालिक कुछ समय तक रखे हुए है = मौसमी या अस्थायी। जो भी काम रोज़-रोज़ मिल जाए वह कर लेते हैं = कभी-कभार या दिहाड़ी। अपना काम करने वालों के लिए: उनका अपना काम कैसे चलता है, वह देखिए। परख पर और तय अवधि वाले यहाँ बहुत कम मिलेंगे; इन्हें यूँ ही न चुनें।</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>yes</t>
@@ -9310,7 +9538,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -9324,22 +9552,22 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one contract</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>workplace_registered</t>
+          <t>contract_status</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
+          <t>Do you have a signed contract? Yes, signed; yes but not yet signed; no contract.</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
+          <t>क्या आपका दस्तख़त किया हुआ अनुबंध (कॉन्ट्रैक्ट) है? हाँ, दस्तख़त किया; हाँ, पर अभी दस्तख़त नहीं हुआ; कोई अनुबंध नहीं।</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -9351,7 +9579,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -9365,22 +9593,22 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>select_one pension</t>
+          <t>select_one yn</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>pension_contrib</t>
+          <t>workplace_registered</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
+          <t>Is your workplace or business registered, for example with a taxpayer or GST number, a shop or trade licence, the Yatra registration, or a union?</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
+          <t>क्या आपका काम या धंधा रजिस्टर्ड है, जैसे GST या टैक्स नंबर, दुकान का लाइसेंस, यात्रा का रजिस्ट्रेशन, या कोई यूनियन?</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -9392,7 +9620,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -9406,22 +9634,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>select_one workins</t>
+          <t>select_one pension</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>work_health_ins</t>
+          <t>pension_contrib</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
+          <t>Do you contribute to any pension system? Yes, the employer deducts it; yes, voluntarily; no.</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
+          <t>क्या आप किसी पेंशन में पैसा डालते हैं? हाँ, मालिक तनख़्वाह से काटता है; हाँ, अपनी मर्ज़ी से डालते हैं; नहीं।</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9447,22 +9675,22 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>select_one workins</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>leave_rights</t>
+          <t>work_health_ins</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
+          <t>Do you have health insurance through your work? Yes; only private or other insurance; none; don't know.</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
+          <t>क्या काम की तरफ़ से आपका स्वास्थ्य बीमा है? हाँ; सिर्फ़ अपना या कोई और बीमा; कोई नहीं; पता नहीं।</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -9493,17 +9721,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>injured_ever</t>
+          <t>leave_rights</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Have you ever been physically injured at your workplace?</t>
+          <t>Do you have the right to paid holiday, sick or maternity leave?</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
+          <t>क्या आपको पैसे वाली छुट्टी मिलती है — त्योहार, बीमारी या ज़च्चगी की?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -9515,7 +9743,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 3</t>
+          <t>(${job_situation} &lt;= 3) and (${employment_type} = 3 or ${employment_type} = 4)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -9534,17 +9762,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>workplace_injury_12m</t>
+          <t>injured_ever</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
+          <t>Have you ever been physically injured at your workplace?</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
+          <t>क्या आपको कभी काम की जगह पर चोट लगी है?</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -9575,17 +9803,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>wants_more_work</t>
+          <t>workplace_injury_12m</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Would you like to work more hours than you do?</t>
+          <t>In the last 12 months, was anyone physically injured or killed at your workplace because of work?</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
+          <t>पिछले 12 महीनों में क्या आपके काम की जगह पर काम की वजह से किसी को चोट लगी या किसी की मौत हुई?</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -9597,7 +9825,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>${job_situation} &lt;= 7</t>
+          <t>${job_situation} &lt;= 3</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -9611,22 +9839,22 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one yndk</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>more_hours_day</t>
+          <t>wants_more_work</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>On a working day, how many MORE hours would you like to work?</t>
+          <t>Would you like to work more hours than you do?</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
+          <t>क्या आप अभी से ज़्यादा घंटे काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -9638,7 +9866,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+          <t>${job_situation} &lt;= 7</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -9657,17 +9885,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>months_looked_for_work</t>
+          <t>more_hours_day</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
+          <t>On a working day, how many MORE hours would you like to work?</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
+          <t>काम के दिन में आप कितने घंटे और काम करना चाहेंगे?</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -9679,12 +9907,24 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
+          <t>${wants_more_work} = 1 or ${job_situation} = 8</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . + ${hours_day_yatra} &lt;= 18</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Hours wanted plus hours already worked cannot exceed 18 in a day.</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
@@ -9693,22 +9933,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>select_one yndk</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>first_job_ever</t>
+          <t>months_looked_for_work</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Was your current work the first paid job you ever had?</t>
+          <t>Across the months when you had no paid work, about how many MONTHS in total were you looking for work?</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+          <t>जिन महीनों में आपके पास कोई पैसे वाला काम नहीं था, उनमें कुल मिलाकर लगभग कितने महीने आप काम ढूँढते रहे?</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -9718,7 +9958,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>${calc_months_no_work} &gt; 0 or ${job_situation} = 8</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
@@ -9730,15 +9974,31 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
+          <t>select_one yndk</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>first_job_ever</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Was your current work the first paid job you ever had?</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>क्या यह आपका पहला पैसे वाला काम है?</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
@@ -9751,24 +10011,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>begin_group</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>grp_L</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Module L: Tasks and skills (short block)</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
@@ -9779,31 +10027,27 @@
       <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>intro_L</t>
+          <t>grp_L</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
+          <t>Module L: Tasks and skills (short block)</t>
         </is>
       </c>
       <c r="E242" t="inlineStr"/>
@@ -9816,36 +10060,36 @@
       <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>select_one task3</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>tk_load</t>
+          <t>intro_L</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
+          <t>Last, I will read out some kinds of work-tasks and ask whether you do them. There is no right or wrong answer -- we are trying to understand what skills the work here actually uses.</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>आख़िर में, मैं कुछ तरह के कामों के नाम पढ़ूँगा और पूछूँगा कि आप वे करते हैं या नहीं। इसमें सही या ग़लत जवाब कुछ नहीं है — हम बस यह समझना चाहते हैं कि यहाँ के काम में कौन-कौन से हुनर लगते हैं।</t>
         </is>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
@@ -9863,17 +10107,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tk_drive</t>
+          <t>tk_load</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you drive a motor vehicle? </t>
+          <t xml:space="preserve">Do you load, unload, stack or count goods? </t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान चढ़ाना-उतारना, लगाना या गिनना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -9900,17 +10144,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>tk_engine</t>
+          <t>tk_drive</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you operate an engine or machine? </t>
+          <t xml:space="preserve">Do you drive a motor vehicle? </t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप गाड़ी चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -9937,17 +10181,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>tk_electric</t>
+          <t>tk_engine</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you do electrical or wiring work? </t>
+          <t xml:space="preserve">Do you operate an engine or machine? </t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप इंजन या मशीन चलाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -9974,17 +10218,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>tk_safety</t>
+          <t>tk_electric</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
+          <t xml:space="preserve">Do you do electrical or wiring work? </t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप बिजली या तार का काम करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -10011,17 +10255,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>tk_sell</t>
+          <t>tk_safety</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you sell goods or services? </t>
+          <t xml:space="preserve">Do you check equipment or the route for safety? </t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या रास्ते की सुरक्षा जाँचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -10048,17 +10292,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>tk_cash</t>
+          <t>tk_sell</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you handle cash and payments? </t>
+          <t xml:space="preserve">Do you sell goods or services? </t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप सामान या सेवा बेचना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -10085,17 +10329,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>tk_cook</t>
+          <t>tk_cash</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
+          <t xml:space="preserve">Do you handle cash and payments? </t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप पैसे और भुगतान सँभालना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -10122,17 +10366,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>tk_serve</t>
+          <t>tk_cook</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you serve guests or customers? </t>
+          <t xml:space="preserve">Do you cook or prepare food or drink? </t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप खाना या पीने की चीज़ बनाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -10159,17 +10403,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>tk_clean</t>
+          <t>tk_serve</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you clean rooms or public areas? </t>
+          <t xml:space="preserve">Do you serve guests or customers? </t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप मेहमानों या ग्राहकों की सेवा करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -10196,17 +10440,17 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>tk_guide</t>
+          <t>tk_clean</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
+          <t xml:space="preserve">Do you clean rooms or public areas? </t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप कमरे या सार्वजनिक जगह साफ़ करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -10233,17 +10477,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>tk_coord</t>
+          <t>tk_guide</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
+          <t xml:space="preserve">Do you guide or explain things to visitors? </t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
+          <t>क्या आप आने वालों को रास्ता या बात समझाना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
@@ -10265,22 +10509,22 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>select_one yn</t>
+          <t>select_one task3</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>drove_twowheeler</t>
+          <t>tk_coord</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
+          <t xml:space="preserve">Do you coordinate work by phone, radio or signals? </t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
+          <t>क्या आप फ़ोन, रेडियो या इशारों से दूसरों के साथ तालमेल करना का काम करते हैं? (1 अपने मुख्य यात्रा-काम में नियमित; 2 मुख्य काम में नहीं, पर पहले कहीं और किया है; 3 कभी नहीं)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -10290,11 +10534,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
-        </is>
-      </c>
+      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10311,17 +10551,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>drove_car</t>
+          <t>drove_twowheeler</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>... a car or jeep?</t>
+          <t>Have you ever driven a motorcycle or scooter, with or without a licence?</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>...कार या जीप?</t>
+          <t>क्या आपने कभी मोटरसाइकिल या स्कूटर चलाई है, लाइसेंस हो या न हो?</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -10352,17 +10592,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>drove_heavy</t>
+          <t>drove_car</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>... a truck or bus?</t>
+          <t>... a car or jeep?</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>...ट्रक या बस?</t>
+          <t>...कार या जीप?</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -10393,17 +10633,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>read_at_work</t>
+          <t>drove_heavy</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
+          <t>... a truck or bus?</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
+          <t>...ट्रक या बस?</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -10413,7 +10653,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr"/>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>${tk_drive} = 1 or ${tk_drive} = 2</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
@@ -10430,17 +10674,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>calc_at_work</t>
+          <t>read_at_work</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>In your work, do you work out prices or costs?</t>
+          <t>In your work, do you read anything (notes, rate lists, tickets, messages)?</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+          <t>अपने काम में क्या आप कुछ पढ़ते हैं (पर्ची, रेट लिस्ट, टिकट, मैसेज)?</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -10462,15 +10706,31 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
+          <t>select_one yn</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>calc_at_work</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>In your work, do you work out prices or costs?</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>अपने काम में क्या आप दाम या ख़र्चा जोड़ते-घटाते हैं?</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
@@ -10500,6 +10760,27 @@
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -2962,11 +2962,7 @@
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O242"/>
+  <dimension ref="A1:O236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,7 +768,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>'2026-10-13.f7c13e'</t>
+          <t>'2026-10-13.d38003'</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -9764,22 +9764,22 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>select_one permdk</t>
+          <t>select_one cpruse</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>cpr_permitted</t>
+          <t>cpr_home_access</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Where you work, is it allowed to take firewood, fodder or forest produce from the forest or common land? Ask what they understand the rule to be; do not correct them.</t>
+          <t>At your usual home village -- not here on the Yatra route -- does your household get fuel wood, fodder or grazing, from your OWN land or from common or forest land, without having to buy it?</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>आप जहाँ काम करते हैं, वहाँ जंगल या सार्वजनिक ज़मीन से लकड़ी, चारा या जंगल की चीज़ें लेना मना है या नहीं? वे जो नियम समझते हैं वही पूछें; उन्हें सुधारें नहीं।</t>
+          <t>आपके असली घर पर — यहाँ यात्रा के रास्ते पर नहीं — क्या आपके घर को लकड़ी, चारा या जानवर चराने की जगह, अपनी ज़मीन से या साझा या जंगल की ज़मीन से, बिना पैसे दिए मिल जाती है?</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -9802,17 +9802,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>cpr_firewood</t>
+          <t>cpr_worksite_use</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect firewood or dead wood from common land or forest in the Yatra region or workplace region?</t>
+          <t>Along your route or near your worksite, do you or any animal of yours or of anyone staying with you here get grazing or fodder from common land, without paying, in this Yatra season or last Yatra season?</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन या जंगल से लकड़ी या सूखी टहनियाँ इकट्ठी कीं?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपको या आपके किसी जानवर को, या आपके साथ यहाँ रहने वाले किसी को, रास्ते पर या काम की जगह के पास साझा ज़मीन से बिना पैसे दिए चारा या चरागाह मिली?</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -9830,22 +9830,22 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>select_one cpruse</t>
+          <t>select_one cprchange</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>cpr_fodder</t>
+          <t>cpr_access_change</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here cut grass or fodder from common land in the Yatra region or workplace region?</t>
+          <t>In this Yatra season or last Yatra season, has it gotten harder, easier, or stayed the same to use common land, forest or pasture near your worksite without being stopped or asked to pay?</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह की साझा ज़मीन से घास या चारा काटा?</t>
+          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, अपने काम की जगह के पास साझा ज़मीन, जंगल या चरागाह का बिना रोक-टोक या पैसे दिए इस्तेमाल करना — पहले से मुश्किल हुआ है, आसान हुआ है, या वैसा ही है?</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -9863,24 +9863,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>select_one cpruse</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>cpr_forest_produce</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>In this Yatra season or last Yatra season, did you or anyone staying with you here collect herbs, mushrooms or wild fruit from the forest in the Yatra region or workplace region?</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपने या आपके साथ यहाँ रहने वाले किसी ने यात्रा क्षेत्र या काम की जगह के जंगल से जड़ी-बूटी, मशरूम या जंगली फल इकट्ठे किए?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
@@ -9896,24 +9884,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>select_one cpruse</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>cpr_grazing</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>In this Yatra season or last Yatra season, did any animal of yours or of anyone staying with you here graze on common pasture in the Yatra region or workplace region?</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपका या आपके साथ यहाँ रहने वाले किसी का कोई जानवर यात्रा क्षेत्र या काम की जगह की साझा चरागाह में चरा?</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
@@ -9926,180 +9902,6 @@
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>select_one yndk</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>cpr_restricted</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>In this Yatra season or last Yatra season, has anyone you or someone staying with you here been stopped from using a common forest, pasture or path, or been asked to pay to use it, in the Yatra region or workplace region?</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या आपको या आपके साथ यहाँ रहने वाले किसी को यात्रा क्षेत्र या काम की जगह में साझा जंगल, चरागाह या रास्ते के इस्तेमाल से रोका गया, या इसके लिए पैसे देने को कहा गया?</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
-      <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>select_one yndk</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>cpr_lost_access</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>In this Yatra season or last Yatra season, has a common place you used to collect from or graze on been closed, because of a landslide, flood, road or bridge damage, or construction work, in the Yatra region or workplace region?</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>इस यात्रा सीज़न या पिछले यात्रा सीज़न में, क्या कोई साझा जगह, जहाँ आप पहले लकड़ी, घास या चारा लेते थे, भूस्खलन, बाढ़, सड़क या पुल टूटने, या निर्माण कार्य की वजह से बंद हो गई?</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>select_one cprwater</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>cpr_water_route</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>On your route or near your worksite, can you use a common water source (spring, tap or stream) without paying?</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>रास्ते पर या काम की जगह के पास, क्या आप कोई साझा पानी का स्रोत (झरना, नल या नदी-नाला) बिना पैसे दिए इस्तेमाल कर सकते हैं?</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
-      <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>select_one cprgov</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>cpr_governance</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>In the Yatra region or workplace region, who decides who may use the common land and forest? Ask and code what they name; do not read the list.</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>यात्रा क्षेत्र या काम की जगह की साझा ज़मीन और जंगल का फ़ैसला कौन करता है, कि कौन उसका इस्तेमाल कर सकता है? जो नाम लें वही लिख लें; सूची न पढ़ें।</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10111,7 +9913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E342"/>
+  <dimension ref="A1:E333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11248,7 +11050,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cprgov</t>
+          <t>cprchange</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -11256,12 +11058,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Village head or panchayat</t>
+          <t>Harder now</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>गाँव के प्रधान या पंचायत</t>
+          <t>अब मुश्किल है</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -11271,7 +11073,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cprgov</t>
+          <t>cprchange</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -11279,12 +11081,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forest department</t>
+          <t>Easier now</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>वन विभाग</t>
+          <t>अब आसान है</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -11294,7 +11096,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cprgov</t>
+          <t>cprchange</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -11302,12 +11104,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Local committee or community group</t>
+          <t>Same as before</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>गाँव या समूह की समिति</t>
+          <t>पहले जैसा ही है</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -11317,47 +11119,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>cprgov</t>
+          <t>cprchange</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nobody decides; it is open to all</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>कोई तय नहीं करता, सब के लिए खुला है</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>cprgov</t>
+          <t>cpruse</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -11367,20 +11169,20 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>नहीं</t>
+          <t>हाँ</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -11390,20 +11192,20 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No, it is not allowed here</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>हाँ</t>
+          <t>नहीं, यहाँ इसकी मनाही है</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -11413,135 +11215,135 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>No, it is not allowed here</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>नहीं, यहाँ इसकी मनाही है</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cpruse</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Nationalised or public-sector bank</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>सरकारी बैंक</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cprwater</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yes, free to use</t>
+          <t>Private bank</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>हाँ, बिना पैसे के</t>
+          <t>प्राइवेट बैंक</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cprwater</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A source exists but we must pay</t>
+          <t>Cooperative bank or RRB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>स्रोत है, पर पैसे देने पड़ते हैं</t>
+          <t>सहकारी बैंक या ग्रामीण बैंक</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cprwater</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>No source nearby</t>
+          <t>Microfinance institution or SHG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>पास में कोई स्रोत नहीं है</t>
+          <t>माइक्रोफ़ाइनेंस या स्वयं सहायता समूह</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cprwater</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Moneylender</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>साहूकार</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>97</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -11551,20 +11353,20 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nationalised or public-sector bank</t>
+          <t>Relative or friend</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>सरकारी बैंक</t>
+          <t>रिश्तेदार या दोस्त</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -11574,20 +11376,20 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Private bank</t>
+          <t>Employer or contractor (advance)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>प्राइवेट बैंक</t>
+          <t>मालिक या ठेकेदार (पेशगी)</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -11597,135 +11399,135 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cooperative bank or RRB</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>सहकारी बैंक या ग्रामीण बैंक</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Microfinance institution or SHG</t>
+          <t>Nothing of this kind happened</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>माइक्रोफ़ाइनेंस या स्वयं सहायता समूह</t>
+          <t>ऐसा कुछ नहीं हुआ</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moneylender</t>
+          <t>Serious illness or death of an earning member</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>साहूकार</t>
+          <t>कमाने वाले की गंभीर बीमारी या मौत</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Relative or friend</t>
+          <t>Crop failure or livestock loss</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>रिश्तेदार या दोस्त</t>
+          <t>फ़सल या जानवर का नुक़सान</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Employer or contractor (advance)</t>
+          <t>Damage from a natural disaster (flood, landslide, fire)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>मालिक या ठेकेदार (पेशगी)</t>
+          <t>किसी आपदा से नुक़सान (बाढ़, भूस्खलन, आग)</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>distress</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Loss of business, goods or assets</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>धंधे, सामान या संपत्ति का नुक़सान</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -11735,20 +11537,20 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nothing of this kind happened</t>
+          <t>Road or bridge blocked, route closed</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ऐसा कुछ नहीं हुआ</t>
+          <t>रास्ता या पुल बंद हो गया</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -11758,20 +11560,20 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Serious illness or death of an earning member</t>
+          <t>Yatra stopped early or badly disrupted</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>कमाने वाले की गंभीर बीमारी या मौत</t>
+          <t>यात्रा जल्दी बंद हुई या बुरी तरह बाधित हुई</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -11781,20 +11583,20 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Crop failure or livestock loss</t>
+          <t>Sharp fall in customers or prices</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>फ़सल या जानवर का नुक़सान</t>
+          <t>ग्राहक या दाम बहुत गिर गए</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
@@ -11804,135 +11606,135 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Damage from a natural disaster (flood, landslide, fire)</t>
+          <t>Lost the work or the work stopped</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>किसी आपदा से नुक़सान (बाढ़, भूस्खलन, आग)</t>
+          <t>काम छूट गया या काम बंद हो गया</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>distress</t>
+          <t>earnrange</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Loss of business, goods or assets</t>
+          <t>Under Rs 5,000</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>धंधे, सामान या संपत्ति का नुक़सान</t>
+          <t>5,000 रुपये से कम</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>distress</t>
+          <t>earnrange</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Road or bridge blocked, route closed</t>
+          <t>Rs 5,000 to 10,000</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>रास्ता या पुल बंद हो गया</t>
+          <t>5,000 से 10,000</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>distress</t>
+          <t>earnrange</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yatra stopped early or badly disrupted</t>
+          <t>Rs 10,000 to 20,000</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>यात्रा जल्दी बंद हुई या बुरी तरह बाधित हुई</t>
+          <t>10,000 से 20,000</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>distress</t>
+          <t>earnrange</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sharp fall in customers or prices</t>
+          <t>Rs 20,000 to 35,000</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ग्राहक या दाम बहुत गिर गए</t>
+          <t>20,000 से 35,000</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>distress</t>
+          <t>earnrange</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lost the work or the work stopped</t>
+          <t>Rs 35,000 to 50,000</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>काम छूट गया या काम बंद हो गया</t>
+          <t>35,000 से 50,000</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -11942,20 +11744,20 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Under Rs 5,000</t>
+          <t>Rs 50,000 or more</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5,000 रुपये से कम</t>
+          <t>50,000 या ज़्यादा</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -11965,141 +11767,141 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rs 5,000 to 10,000</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5,000 से 10,000</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>earnrange</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rs 10,000 to 20,000</t>
+          <t>No formal education</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10,000 से 20,000</t>
+          <t>बिल्कुल नहीं पढ़े</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>earnrange</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rs 20,000 to 35,000</t>
+          <t>Some schooling, did not complete primary</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20,000 से 35,000</t>
+          <t>थोड़ा पढ़े, प्राइमरी पूरी नहीं</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>earnrange</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rs 35,000 to 50,000</t>
+          <t>Completed primary but not secondary</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>35,000 से 50,000</t>
+          <t>प्राइमरी पूरी, दसवीं नहीं</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>earnrange</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rs 50,000 or more</t>
+          <t>Completed secondary or higher</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>50,000 या ज़्यादा</t>
+          <t>दसवीं या उससे ज़्यादा</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>earnrange</t>
+          <t>edu2</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -12107,12 +11909,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>No formal education</t>
+          <t>Own-account (self-employed, no hired workers)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>बिल्कुल नहीं पढ़े</t>
+          <t>अपना काम, कोई नौकर नहीं</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -12122,7 +11924,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -12130,12 +11932,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Some schooling, did not complete primary</t>
+          <t>Employer/business owner (self-employed)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>थोड़ा पढ़े, प्राइमरी पूरी नहीं</t>
+          <t>मालिक, दूसरों को काम पर रखते हैं</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -12145,7 +11947,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -12153,12 +11955,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Completed primary but not secondary</t>
+          <t>Regular wage or salary</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>प्राइमरी पूरी, दसवीं नहीं</t>
+          <t>महीने की पक्की तनख़्वाह</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -12168,7 +11970,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -12176,12 +11978,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Completed secondary or higher</t>
+          <t>Casual or daily wage labour</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>दसवीं या उससे ज़्यादा</t>
+          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -12191,30 +11993,30 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>edu2</t>
+          <t>emptype</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Unpaid family worker</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>घर के काम में बिना पैसे के हाथ बँटाते हैं</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -12222,12 +12024,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Own-account (self-employed, no hired workers)</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>अपना काम, कोई नौकर नहीं</t>
+          <t>रमन</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -12237,7 +12039,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -12245,12 +12047,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Employer/business owner (self-employed)</t>
+          <t>Rishit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>मालिक, दूसरों को काम पर रखते हैं</t>
+          <t>ऋषित</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -12260,7 +12062,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -12268,12 +12070,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Regular wage or salary</t>
+          <t>Tanmay</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>महीने की पक्की तनख़्वाह</t>
+          <t>तन्मय</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -12283,7 +12085,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -12291,12 +12093,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Casual or daily wage labour</t>
+          <t>Anuj</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
+          <t>अनुज</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -12306,116 +12108,116 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>emptype</t>
+          <t>fies5</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Unpaid family worker</t>
+          <t>Had to skip a meal</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>घर के काम में बिना पैसे के हाथ बँटाते हैं</t>
+          <t>खाना छोड़ना पड़ा</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>fies5</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Ate less than you thought you should</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>रमन</t>
+          <t>जितना चाहिए उससे कम खाया</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>fies5</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rishit</t>
+          <t>Your household ran out of food</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ऋषित</t>
+          <t>घर में खाना ख़त्म हो गया</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>fies5</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tanmay</t>
+          <t>Were hungry but did not eat</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>तन्मय</t>
+          <t>भूख लगी पर खाया नहीं</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>fies5</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Anuj</t>
+          <t>Went a whole day without eating</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>अनुज</t>
+          <t>पूरा दिन कुछ नहीं खाया</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
@@ -12425,204 +12227,204 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Had to skip a meal</t>
+          <t>None of these happened</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>खाना छोड़ना पड़ा</t>
+          <t>ऐसा कुछ नहीं हुआ</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>fies5</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ate less than you thought you should</t>
+          <t>Mud/kaccha</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>जितना चाहिए उससे कम खाया</t>
+          <t>मिट्टी/कच्चा</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>fies5</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Your household ran out of food</t>
+          <t>Cement/mud-cement</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>घर में खाना ख़त्म हो गया</t>
+          <t>सीमेंट या सीमेंट-मिट्टी</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>fies5</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Were hungry but did not eat</t>
+          <t>Tile/mosaic/marble</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>भूख लगी पर खाया नहीं</t>
+          <t>टाइल/मोज़ेक/मार्बल</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>fies5</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Went a whole day without eating</t>
+          <t>LPG or cylinder gas</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>पूरा दिन कुछ नहीं खाया</t>
+          <t>LPG या सिलेंडर गैस</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>fies5</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>None of these happened</t>
+          <t>Piped natural gas</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ऐसा कुछ नहीं हुआ</t>
+          <t>पाइप से आने वाली गैस</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mud/kaccha</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>मिट्टी/कच्चा</t>
+          <t>बिजली</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cement/mud-cement</t>
+          <t>Biogas (gobar gas plant)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>सीमेंट या सीमेंट-मिट्टी</t>
+          <t>गोबर गैस (बायोगैस)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>fuel</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tile/mosaic/marble</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>टाइल/मोज़ेक/मार्बल</t>
+          <t>मिट्टी का तेल</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -12632,20 +12434,20 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LPG or cylinder gas</t>
+          <t>Firewood</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LPG या सिलेंडर गैस</t>
+          <t>लकड़ी</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111">
@@ -12655,20 +12457,20 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Piped natural gas</t>
+          <t>Dung cakes (gobar)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>पाइप से आने वाली गैस</t>
+          <t>गोबर के उपले</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
@@ -12678,20 +12480,20 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Crop residue, straw or shrubs</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>बिजली</t>
+          <t>फ़सल के डंठल, पुआल या झाड़ियाँ</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
@@ -12701,20 +12503,20 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Biogas (gobar gas plant)</t>
+          <t>Charcoal</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>गोबर गैस (बायोगैस)</t>
+          <t>लकड़ी का कोयला</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
@@ -12724,135 +12526,135 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>Coal or lignite</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>मिट्टी का तेल</t>
+          <t>पत्थर का कोयला</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Firewood</t>
+          <t>Self (respondent is the head)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>लकड़ी</t>
+          <t>मैं खुद मुखिया हूँ</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dung cakes (gobar)</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>गोबर के उपले</t>
+          <t>पति</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Crop residue, straw or shrubs</t>
+          <t>Wife</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>फ़सल के डंठल, पुआल या झाड़ियाँ</t>
+          <t>पत्नी</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charcoal</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>लकड़ी का कोयला</t>
+          <t>पिता</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>fuel</t>
+          <t>hohrel</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coal or lignite</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>पत्थर का कोयला</t>
+          <t>माता</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -12862,20 +12664,20 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Self (respondent is the head)</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>मैं खुद मुखिया हूँ</t>
+          <t>बेटा</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121">
@@ -12885,20 +12687,20 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Daughter</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>पति</t>
+          <t>बेटी</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -12908,20 +12710,20 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wife</t>
+          <t>Brother</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>पत्नी</t>
+          <t>भाई</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -12931,20 +12733,20 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>पिता</t>
+          <t>बहन</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124">
@@ -12954,20 +12756,20 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Other male relative</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>माता</t>
+          <t>कोई और पुरुष रिश्तेदार</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
@@ -12977,20 +12779,20 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Other female relative</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>बेटा</t>
+          <t>कोई और महिला रिश्तेदार</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
@@ -13000,20 +12802,20 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Daughter</t>
+          <t>Other, non-relative (male)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>बेटी</t>
+          <t>रिश्तेदार नहीं, पुरुष</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
@@ -13023,210 +12825,210 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Other, non-relative (female)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>भाई</t>
+          <t>रिश्तेदार नहीं, महिला</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>instypes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Health insurance or scheme (incl. government)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>बहन</t>
+          <t>स्वास्थ्य बीमा या योजना (सरकारी भी)</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>instypes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Other male relative</t>
+          <t>Life insurance</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>कोई और पुरुष रिश्तेदार</t>
+          <t>जीवन बीमा</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>instypes</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Other female relative</t>
+          <t>Crop insurance</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>कोई और महिला रिश्तेदार</t>
+          <t>फ़सल बीमा</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Other, non-relative (male)</t>
+          <t>Nali</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, पुरुष</t>
+          <t>नाली</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>hohrel</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Other, non-relative (female)</t>
+          <t>Bigha</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>रिश्तेदार नहीं, महिला</t>
+          <t>बीघा</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>instypes</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Health insurance or scheme (incl. government)</t>
+          <t>Acres</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>स्वास्थ्य बीमा या योजना (सरकारी भी)</t>
+          <t>एकड़</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>instypes</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Life insurance</t>
+          <t>Hectares</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>जीवन बीमा</t>
+          <t>हेक्टेयर</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>instypes</t>
+          <t>landunit</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Crop insurance</t>
+          <t>No land</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>फ़सल बीमा</t>
+          <t>ज़मीन नहीं है</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -13234,12 +13036,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nali</t>
+          <t>Cows or buffaloes</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>नाली</t>
+          <t>गाय या भैंस</t>
         </is>
       </c>
       <c r="E136" t="n">
@@ -13249,7 +13051,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -13257,12 +13059,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bigha</t>
+          <t>Goats or sheep</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>बीघा</t>
+          <t>बकरी या भेड़</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -13272,7 +13074,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>livestock</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -13280,12 +13082,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Acres</t>
+          <t>Ponies or mules</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>एकड़</t>
+          <t>घोड़े या खच्चर</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -13295,116 +13097,116 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hectares</t>
+          <t>Medical or hospital costs</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>हेक्टेयर</t>
+          <t>इलाज या अस्पताल का ख़र्च</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>landunit</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>No land</t>
+          <t>Buying an animal, vehicle or equipment for work</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ज़मीन नहीं है</t>
+          <t>काम के लिए जानवर, गाड़ी या औज़ार ख़रीदने</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>livestock</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cows or buffaloes</t>
+          <t>Shop stock or business</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>गाय या भैंस</t>
+          <t>दुकान का सामान या धंधा</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>livestock</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Goats or sheep</t>
+          <t>Food or daily household needs</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>बकरी या भेड़</t>
+          <t>खाने या घर की रोज़ की ज़रूरत</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>livestock</t>
+          <t>loanpurpose</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ponies or mules</t>
+          <t>A wedding, funeral or ceremony</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>घोड़े या खच्चर</t>
+          <t>शादी, मृत्यु-भोज या कोई समारोह</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
@@ -13414,20 +13216,20 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Medical or hospital costs</t>
+          <t>House building or repair</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>इलाज या अस्पताल का ख़र्च</t>
+          <t>मकान बनाने या मरम्मत</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
@@ -13437,20 +13239,20 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Buying an animal, vehicle or equipment for work</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>काम के लिए जानवर, गाड़ी या औज़ार ख़रीदने</t>
+          <t>पढ़ाई</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
@@ -13460,20 +13262,20 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Shop stock or business</t>
+          <t>Repaying another loan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>दुकान का सामान या धंधा</t>
+          <t>पुराना क़र्ज़ चुकाने</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147">
@@ -13483,204 +13285,204 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Food or daily household needs</t>
+          <t>Something else</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>खाने या घर की रोज़ की ज़रूरत</t>
+          <t>कोई और काम</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>A wedding, funeral or ceremony</t>
+          <t>Currently married</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>शादी, मृत्यु-भोज या कोई समारोह</t>
+          <t>शादीशुदा</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>House building or repair</t>
+          <t>Never married</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>मकान बनाने या मरम्मत</t>
+          <t>शादी नहीं हुई</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>marital</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Widowed/divorced/separated</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>पढ़ाई</t>
+          <t>विधवा/विधुर या अलग</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Repaying another loan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>पुराना क़र्ज़ चुकाने</t>
+          <t>जनवरी</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>loanpurpose</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Something else</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>कोई और काम</t>
+          <t>फ़रवरी</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Currently married</t>
+          <t>March</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>शादीशुदा</t>
+          <t>मार्च</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Never married</t>
+          <t>April</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>शादी नहीं हुई</t>
+          <t>अप्रैल</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>marital</t>
+          <t>month</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Widowed/divorced/separated</t>
+          <t>May</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>विधवा/विधुर या अलग</t>
+          <t>मई</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
@@ -13690,20 +13492,20 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>June</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>जनवरी</t>
+          <t>जून</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
@@ -13713,20 +13515,20 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>July</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>फ़रवरी</t>
+          <t>जुलाई</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158">
@@ -13736,20 +13538,20 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>August</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>मार्च</t>
+          <t>अगस्त</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159">
@@ -13759,20 +13561,20 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>September</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>अप्रैल</t>
+          <t>सितंबर</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -13782,20 +13584,20 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>October</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>मई</t>
+          <t>अक्टूबर</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161">
@@ -13805,20 +13607,20 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>जून</t>
+          <t>नवंबर</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162">
@@ -13828,135 +13630,135 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>जुलाई</t>
+          <t>दिसंबर</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Garhwali</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>अगस्त</t>
+          <t>गढ़वाली</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>Kumaoni</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>सितंबर</t>
+          <t>कुमाऊँनी</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>October</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>अक्टूबर</t>
+          <t>हिंदी</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>November</t>
+          <t>Nepali</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>नवंबर</t>
+          <t>नेपाली</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>nativelang</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>December</t>
+          <t>Bhojpuri</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>दिसंबर</t>
+          <t>भोजपुरी</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -13966,20 +13768,20 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Garhwali</t>
+          <t>Assamese</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>गढ़वाली</t>
+          <t>असमिया</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169">
@@ -13989,20 +13791,20 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kumaoni</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>कुमाऊँनी</t>
+          <t>बांग्ला</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -14012,20 +13814,20 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Bodo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>हिंदी</t>
+          <t>बोडो</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171">
@@ -14035,20 +13837,20 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nepali</t>
+          <t>Dogri</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>नेपाली</t>
+          <t>डोगरी</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -14058,20 +13860,20 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bhojpuri</t>
+          <t>Gujarati</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>भोजपुरी</t>
+          <t>गुजराती</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173">
@@ -14081,20 +13883,20 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Assamese</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>असमिया</t>
+          <t>कन्नड़</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174">
@@ -14104,20 +13906,20 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Kashmiri</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>बांग्ला</t>
+          <t>कश्मीरी</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175">
@@ -14127,20 +13929,20 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bodo</t>
+          <t>Konkani</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>बोडो</t>
+          <t>कोंकणी</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -14150,20 +13952,20 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Dogri</t>
+          <t>Maithili</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>डोगरी</t>
+          <t>मैथिली</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
@@ -14173,20 +13975,20 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Gujarati</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>गुजराती</t>
+          <t>मलयालम</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178">
@@ -14196,20 +13998,20 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Manipuri (Meitei)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>कन्नड़</t>
+          <t>मणिपुरी (मैतेई)</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179">
@@ -14219,20 +14021,20 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Kashmiri</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>कश्मीरी</t>
+          <t>मराठी</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="180">
@@ -14242,20 +14044,20 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Konkani</t>
+          <t>Odia</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>कोंकणी</t>
+          <t>ओड़िया</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="181">
@@ -14265,20 +14067,20 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Maithili</t>
+          <t>Punjabi</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>मैथिली</t>
+          <t>पंजाबी</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182">
@@ -14288,20 +14090,20 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>मलयालम</t>
+          <t>संस्कृत</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183">
@@ -14311,20 +14113,20 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Manipuri (Meitei)</t>
+          <t>Santali</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>मणिपुरी (मैतेई)</t>
+          <t>संताली</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="184">
@@ -14334,20 +14136,20 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Marathi</t>
+          <t>Sindhi</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>मराठी</t>
+          <t>सिंधी</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185">
@@ -14357,20 +14159,20 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Odia</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ओड़िया</t>
+          <t>तमिल</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186">
@@ -14380,20 +14182,20 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Punjabi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>पंजाबी</t>
+          <t>तेलुगु</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="187">
@@ -14403,20 +14205,20 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Urdu</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>संस्कृत</t>
+          <t>उर्दू</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="188">
@@ -14426,20 +14228,20 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Santali</t>
+          <t>Other Indian language</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>संताली</t>
+          <t>कोई और भारतीय भाषा</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="189">
@@ -14449,227 +14251,227 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sindhi</t>
+          <t>Other / foreign language</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>सिंधी</t>
+          <t>कोई और / विदेशी भाषा</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsenv</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Normal crowd, normal weather</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>तमिल</t>
+          <t>भीड़ और मौसम सामान्य</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsenv</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>High crowd or peak hours</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>तेलुगु</t>
+          <t>ज़्यादा भीड़ या भीड़ का समय</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsenv</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Rain or extreme weather</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>उर्दू</t>
+          <t>बारिश या बहुत ख़राब मौसम</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>obsenv</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Other Indian language</t>
+          <t>Both high crowd and bad weather</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>कोई और भारतीय भाषा</t>
+          <t>भीड़ भी ज़्यादा और मौसम भी ख़राब</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>nativelang</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Other / foreign language</t>
+          <t>Pony/mule worker (works the animals, does not own them)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>कोई और / विदेशी भाषा</t>
+          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>obsenv</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Normal crowd, normal weather</t>
+          <t>Pony/mule owner (owns the animals)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>भीड़ और मौसम सामान्य</t>
+          <t>घोड़े/खच्चर का मालिक</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>obsenv</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>High crowd or peak hours</t>
+          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>ज़्यादा भीड़ या भीड़ का समय</t>
+          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>obsenv</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Rain or extreme weather</t>
+          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>बारिश या बहुत ख़राब मौसम</t>
+          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>obsenv</t>
+          <t>occ</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Both high crowd and bad weather</t>
+          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>भीड़ भी ज़्यादा और मौसम भी ख़राब</t>
+          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
@@ -14679,20 +14481,20 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Pony/mule worker (works the animals, does not own them)</t>
+          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर वाला (जानवर चलाते हैं, मालिक नहीं)</t>
+          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
@@ -14702,20 +14504,20 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pony/mule owner (owns the animals)</t>
+          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>घोड़े/खच्चर का मालिक</t>
+          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201">
@@ -14725,20 +14527,20 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Porter (carries on own back/shoulders - goods, luggage, or a person in a kandi)</t>
+          <t>Shop OWNER (goods, not prepared food)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>पोर्टर/कुली (अपनी पीठ या कंधे पर — सामान या कंडी में कोई व्यक्ति)</t>
+          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202">
@@ -14748,20 +14550,20 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Palki / dandi bearer (carries a person on a palanquin, as part of a team)</t>
+          <t>Hotel / lodge WORKER</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>पालकी / डंडी वाला (पालकी पर व्यक्ति, कई लोग मिलकर)</t>
+          <t>होटल / लॉज में काम</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203">
@@ -14771,20 +14573,20 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall WORKER (prepared food or tea)</t>
+          <t>Hotel / lodge OWNER</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान में काम (बना हुआ खाना या चाय)</t>
+          <t>होटल / लॉज का मालिक</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204">
@@ -14794,20 +14596,20 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Dhaba, tea stall or food stall OWNER (prepared food or tea)</t>
+          <t>Driver (any motor vehicle)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ढाबा, चाय या खाने की दुकान का मालिक</t>
+          <t>ड्राइवर (कोई भी गाड़ी)</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205">
@@ -14817,20 +14619,20 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Shop WORKER (goods: prasad, puja items, clothes, general store)</t>
+          <t>Guide</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>दुकान में काम (सामान: प्रसाद, पूजा का सामान, कपड़े, परचून)</t>
+          <t>गाइड</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206">
@@ -14840,20 +14642,20 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Shop OWNER (goods, not prepared food)</t>
+          <t>Wage labourer (construction, loading, odd jobs)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>दुकान का मालिक (सामान, बना हुआ खाना नहीं)</t>
+          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207">
@@ -14863,135 +14665,135 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hotel / lodge WORKER</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>होटल / लॉज में काम</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>offact</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hotel / lodge OWNER</t>
+          <t>Farming (crops)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>होटल / लॉज का मालिक</t>
+          <t>खेती (फ़सल)</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>offact</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Driver (any motor vehicle)</t>
+          <t>Livestock (animals)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ड्राइवर (कोई भी गाड़ी)</t>
+          <t>पशुपालन (जानवर)</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>offact</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Guide</t>
+          <t>Casual or daily wage labour</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>गाइड</t>
+          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>offact</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Wage labourer (construction, loading, odd jobs)</t>
+          <t>Construction work</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>दिहाड़ी मज़दूर (निर्माण, सामान चढ़ाना, फुटकर काम)</t>
+          <t>निर्माण का काम</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>occ</t>
+          <t>offact</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Own small shop, stall or trade</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>अपनी छोटी दुकान, ठेला या धंधा</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213">
@@ -15001,20 +14803,20 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Farming (crops)</t>
+          <t>Salaried job</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>खेती (फ़सल)</t>
+          <t>तनख़्वाह वाली नौकरी</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214">
@@ -15024,20 +14826,20 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Livestock (animals)</t>
+          <t>Some other work</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>पशुपालन (जानवर)</t>
+          <t>कोई और काम</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
     </row>
     <row r="215">
@@ -15047,279 +14849,279 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Casual or daily wage labour</t>
+          <t>There were no such months</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>दिहाड़ी या रोज़ की मज़दूरी</t>
+          <t>ऐसे कोई महीने नहीं थे</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>offact</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Construction work</t>
+          <t>Local (same district)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>निर्माण का काम</t>
+          <t>यहीं का (इसी ज़िले का)</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>offact</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Own small shop, stall or trade</t>
+          <t>Other Uttarakhand district</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>अपनी छोटी दुकान, ठेला या धंधा</t>
+          <t>उत्तराखंड का दूसरा ज़िला</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>offact</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Salaried job</t>
+          <t>Other Indian state</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>तनख़्वाह वाली नौकरी</t>
+          <t>भारत का दूसरा राज्य</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>offact</t>
+          <t>origin</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Some other work</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>कोई और काम</t>
+          <t>नेपाल</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>offact</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>There were no such months</t>
+          <t>Better income</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>ऐसे कोई महीने नहीं थे</t>
+          <t>ज़्यादा कमाई</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Local (same district)</t>
+          <t>Lost the previous work</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>यहीं का (इसी ज़िले का)</t>
+          <t>पहला काम छूट गया</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Other Uttarakhand district</t>
+          <t>Work ended with the season</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>उत्तराखंड का दूसरा ज़िला</t>
+          <t>मौसम के साथ काम ख़त्म हो गया</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Other Indian state</t>
+          <t>Family reasons</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>भारत का दूसरा राज्य</t>
+          <t>घर की वजह से</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>origin</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Health or injury</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>नेपाल</t>
+          <t>सेहत या चोट</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>permdk</t>
+          <t>prevreason</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Yes, it is allowed</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>हाँ, इसकी इजाज़त है</t>
+          <t>कोई और वजह</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>permdk</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>No, it is not allowed</t>
+          <t>A family member already working here</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>नहीं, मना है</t>
+          <t>यहाँ पहले से काम कर रहा घरवाला</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>permdk</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -15327,12 +15129,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Allowed only with a permit or a fee</t>
+          <t>A friend or someone from the village</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>सिर्फ़ परमिट या शुल्क देकर</t>
+          <t>दोस्त या गाँव का कोई आदमी</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -15342,967 +15144,967 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>permdk</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>A thekedar or contractor I now work for</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Better income</t>
+          <t>An agent or middleman who placed me (usually for a fee)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>ज़्यादा कमाई</t>
+          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Lost the previous work</t>
+          <t>No one; I found it myself</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>पहला काम छूट गया</t>
+          <t>कोई नहीं, ख़ुद ढूँढा</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Work ended with the season</t>
+          <t>The employer called me directly</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>मौसम के साथ काम ख़त्म हो गया</t>
+          <t>मालिक ने सीधे बुलाया</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Family reasons</t>
+          <t>Someone else</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>घर की वजह से</t>
+          <t>कोई और</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Health or injury</t>
+          <t>From my own phone (UPI or net banking)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>सेहत या चोट</t>
+          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>prevreason</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>In person at a bank branch or bank mitra / CSP</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>कोई और वजह</t>
+          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>A family member already working here</t>
+          <t>Money order or post office</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>यहाँ पहले से काम कर रहा घरवाला</t>
+          <t>मनीऑर्डर या डाकघर से</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>A friend or someone from the village</t>
+          <t>Sent with someone going home</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>दोस्त या गाँव का कोई आदमी</t>
+          <t>घर जा रहे किसी के हाथ</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>A thekedar or contractor I now work for</t>
+          <t>Carried it myself</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>ठेकेदार जिसके लिए मैं अब काम करता हूँ</t>
+          <t>ख़ुद लेकर गए</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>An agent or middleman who placed me (usually for a fee)</t>
+          <t>Through an agent or middleman</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>एजेंट या बिचौलिया जिसने लगवाया (आम तौर पर पैसे लेकर)</t>
+          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>remitmode</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>No one; I found it myself</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>कोई नहीं, ख़ुद ढूँढा</t>
+          <t>कोई और तरीक़ा</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>The employer called me directly</t>
+          <t>Thatch/wood/mud</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>मालिक ने सीधे बुलाया</t>
+          <t>फूस/लकड़ी/मिट्टी</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>referral</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Someone else</t>
+          <t>Tin/GI sheet</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>कोई और</t>
+          <t>टीन/चादर</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>roof</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>From my own phone (UPI or net banking)</t>
+          <t>Concrete/RCC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>अपने फ़ोन से (UPI या नेट बैंकिंग)</t>
+          <t>छत (कंक्रीट/RCC)</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>In person at a bank branch or bank mitra / CSP</t>
+          <t>More work for me</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>ख़ुद जाकर बैंक शाखा या बैंक मित्र / CSP पर</t>
+          <t>मेरे लिए ज़्यादा काम</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Money order or post office</t>
+          <t>Less work for me</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>मनीऑर्डर या डाकघर से</t>
+          <t>मेरे लिए कम काम</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Sent with someone going home</t>
+          <t>About the same</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>घर जा रहे किसी के हाथ</t>
+          <t>लगभग वैसा ही</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropexp</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Carried it myself</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>ख़ुद लेकर गए</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5</v>
+        <v>97</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Through an agent or middleman</t>
+          <t>People from these villages</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>किसी एजेंट या बिचौलिए के ज़रिए</t>
+          <t>इन गाँवों के लोगों को</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>remitmode</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>People from outside the area</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>कोई और तरीक़ा</t>
+          <t>इलाके के बाहर के लोगों को</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Thatch/wood/mud</t>
+          <t>Nobody will get jobs</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>फूस/लकड़ी/मिट्टी</t>
+          <t>किसी को नहीं मिलेंगी</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>ropjobs</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Tin/GI sheet</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>टीन/चादर</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>roof</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Concrete/RCC</t>
+          <t>Village (rural)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>छत (कंक्रीट/RCC)</t>
+          <t>गाँव में</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ropexp</t>
+          <t>ruralurban</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>More work for me</t>
+          <t>Town or city (urban)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>मेरे लिए ज़्यादा काम</t>
+          <t>शहर या क़स्बे में</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ropexp</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Less work for me</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>मेरे लिए कम काम</t>
+          <t>पुरुष</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ropexp</t>
+          <t>sex</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>About the same</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>लगभग वैसा ही</t>
+          <t>महिला</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ropexp</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Kedarnath (Gaurikund to Kedarnath)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ropjobs</t>
+          <t>site</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>People from these villages</t>
+          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>इन गाँवों के लोगों को</t>
+          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ropjobs</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>People from outside the area</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>इलाके के बाहर के लोगों को</t>
+          <t>समर्थन में</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ropjobs</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Nobody will get jobs</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>किसी को नहीं मिलेंगी</t>
+          <t>तटस्थ</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ropjobs</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Oppose</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>विरोध में</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>stance</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Village (rural)</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>गाँव में</t>
+          <t>बताना नहीं चाहते</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ruralurban</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Town or city (urban)</t>
+          <t>Andhra Pradesh</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>शहर या क़स्बे में</t>
+          <t>आंध्र प्रदेश</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Arunachal Pradesh</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>पुरुष</t>
+          <t>अरुणाचल प्रदेश</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>महिला</t>
+          <t>असम</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Kedarnath (Gaurikund to Kedarnath)</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>केदारनाथ (गौरीकुंड से केदारनाथ)</t>
+          <t>बिहार</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>site</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Hemkund Sahib (Govindghat to Hemkund)</t>
+          <t>Chhattisgarh</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>हेमकुंड साहिब (गोविंदघाट से हेमकुंड)</t>
+          <t>छत्तीसगढ़</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>समर्थन में</t>
+          <t>गोवा</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>तटस्थ</t>
+          <t>गुजरात</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Oppose</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>विरोध में</t>
+          <t>हरियाणा</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>stance</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Prefer not to say</t>
+          <t>Himachal Pradesh</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>बताना नहीं चाहते</t>
+          <t>हिमाचल प्रदेश</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270">
@@ -16312,20 +16114,20 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Andhra Pradesh</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>आंध्र प्रदेश</t>
+          <t>झारखंड</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
@@ -16335,20 +16137,20 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Arunachal Pradesh</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>अरुणाचल प्रदेश</t>
+          <t>कर्नाटक</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272">
@@ -16358,20 +16160,20 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>असम</t>
+          <t>केरल</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="273">
@@ -16381,20 +16183,20 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>बिहार</t>
+          <t>मध्य प्रदेश</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="274">
@@ -16404,20 +16206,20 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chhattisgarh</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>छत्तीसगढ़</t>
+          <t>महाराष्ट्र</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="275">
@@ -16427,20 +16229,20 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Manipur</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>गोवा</t>
+          <t>मणिपुर</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276">
@@ -16450,20 +16252,20 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Meghalaya</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>गुजरात</t>
+          <t>मेघालय</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="277">
@@ -16473,20 +16275,20 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Mizoram</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>हरियाणा</t>
+          <t>मिज़ोरम</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="278">
@@ -16496,20 +16298,20 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Himachal Pradesh</t>
+          <t>Nagaland</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>हिमाचल प्रदेश</t>
+          <t>नागालैंड</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="279">
@@ -16519,20 +16321,20 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>झारखंड</t>
+          <t>ओडिशा</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280">
@@ -16542,20 +16344,20 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>कर्नाटक</t>
+          <t>पंजाब</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281">
@@ -16565,20 +16367,20 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>केरल</t>
+          <t>राजस्थान</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="282">
@@ -16588,20 +16390,20 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Sikkim</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>मध्य प्रदेश</t>
+          <t>सिक्किम</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="283">
@@ -16611,20 +16413,20 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>महाराष्ट्र</t>
+          <t>तमिलनाडु</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="284">
@@ -16634,20 +16436,20 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Manipur</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>मणिपुर</t>
+          <t>तेलंगाना</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="285">
@@ -16657,20 +16459,20 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Meghalaya</t>
+          <t>Tripura</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>मेघालय</t>
+          <t>त्रिपुरा</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="286">
@@ -16680,20 +16482,20 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mizoram</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>मिज़ोरम</t>
+          <t>उत्तर प्रदेश</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="287">
@@ -16703,20 +16505,20 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Nagaland</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>नागालैंड</t>
+          <t>पश्चिम बंगाल</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="288">
@@ -16726,20 +16528,20 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Andaman and Nicobar Islands</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>ओडिशा</t>
+          <t>अंडमान और निकोबार द्वीप समूह</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="289">
@@ -16749,20 +16551,20 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>पंजाब</t>
+          <t>चंडीगढ़</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290">
@@ -16772,20 +16574,20 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>राजस्थान</t>
+          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="291">
@@ -16795,20 +16597,20 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Sikkim</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>सिक्किम</t>
+          <t>दिल्ली</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="292">
@@ -16818,20 +16620,20 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Jammu and Kashmir</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>तमिलनाडु</t>
+          <t>जम्मू और कश्मीर</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="293">
@@ -16841,20 +16643,20 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Ladakh</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>तेलंगाना</t>
+          <t>लद्दाख</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="294">
@@ -16864,20 +16666,20 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Tripura</t>
+          <t>Lakshadweep</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>त्रिपुरा</t>
+          <t>लक्षद्वीप</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="295">
@@ -16887,394 +16689,394 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Puducherry</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>उत्तर प्रदेश</t>
+          <t>पुदुच्चेरी</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Yes, regularly in my main Yatra work</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>पश्चिम बंगाल</t>
+          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Andaman and Nicobar Islands</t>
+          <t>Not in my main work, but done before elsewhere</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>अंडमान और निकोबार द्वीप समूह</t>
+          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>task3</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Never done</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>चंडीगढ़</t>
+          <t>कभी नहीं किया</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+          <t>No toilet / open defecation</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>दादरा और नगर हवेली तथा दमन और दीव</t>
+          <t>शौचालय नहीं / खुले में</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Pit latrine without slab or open pit</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>दिल्ली</t>
+          <t>बिना ढँके गड्ढे वाला शौचालय</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Jammu and Kashmir</t>
+          <t>Improved toilet, but shared with other households</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>जम्मू और कश्मीर</t>
+          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>toilet</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Ladakh</t>
+          <t>Improved toilet, used only by this household</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>लद्दाख</t>
+          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Lakshadweep</t>
+          <t>Private company</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>लक्षद्वीप</t>
+          <t>निजी कंपनी</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Puducherry</t>
+          <t>Government or public body</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>पुदुच्चेरी</t>
+          <t>सरकारी या सार्वजनिक विभाग</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Yes, regularly in my main Yatra work</t>
+          <t>A household (domestic work)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>हाँ, अपने मुख्य यात्रा-काम में नियमित</t>
+          <t>कोई घर (घरेलू काम)</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Not in my main work, but done before elsewhere</t>
+          <t>A contractor or agent</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>मुख्य काम में नहीं, पर पहले कहीं और किया है</t>
+          <t>ठेकेदार या एजेंट</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>task3</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Never done</t>
+          <t>An individual employer</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>कभी नहीं किया</t>
+          <t>कोई व्यक्ति जो सीधे पैसे देता है</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wageemp</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>No toilet / open defecation</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>शौचालय नहीं / खुले में</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Pit latrine without slab or open pit</t>
+          <t>Mud, thatch, bamboo or other natural material</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>बिना ढँके गड्ढे वाला शौचालय</t>
+          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Improved toilet, but shared with other households</t>
+          <t>Unburnt brick, wood or tin</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, पर दूसरे घरों के साथ साझा</t>
+          <t>कच्ची ईंट, लकड़ी या टीन</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>toilet</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Improved toilet, used only by this household</t>
+          <t>Burnt brick, cement, concrete or stone</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>अच्छा शौचालय, सिर्फ़ इसी घर के लिए</t>
+          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -17282,12 +17084,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Private company</t>
+          <t>Piped into the house or yard</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>निजी कंपनी</t>
+          <t>घर या आँगन में नल</t>
         </is>
       </c>
       <c r="E312" t="n">
@@ -17297,7 +17099,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -17305,12 +17107,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Government or public body</t>
+          <t>Public tap or standpipe</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>सरकारी या सार्वजनिक विभाग</t>
+          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
         </is>
       </c>
       <c r="E313" t="n">
@@ -17320,7 +17122,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -17328,12 +17130,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>A household (domestic work)</t>
+          <t>Handpump, tubewell or borewell</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>कोई घर (घरेलू काम)</t>
+          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
         </is>
       </c>
       <c r="E314" t="n">
@@ -17343,7 +17145,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -17351,12 +17153,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>A contractor or agent</t>
+          <t>Protected well or protected spring</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>ठेकेदार या एजेंट</t>
+          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -17366,7 +17168,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -17374,12 +17176,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>An individual employer</t>
+          <t>Rainwater collection</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>कोई व्यक्ति जो सीधे पैसे देता है</t>
+          <t>बारिश का पानी जमा करके</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -17389,99 +17191,99 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>wageemp</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Don't know</t>
+          <t>Bottled, packaged or community RO</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>पता नहीं</t>
+          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mud, thatch, bamboo or other natural material</t>
+          <t>Unprotected well or unprotected spring</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>मिट्टी, फूस, बाँस या ऐसी ही कोई चीज़</t>
+          <t>खुला कुआँ या खुला सोता</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Unburnt brick, wood or tin</t>
+          <t>River, stream, pond or canal</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>कच्ची ईंट, लकड़ी या टीन</t>
+          <t>नदी, गाड़, तालाब या नहर</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>water</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Burnt brick, cement, concrete or stone</t>
+          <t>Tanker truck or cart with drum</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>पक्की ईंट, सीमेंट, कंक्रीट या पत्थर</t>
+          <t>टैंकर या ड्रम वाली गाड़ी</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -17489,12 +17291,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Piped into the house or yard</t>
+          <t>No difficulty</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>घर या आँगन में नल</t>
+          <t>कोई दिक़्क़त नहीं</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -17504,7 +17306,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -17512,12 +17314,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Public tap or standpipe</t>
+          <t>Some difficulty</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>सार्वजनिक नल या स्टैंडपोस्ट</t>
+          <t>थोड़ी दिक़्क़त</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -17527,7 +17329,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -17535,12 +17337,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Handpump, tubewell or borewell</t>
+          <t>A lot of difficulty</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>हैंडपंप, ट्यूबवेल या बोरवेल</t>
+          <t>बहुत दिक़्क़त</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -17550,7 +17352,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>wgdiff</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -17558,12 +17360,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Protected well or protected spring</t>
+          <t>Cannot do it at all</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ढका हुआ कुआँ या ढका हुआ सोता</t>
+          <t>बिलकुल नहीं कर पाते</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -17573,122 +17375,122 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Rainwater collection</t>
+          <t>Yes, through work</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>बारिश का पानी जमा करके</t>
+          <t>हाँ, काम की तरफ़ से</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bottled, packaged or community RO</t>
+          <t>Only private or other insurance</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>बोतलबंद, पैकेट या सामुदायिक RO</t>
+          <t>सिर्फ़ अपना या कोई और बीमा</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Unprotected well or unprotected spring</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>खुला कुआँ या खुला सोता</t>
+          <t>कोई नहीं</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>workins</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>River, stream, pond or canal</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>नदी, गाड़, तालाब या नहर</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Tanker truck or cart with drum</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>टैंकर या ड्रम वाली गाड़ी</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>yn</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -17696,12 +17498,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>No difficulty</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>कोई दिक़्क़त नहीं</t>
+          <t>हाँ</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -17711,276 +17513,69 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>yndk</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Some difficulty</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>थोड़ी दिक़्क़त</t>
+          <t>नहीं</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>yndk</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>A lot of difficulty</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>बहुत दिक़्क़त</t>
+          <t>हाँ</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>wgdiff</t>
+          <t>yndk</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Cannot do it at all</t>
+          <t>Don't know</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>बिलकुल नहीं कर पाते</t>
+          <t>पता नहीं</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>workins</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>1</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Yes, through work</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>हाँ, काम की तरफ़ से</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>workins</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>2</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Only private or other insurance</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>सिर्फ़ अपना या कोई और बीमा</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>workins</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>3</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>कोई नहीं</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>workins</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>4</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Don't know</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>पता नहीं</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>yn</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>0</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>नहीं</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>yn</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>1</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>हाँ</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>yndk</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>नहीं</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>yndk</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>1</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>हाँ</t>
-        </is>
-      </c>
-      <c r="E341" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>yndk</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>97</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Don't know</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>पता नहीं</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
         <v>97</v>
       </c>
     </row>

--- a/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
+++ b/replication/final_instrument/questionnaire/Kedarnath_final_kobo.xlsx
@@ -12024,12 +12024,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Enumerator 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>रमन</t>
+          <t>सर्वेक्षक 1</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rishit</t>
+          <t>Enumerator 2</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ऋषित</t>
+          <t>सर्वेक्षक 2</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -12070,12 +12070,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tanmay</t>
+          <t>Enumerator 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>तन्मय</t>
+          <t>सर्वेक्षक 3</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -12093,12 +12093,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Anuj</t>
+          <t>Enumerator 4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>अनुज</t>
+          <t>सर्वेक्षक 4</t>
         </is>
       </c>
       <c r="E95" t="n">
